--- a/data/ventilation.xlsx
+++ b/data/ventilation.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ล่าสุด'!$A$1:$I$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,7 +45,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00143B59"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,12 +76,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -516,7 +523,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>625</v>
+        <v>125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -525,7 +532,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -535,7 +542,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:12.865286+07:00</t>
+          <t>2026-10-21T09:43:31.589597+07:00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -548,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -557,7 +564,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1625</v>
+        <v>1000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -566,7 +573,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -576,7 +583,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:34.791540+07:00</t>
+          <t>2026-10-21T09:42:59.941802+07:00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -589,7 +596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -598,7 +605,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1250</v>
+        <v>875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -607,7 +614,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -617,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:05.128336+07:00</t>
+          <t>2026-10-21T09:43:24.167462+07:00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -630,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -648,7 +655,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -658,7 +665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:51.847235+07:00</t>
+          <t>2026-10-21T09:43:15.312133+07:00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -671,7 +678,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -680,7 +687,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>375</v>
+        <v>875</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -689,7 +696,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -699,7 +706,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:45.064387+07:00</t>
+          <t>2026-10-21T09:43:09.056689+07:00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -712,7 +719,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -721,7 +728,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1500</v>
+        <v>1375</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -730,7 +737,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -740,7 +747,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:47.723281+07:00</t>
+          <t>2026-10-21T09:43:11.226853+07:00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -753,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -762,7 +769,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -771,7 +778,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -781,7 +788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:07.806420+07:00</t>
+          <t>2026-10-21T09:43:27.243076+07:00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -794,7 +801,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -803,7 +810,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1750</v>
+        <v>250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -812,7 +819,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -822,7 +829,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:05.160048+07:00</t>
+          <t>2026-10-21T09:43:25.326826+07:00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -835,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -844,7 +851,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -853,7 +860,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -863,7 +870,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:05.213501+07:00</t>
+          <t>2026-10-21T09:43:25.726303+07:00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -876,7 +883,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -885,7 +892,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -894,7 +901,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -904,7 +911,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:58.053209+07:00</t>
+          <t>2026-10-21T09:43:20.779015+07:00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -917,7 +924,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -926,7 +933,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2375</v>
+        <v>2625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -935,7 +942,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -945,7 +952,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:54.423477+07:00</t>
+          <t>2026-10-21T09:43:17.013772+07:00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -956,50 +963,44 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>ชุมพร</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-10-19 00Z</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-10-20T12:46:11.122785+07:00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:29.896326+07:00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>cannot_locate_bar</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1008,7 +1009,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>125</v>
+        <v>375</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1017,7 +1018,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1027,7 +1028,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:12.941622+07:00</t>
+          <t>2026-10-21T09:43:33.143661+07:00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1040,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1058,7 +1059,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1068,7 +1069,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:07.811220+07:00</t>
+          <t>2026-10-21T09:43:27.337986+07:00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1081,7 +1082,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1099,7 +1100,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1109,7 +1110,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:42.414874+07:00</t>
+          <t>2026-10-21T09:43:07.148513+07:00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1122,7 +1123,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1131,7 +1132,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1125</v>
+        <v>375</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1140,7 +1141,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1150,7 +1151,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:00.712826+07:00</t>
+          <t>2026-10-21T09:43:22.503098+07:00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1163,7 +1164,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1172,7 +1173,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1375</v>
+        <v>625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1181,7 +1182,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1191,7 +1192,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:37.173194+07:00</t>
+          <t>2026-10-21T09:43:01.701313+07:00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1204,7 +1205,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1213,7 +1214,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>750</v>
+        <v>1375</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1222,7 +1223,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1232,7 +1233,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:49.654301+07:00</t>
+          <t>2026-10-21T09:43:12.674121+07:00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1245,7 +1246,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1254,7 +1255,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1375</v>
+        <v>1000</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1263,7 +1264,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1273,7 +1274,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:56.093195+07:00</t>
+          <t>2026-10-21T09:43:18.952911+07:00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1286,7 +1287,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1295,7 +1296,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>625</v>
+        <v>375</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1304,7 +1305,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1314,7 +1315,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:12.762426+07:00</t>
+          <t>2026-10-21T09:43:31.481641+07:00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1327,7 +1328,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1336,7 +1337,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1345,7 +1346,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1355,7 +1356,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:58.045514+07:00</t>
+          <t>2026-10-21T09:43:19.094054+07:00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1368,7 +1369,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1377,7 +1378,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1375</v>
+        <v>625</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1386,7 +1387,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1396,7 +1397,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:34.792443+07:00</t>
+          <t>2026-10-21T09:42:59.942590+07:00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1409,7 +1410,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1427,7 +1428,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1437,7 +1438,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:14.616337+07:00</t>
+          <t>2026-10-21T09:43:34.811501+07:00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1450,7 +1451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1468,7 +1469,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1478,7 +1479,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:39.820596+07:00</t>
+          <t>2026-10-21T09:43:04.760658+07:00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1491,7 +1492,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1500,7 +1501,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>250</v>
+        <v>625</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1509,7 +1510,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1519,7 +1520,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:47.723964+07:00</t>
+          <t>2026-10-21T09:43:11.235316+07:00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1532,7 +1533,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1541,7 +1542,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1500</v>
+        <v>875</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1550,7 +1551,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1560,7 +1561,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:55.984486+07:00</t>
+          <t>2026-10-21T09:43:17.040027+07:00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1573,7 +1574,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1582,7 +1583,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1375</v>
+        <v>625</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1591,7 +1592,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1601,7 +1602,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:34.793021+07:00</t>
+          <t>2026-10-21T09:42:59.943147+07:00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1614,7 +1615,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1623,7 +1624,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1632,7 +1633,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1642,7 +1643,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:09.653953+07:00</t>
+          <t>2026-10-21T09:43:29.882121+07:00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1655,7 +1656,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1664,7 +1665,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1625</v>
+        <v>500</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1673,7 +1674,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1683,7 +1684,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:07.785359+07:00</t>
+          <t>2026-10-21T09:43:25.768646+07:00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1696,7 +1697,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1705,7 +1706,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>250</v>
+        <v>625</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1714,7 +1715,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1724,7 +1725,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:14.388627+07:00</t>
+          <t>2026-10-21T09:43:33.176227+07:00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1737,7 +1738,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1746,7 +1747,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1755,7 +1756,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1765,7 +1766,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:00.705031+07:00</t>
+          <t>2026-10-21T09:43:20.830356+07:00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1778,7 +1779,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1796,7 +1797,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1806,7 +1807,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:39.820018+07:00</t>
+          <t>2026-10-21T09:43:04.353293+07:00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1819,7 +1820,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1828,7 +1829,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1837,7 +1838,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1847,7 +1848,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:11.312313+07:00</t>
+          <t>2026-10-21T09:43:31.458513+07:00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1860,7 +1861,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1869,7 +1870,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1125</v>
+        <v>875</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1878,7 +1879,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1888,7 +1889,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:12.887238+07:00</t>
+          <t>2026-10-21T09:43:33.060988+07:00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1901,7 +1902,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1919,7 +1920,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1929,7 +1930,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:45.065045+07:00</t>
+          <t>2026-10-21T09:43:09.057665+07:00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1942,7 +1943,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1951,7 +1952,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>500</v>
+        <v>125</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1960,7 +1961,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1970,7 +1971,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:45.064099+07:00</t>
+          <t>2026-10-21T09:43:08.198022+07:00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1983,7 +1984,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1992,7 +1993,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1750</v>
+        <v>1625</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2001,7 +2002,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2011,7 +2012,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:09.494528+07:00</t>
+          <t>2026-10-21T09:43:28.253989+07:00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2024,7 +2025,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2033,7 +2034,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2375</v>
+        <v>2000</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2042,7 +2043,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2052,7 +2053,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:54.242287+07:00</t>
+          <t>2026-10-21T09:43:15.325269+07:00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2065,7 +2066,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2074,16 +2075,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1375</v>
+        <v>2375</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2093,7 +2094,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:51.738404+07:00</t>
+          <t>2026-10-21T09:43:15.301176+07:00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2106,7 +2107,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2115,7 +2116,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2124,7 +2125,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2134,7 +2135,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:14.545477+07:00</t>
+          <t>2026-10-21T09:43:34.684282+07:00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2147,7 +2148,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2156,7 +2157,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>625</v>
+        <v>1750</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2165,7 +2166,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2175,7 +2176,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:55.959458+07:00</t>
+          <t>2026-10-21T09:43:17.034264+07:00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2188,7 +2189,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2197,7 +2198,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1375</v>
+        <v>875</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2206,7 +2207,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2216,7 +2217,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:11.162506+07:00</t>
+          <t>2026-10-21T09:43:29.948723+07:00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2229,7 +2230,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2238,7 +2239,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1625</v>
+        <v>875</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2247,7 +2248,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2257,7 +2258,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:05.538230+07:00</t>
+          <t>2026-10-21T09:43:25.763293+07:00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2270,7 +2271,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2279,7 +2280,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1125</v>
+        <v>1500</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2288,7 +2289,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2298,7 +2299,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:02.591837+07:00</t>
+          <t>2026-10-21T09:43:22.512830+07:00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2311,7 +2312,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2329,7 +2330,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2339,7 +2340,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:54.306122+07:00</t>
+          <t>2026-10-21T09:43:15.328040+07:00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2352,7 +2353,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2361,7 +2362,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1500</v>
+        <v>625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2370,7 +2371,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2380,7 +2381,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:02.752058+07:00</t>
+          <t>2026-10-21T09:43:24.109329+07:00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2393,7 +2394,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2402,7 +2403,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2411,7 +2412,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2421,7 +2422,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:42.413403+07:00</t>
+          <t>2026-10-21T09:43:06.145893+07:00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2434,7 +2435,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2452,7 +2453,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2462,7 +2463,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:39.945500+07:00</t>
+          <t>2026-10-21T09:43:04.761497+07:00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2475,7 +2476,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2484,7 +2485,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>250</v>
+        <v>1125</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2493,7 +2494,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2503,7 +2504,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:56.083611+07:00</t>
+          <t>2026-10-21T09:43:18.887600+07:00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2516,7 +2517,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2525,7 +2526,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1625</v>
+        <v>1750</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2534,7 +2535,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2544,7 +2545,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:51.736034+07:00</t>
+          <t>2026-10-21T09:43:13.268757+07:00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2557,7 +2558,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2566,7 +2567,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2575,7 +2576,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2585,7 +2586,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:09.436146+07:00</t>
+          <t>2026-10-21T09:43:27.375750+07:00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2598,7 +2599,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2607,7 +2608,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2616,7 +2617,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2626,7 +2627,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:14.542980+07:00</t>
+          <t>2026-10-21T09:43:33.209518+07:00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2639,7 +2640,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2648,7 +2649,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1375</v>
+        <v>500</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2657,7 +2658,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2667,7 +2668,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:34.793899+07:00</t>
+          <t>2026-10-21T09:42:59.944004+07:00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2680,7 +2681,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2689,7 +2690,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>875</v>
+        <v>1125</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2698,7 +2699,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2708,7 +2709,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:04.016999+07:00</t>
+          <t>2026-10-21T09:43:24.155602+07:00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2721,7 +2722,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2730,7 +2731,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1250</v>
+        <v>1125</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2739,7 +2740,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2749,7 +2750,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:37.302934+07:00</t>
+          <t>2026-10-21T09:43:01.864362+07:00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2760,50 +2761,44 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>สระบุรี</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>625</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026-10-19 00Z</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2026-10-20T12:46:02.538670+07:00</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:22.503997+07:00</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_418000.png</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>cannot_locate_bar</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2812,7 +2807,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1625</v>
+        <v>750</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2821,7 +2816,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2831,7 +2826,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:07.805930+07:00</t>
+          <t>2026-10-21T09:43:26.779898+07:00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2844,7 +2839,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2853,7 +2848,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2862,7 +2857,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2872,7 +2867,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:00.708692+07:00</t>
+          <t>2026-10-21T09:43:22.476108+07:00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2885,7 +2880,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2903,7 +2898,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2913,7 +2908,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:02.628212+07:00</t>
+          <t>2026-10-21T09:43:23.825668+07:00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2926,7 +2921,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2935,7 +2930,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1125</v>
+        <v>250</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2944,7 +2939,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2954,7 +2949,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:11.180114+07:00</t>
+          <t>2026-10-21T09:43:31.423781+07:00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2967,7 +2962,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2976,7 +2971,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>500</v>
+        <v>1625</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2985,7 +2980,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2995,7 +2990,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:58.044822+07:00</t>
+          <t>2026-10-21T09:43:18.962019+07:00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3008,7 +3003,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3017,7 +3012,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>625</v>
+        <v>750</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3026,7 +3021,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3036,7 +3031,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:45.062989+07:00</t>
+          <t>2026-10-21T09:43:08.193258+07:00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3049,7 +3044,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3058,7 +3053,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3067,7 +3062,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3077,7 +3072,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:49.652976+07:00</t>
+          <t>2026-10-21T09:43:11.731628+07:00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3090,7 +3085,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3099,7 +3094,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>125</v>
+        <v>1000</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3108,7 +3103,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3118,7 +3113,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:51.664008+07:00</t>
+          <t>2026-10-21T09:43:13.239790+07:00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3131,7 +3126,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3140,16 +3135,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3159,7 +3154,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:54.320315+07:00</t>
+          <t>2026-10-21T09:43:17.012490+07:00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3172,7 +3167,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3181,7 +3176,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>125</v>
+        <v>875</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3190,7 +3185,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3200,7 +3195,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:49.654883+07:00</t>
+          <t>2026-10-21T09:43:12.895504+07:00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3213,7 +3208,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3222,7 +3217,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3231,7 +3226,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3241,7 +3236,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:42.415551+07:00</t>
+          <t>2026-10-21T09:43:07.333278+07:00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3254,7 +3249,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3263,7 +3258,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3272,7 +3267,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3282,7 +3277,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:58.046131+07:00</t>
+          <t>2026-10-21T09:43:20.777992+07:00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3295,7 +3290,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3313,7 +3308,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3323,7 +3318,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:47.722725+07:00</t>
+          <t>2026-10-21T09:43:10.099027+07:00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3336,7 +3331,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3354,7 +3349,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3364,7 +3359,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:00.703845+07:00</t>
+          <t>2026-10-21T09:43:20.788981+07:00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3377,7 +3372,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3395,7 +3390,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3405,7 +3400,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:37.496768+07:00</t>
+          <t>2026-10-21T09:43:02.441458+07:00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3418,7 +3413,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3427,7 +3422,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>750</v>
+        <v>625</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3436,7 +3431,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3446,7 +3441,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:37.469717+07:00</t>
+          <t>2026-10-21T09:43:02.249349+07:00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3459,7 +3454,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3468,7 +3463,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>500</v>
+        <v>875</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3477,7 +3472,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3487,7 +3482,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-20T12:46:09.505332+07:00</t>
+          <t>2026-10-21T09:43:29.831480+07:00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3500,7 +3495,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3509,7 +3504,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3518,7 +3513,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3528,7 +3523,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:47.722301+07:00</t>
+          <t>2026-10-21T09:43:10.086658+07:00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3541,7 +3536,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3550,7 +3545,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>625</v>
+        <v>1000</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3559,7 +3554,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3569,7 +3564,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:49.654037+07:00</t>
+          <t>2026-10-21T09:43:11.750998+07:00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3582,7 +3577,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3600,7 +3595,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3610,7 +3605,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:42.414322+07:00</t>
+          <t>2026-10-21T09:43:06.344622+07:00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3623,7 +3618,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3632,7 +3627,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>375</v>
+        <v>625</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3641,7 +3636,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-19 00Z</t>
+          <t>2026-10-20 00Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3651,7 +3646,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-20T12:45:39.763414+07:00</t>
+          <t>2026-10-21T09:43:04.348109+07:00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3752,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6970,8 +6965,3153 @@
       </c>
       <c r="I78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>กระบี่</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>125</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:31.589597+07:00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_566202.png</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:42:59.941802+07:00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_455301.png</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>875</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:24.167462+07:00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_450201.png</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>กาฬสินธุ์</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:15.312133+07:00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_388401.png</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>กำแพงเพชร</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>875</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:09.056689+07:00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_380201.png</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ขอนแก่น</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:11.226853+07:00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_381201.png</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>จันทบุรี</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>500</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:27.243076+07:00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_480201.png</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ฉะเชิงเทรา</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>250</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:25.326826+07:00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_423301.png</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ชลบุรี</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>250</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:25.726303+07:00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_459201.png</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ชัยนาท</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>500</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:20.779015+07:00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_402301.png</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ชัยภูมิ</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2625</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:17.013772+07:00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_403201.png</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n"/>
+      <c r="D90" s="3" t="inlineStr"/>
+      <c r="E90" s="3" t="inlineStr"/>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:29.896326+07:00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>cannot_locate_bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ตรัง</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>375</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:33.143661+07:00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_567201.png</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ตราด</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>500</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:27.337986+07:00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_501201.png</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ตาก</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>875</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:07.148513+07:00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_376201.png</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>375</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:22.503098+07:00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_417201.png</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>625</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:01.701313+07:00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>นครพนม</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:12.674121+07:00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_357201.png</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>นครราชสีมา</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:18.952911+07:00</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_431201.png</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>นครศรีธรรมราช</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>375</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:31.481641+07:00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_552201.png</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>นครสวรรค์</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>375</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:19.094054+07:00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_400201.png</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>625</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:42:59.942590+07:00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_411000.png</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>นราธิวาส</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>375</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:34.811501+07:00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_583201.png</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>น่าน</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>250</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:04.760658+07:00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_331201.png</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>บึงกาฬ</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>625</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:11.235316+07:00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_363201.png</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>บุรีรัมย์</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>875</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:17.040027+07:00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_436201.png</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ปทุมธานี</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>625</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:42:59.943147+07:00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_419301.png</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ประจวบคีรีขันธ์</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>250</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:29.882121+07:00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_500201.png</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ปราจีนบุรี</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>500</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:25.768646+07:00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_430201.png</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>625</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:33.176227+07:00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>พระนครศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>375</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:20.830356+07:00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>พะเยา</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:04.353293+07:00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_310201.png</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>พังงา</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>750</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:31.458513+07:00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_561201.png</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>พัทลุง</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>875</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:33.060988+07:00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_560301.png</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>พิจิตร</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>500</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:09.057665+07:00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_386301.png</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>125</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:08.198022+07:00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_378201.png</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ภูเก็ต</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:28.253989+07:00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_564201.png</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>มหาสารคาม</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:15.325269+07:00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_387401.png</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>มุกดาหาร</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:15.301176+07:00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ยะลา</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>250</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:34.684282+07:00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_581301.png</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ยโสธร</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:17.034264+07:00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_406201.png</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ระนอง</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>875</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:29.948723+07:00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_532201.png</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ระยอง</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>875</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:25.763293+07:00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ราชบุรี</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:22.512830+07:00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:15.328040+07:00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_405201.png</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ลพบุรี</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>625</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:24.109329+07:00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_426201.png</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ลำปาง</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>250</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:06.145893+07:00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_328201.png</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ลำพูน</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>375</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:04.761497+07:00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_329201.png</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ศรีสะเกษ</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:18.887600+07:00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_409301.png</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>สกลนคร</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:13.268757+07:00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_356201.png</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>สงขลา</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>750</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:27.375750+07:00</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_568501.png</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>สตูล</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>500</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:33.209518+07:00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_570201.png</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>สมุทรปราการ</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>500</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:42:59.944004+07:00</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_429301.png</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>สมุทรสงคราม</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:24.155602+07:00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_438201.png</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>สมุทรสาคร</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:01.864362+07:00</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_474000.png</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>สระบุรี</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n"/>
+      <c r="D134" s="3" t="inlineStr"/>
+      <c r="E134" s="3" t="inlineStr"/>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:22.503997+07:00</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_418000.png</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>cannot_locate_bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>สระแก้ว</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>750</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:26.779898+07:00</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_440401.png</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>สิงห์บุรี</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>750</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:22.476108+07:00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_416000.png</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>750</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:23.825668+07:00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_425201.png</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>สุราษฎร์ธานี</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>250</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:31.423781+07:00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_551201.png</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>สุรินทร์</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:18.962019+07:00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_432201.png</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>สุโขทัย</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>750</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:08.193258+07:00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_373201.png</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>หนองคาย</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>750</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:11.731628+07:00</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_352201.png</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>หนองบัวลำภู</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:13.239790+07:00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_360201.png</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>อำนาจเจริญ</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:17.012490+07:00</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>อุดรธานี</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>875</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:12.895504+07:00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>อุตรดิตถ์</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>375</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:07.333278+07:00</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_351201.png</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>อุทัยธานี</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>500</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:20.777992+07:00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_410201.png</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>อุบลราชธานี</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>375</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:10.099027+07:00</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_407501.png</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>อ่างทอง</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>500</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:20.788981+07:00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_414000.png</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>เชียงราย</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:02.441458+07:00</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_303201.png</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>เชียงใหม่</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>625</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:02.249349+07:00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_327501.png</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>เพชรบุรี</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>875</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:29.831480+07:00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_465201.png</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>500</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:10.086658+07:00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_379201.png</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>เลย</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:11.750998+07:00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_353201.png</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>แพร่</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>250</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:06.344622+07:00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_330201.png</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>แม่ฮ่องสอน</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>625</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2026-10-20 00Z</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:04.348109+07:00</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_300201.png</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I78"/>
+  <autoFilter ref="A1:I155"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -7050,6 +10190,83 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId154"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7061,7 +10278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7122,8 +10339,82 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:29.896326+07:00</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>cannot_locate_bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>สระบุรี</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21T09:43:22.503997+07:00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_418000.png</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>cannot_locate_bar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I3"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/ventilation.xlsx
+++ b/data/ventilation.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ล่าสุด'!$A$1:$I$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$232</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:31.589597+07:00</t>
+          <t>2026-10-22T09:44:23.834381+07:00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1000</v>
+        <v>875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-21T09:42:59.941802+07:00</t>
+          <t>2026-10-22T09:43:43.686013+07:00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>875</v>
+        <v>375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:24.167462+07:00</t>
+          <t>2026-10-22T09:44:16.222253+07:00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2500</v>
+        <v>2875</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:15.312133+07:00</t>
+          <t>2026-10-22T09:44:02.024196+07:00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>875</v>
+        <v>625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:09.056689+07:00</t>
+          <t>2026-10-22T09:43:53.560960+07:00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1375</v>
+        <v>1250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:11.226853+07:00</t>
+          <t>2026-10-22T09:43:56.361941+07:00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:27.243076+07:00</t>
+          <t>2026-10-22T09:44:19.451646+07:00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>250</v>
+        <v>625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:25.326826+07:00</t>
+          <t>2026-10-22T09:44:16.415797+07:00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>250</v>
+        <v>625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:25.726303+07:00</t>
+          <t>2026-10-22T09:44:16.649608+07:00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:20.779015+07:00</t>
+          <t>2026-10-22T09:44:10.922684+07:00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -933,16 +933,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2625</v>
+        <v>1625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:17.013772+07:00</t>
+          <t>2026-10-22T09:44:04.855944+07:00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -963,44 +963,50 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>ชุมพร</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21T09:43:29.896326+07:00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="C13" t="n">
+        <v>125</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:21.719633+07:00</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>cannot_locate_bar</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1018,7 +1024,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1028,7 +1034,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:33.143661+07:00</t>
+          <t>2026-10-22T09:44:26.064700+07:00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1041,7 +1047,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1050,7 +1056,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1059,7 +1065,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1069,7 +1075,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:27.337986+07:00</t>
+          <t>2026-10-22T09:44:19.481744+07:00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1082,7 +1088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1091,7 +1097,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>875</v>
+        <v>625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1100,7 +1106,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1110,7 +1116,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:07.148513+07:00</t>
+          <t>2026-10-22T09:43:51.186310+07:00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1123,7 +1129,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1132,7 +1138,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1141,7 +1147,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1151,7 +1157,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:22.503098+07:00</t>
+          <t>2026-10-22T09:44:12.878835+07:00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1164,7 +1170,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1182,7 +1188,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1192,7 +1198,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:01.701313+07:00</t>
+          <t>2026-10-22T09:43:46.037025+07:00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1205,7 +1211,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1214,7 +1220,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1375</v>
+        <v>1000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1223,7 +1229,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1233,7 +1239,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:12.674121+07:00</t>
+          <t>2026-10-22T09:43:59.174478+07:00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1246,7 +1252,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1255,7 +1261,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1264,7 +1270,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1274,7 +1280,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:18.952911+07:00</t>
+          <t>2026-10-22T09:44:08.033356+07:00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1287,7 +1293,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1296,7 +1302,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>375</v>
+        <v>1250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1305,7 +1311,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1315,7 +1321,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:31.481641+07:00</t>
+          <t>2026-10-22T09:44:23.555766+07:00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1328,7 +1334,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1346,7 +1352,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1356,7 +1362,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:19.094054+07:00</t>
+          <t>2026-10-22T09:44:09.805249+07:00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1369,7 +1375,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1378,7 +1384,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>625</v>
+        <v>1125</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1387,7 +1393,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1397,7 +1403,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-21T09:42:59.942590+07:00</t>
+          <t>2026-10-22T09:43:43.686843+07:00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1410,7 +1416,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1419,7 +1425,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>375</v>
+        <v>625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1428,7 +1434,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1438,7 +1444,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:34.811501+07:00</t>
+          <t>2026-10-22T09:44:28.260154+07:00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1451,7 +1457,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1460,7 +1466,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1469,7 +1475,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1479,7 +1485,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:04.760658+07:00</t>
+          <t>2026-10-22T09:43:48.803759+07:00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1492,7 +1498,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1501,7 +1507,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1510,7 +1516,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1520,7 +1526,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:11.235316+07:00</t>
+          <t>2026-10-22T09:43:56.610240+07:00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1533,7 +1539,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1542,7 +1548,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>875</v>
+        <v>1625</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1551,7 +1557,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1561,7 +1567,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:17.040027+07:00</t>
+          <t>2026-10-22T09:44:07.742743+07:00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1574,7 +1580,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1583,7 +1589,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>625</v>
+        <v>1125</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1592,7 +1598,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1602,7 +1608,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-21T09:42:59.943147+07:00</t>
+          <t>2026-10-22T09:43:43.687358+07:00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1615,7 +1621,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1633,7 +1639,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1643,7 +1649,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:29.882121+07:00</t>
+          <t>2026-10-22T09:44:21.339850+07:00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1656,7 +1662,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1665,7 +1671,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1674,7 +1680,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1684,7 +1690,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:25.768646+07:00</t>
+          <t>2026-10-22T09:44:18.029847+07:00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1697,7 +1703,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1706,7 +1712,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>625</v>
+        <v>1125</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1715,7 +1721,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1725,7 +1731,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:33.176227+07:00</t>
+          <t>2026-10-22T09:44:26.085033+07:00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1738,7 +1744,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1747,7 +1753,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>375</v>
+        <v>1750</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1756,7 +1762,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1766,7 +1772,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:20.830356+07:00</t>
+          <t>2026-10-22T09:44:12.611685+07:00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1779,7 +1785,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1788,7 +1794,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1797,7 +1803,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1807,7 +1813,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:04.353293+07:00</t>
+          <t>2026-10-22T09:43:48.589750+07:00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1820,7 +1826,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1829,7 +1835,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>750</v>
+        <v>1125</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1838,7 +1844,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1848,7 +1854,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:31.458513+07:00</t>
+          <t>2026-10-22T09:44:23.161155+07:00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1861,7 +1867,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1870,7 +1876,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>875</v>
+        <v>1000</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1879,7 +1885,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1889,7 +1895,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:33.060988+07:00</t>
+          <t>2026-10-22T09:44:26.037910+07:00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1902,7 +1908,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1911,7 +1917,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1920,7 +1926,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1930,7 +1936,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:09.057665+07:00</t>
+          <t>2026-10-22T09:43:54.801885+07:00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1943,7 +1949,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1952,7 +1958,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>125</v>
+        <v>375</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1961,7 +1967,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1971,7 +1977,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:08.198022+07:00</t>
+          <t>2026-10-22T09:43:53.559340+07:00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1984,7 +1990,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1993,7 +1999,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1625</v>
+        <v>1000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2002,7 +2008,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2012,7 +2018,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:28.253989+07:00</t>
+          <t>2026-10-22T09:44:20.241825+07:00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2025,7 +2031,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2034,7 +2040,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2000</v>
+        <v>2125</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2043,7 +2049,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2053,7 +2059,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:15.325269+07:00</t>
+          <t>2026-10-22T09:44:02.637226+07:00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2066,7 +2072,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2075,7 +2081,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2375</v>
+        <v>2625</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2084,7 +2090,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2094,7 +2100,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:15.301176+07:00</t>
+          <t>2026-10-22T09:44:01.847840+07:00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2107,7 +2113,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2116,7 +2122,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2125,7 +2131,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2135,7 +2141,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:34.684282+07:00</t>
+          <t>2026-10-22T09:44:27.972797+07:00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2148,7 +2154,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2166,7 +2172,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2176,7 +2182,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:17.034264+07:00</t>
+          <t>2026-10-22T09:44:04.863243+07:00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2189,7 +2195,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2198,7 +2204,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>875</v>
+        <v>1250</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2207,7 +2213,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2217,7 +2223,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:29.948723+07:00</t>
+          <t>2026-10-22T09:44:22.031921+07:00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2230,7 +2236,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2239,7 +2245,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>875</v>
+        <v>750</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2248,7 +2254,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2258,7 +2264,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:25.763293+07:00</t>
+          <t>2026-10-22T09:44:17.160198+07:00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2271,7 +2277,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2280,7 +2286,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2289,7 +2295,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2299,7 +2305,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:22.512830+07:00</t>
+          <t>2026-10-22T09:44:14.416804+07:00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2312,7 +2318,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2321,7 +2327,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2000</v>
+        <v>2625</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2330,7 +2336,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2340,7 +2346,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:15.328040+07:00</t>
+          <t>2026-10-22T09:44:04.839375+07:00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2353,7 +2359,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2362,7 +2368,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>625</v>
+        <v>1500</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2371,7 +2377,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2381,7 +2387,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:24.109329+07:00</t>
+          <t>2026-10-22T09:44:14.800697+07:00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2394,7 +2400,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2412,7 +2418,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2422,7 +2428,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:06.145893+07:00</t>
+          <t>2026-10-22T09:43:50.574688+07:00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2435,7 +2441,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2444,7 +2450,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>375</v>
+        <v>125</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2453,7 +2459,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2463,7 +2469,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:04.761497+07:00</t>
+          <t>2026-10-22T09:43:49.284936+07:00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2476,7 +2482,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2485,7 +2491,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1125</v>
+        <v>625</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2494,7 +2500,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2504,7 +2510,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:18.887600+07:00</t>
+          <t>2026-10-22T09:44:07.989307+07:00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2517,7 +2523,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2526,7 +2532,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1750</v>
+        <v>1250</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2535,7 +2541,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2545,7 +2551,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:13.268757+07:00</t>
+          <t>2026-10-22T09:44:01.845590+07:00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2558,7 +2564,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2576,7 +2582,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2586,7 +2592,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:27.375750+07:00</t>
+          <t>2026-10-22T09:44:19.892963+07:00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2599,7 +2605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2608,7 +2614,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2617,7 +2623,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2627,7 +2633,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:33.209518+07:00</t>
+          <t>2026-10-22T09:44:26.098389+07:00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2640,7 +2646,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2649,7 +2655,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2658,7 +2664,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2668,7 +2674,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-21T09:42:59.944004+07:00</t>
+          <t>2026-10-22T09:43:43.688201+07:00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2681,7 +2687,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2690,7 +2696,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1125</v>
+        <v>625</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2699,7 +2705,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2709,7 +2715,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:24.155602+07:00</t>
+          <t>2026-10-22T09:44:15.083278+07:00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2722,7 +2728,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2731,7 +2737,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1125</v>
+        <v>625</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2740,7 +2746,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2750,7 +2756,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:01.864362+07:00</t>
+          <t>2026-10-22T09:43:46.064811+07:00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2761,44 +2767,50 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>สระบุรี</t>
         </is>
       </c>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21T09:43:22.503997+07:00</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="C57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:13.247022+07:00</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_418000.png</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>cannot_locate_bar</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2807,7 +2819,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>750</v>
+        <v>625</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2816,7 +2828,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2826,7 +2838,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:26.779898+07:00</t>
+          <t>2026-10-22T09:44:18.454593+07:00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2839,7 +2851,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2848,7 +2860,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>750</v>
+        <v>875</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2857,7 +2869,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2867,7 +2879,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:22.476108+07:00</t>
+          <t>2026-10-22T09:44:12.718024+07:00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2880,7 +2892,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2889,7 +2901,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2898,7 +2910,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2908,7 +2920,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:23.825668+07:00</t>
+          <t>2026-10-22T09:44:14.591587+07:00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2921,7 +2933,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2930,7 +2942,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2939,7 +2951,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2949,7 +2961,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:31.423781+07:00</t>
+          <t>2026-10-22T09:44:23.081378+07:00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2962,7 +2974,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2971,7 +2983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1625</v>
+        <v>1000</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2980,7 +2992,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2990,7 +3002,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:18.962019+07:00</t>
+          <t>2026-10-22T09:44:08.080297+07:00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3003,7 +3015,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3012,7 +3024,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3021,7 +3033,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3031,7 +3043,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:08.193258+07:00</t>
+          <t>2026-10-22T09:43:53.381817+07:00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3044,7 +3056,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3053,7 +3065,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3062,7 +3074,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3072,7 +3084,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:11.731628+07:00</t>
+          <t>2026-10-22T09:43:57.839405+07:00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3085,7 +3097,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3094,7 +3106,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3103,7 +3115,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3113,7 +3125,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:13.239790+07:00</t>
+          <t>2026-10-22T09:44:00.360544+07:00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3126,7 +3138,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3135,7 +3147,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3144,7 +3156,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3154,7 +3166,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:17.012490+07:00</t>
+          <t>2026-10-22T09:44:04.854700+07:00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3167,7 +3179,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3176,7 +3188,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>875</v>
+        <v>125</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3185,7 +3197,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3195,7 +3207,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:12.895504+07:00</t>
+          <t>2026-10-22T09:43:59.200939+07:00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3208,7 +3220,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3226,7 +3238,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3236,7 +3248,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:07.333278+07:00</t>
+          <t>2026-10-22T09:43:52.020636+07:00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3249,7 +3261,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3258,7 +3270,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>500</v>
+        <v>875</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3267,7 +3279,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3277,7 +3289,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:20.777992+07:00</t>
+          <t>2026-10-22T09:44:10.631018+07:00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3290,7 +3302,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3299,7 +3311,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3308,7 +3320,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3318,7 +3330,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:10.099027+07:00</t>
+          <t>2026-10-22T09:43:56.094227+07:00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3331,7 +3343,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3340,7 +3352,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3349,7 +3361,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3359,7 +3371,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:20.788981+07:00</t>
+          <t>2026-10-22T09:44:10.950039+07:00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3372,7 +3384,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3381,7 +3393,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1125</v>
+        <v>1250</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3390,7 +3402,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3400,7 +3412,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:02.441458+07:00</t>
+          <t>2026-10-22T09:43:46.722014+07:00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3413,7 +3425,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3431,7 +3443,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3441,7 +3453,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:02.249349+07:00</t>
+          <t>2026-10-22T09:43:46.514997+07:00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3454,7 +3466,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3463,7 +3475,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>875</v>
+        <v>375</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3472,7 +3484,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3482,7 +3494,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:29.831480+07:00</t>
+          <t>2026-10-22T09:44:21.276760+07:00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3495,7 +3507,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3504,7 +3516,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3513,7 +3525,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3523,7 +3535,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:10.086658+07:00</t>
+          <t>2026-10-22T09:43:56.062926+07:00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3536,7 +3548,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3545,7 +3557,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1000</v>
+        <v>625</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3554,7 +3566,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3564,7 +3576,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:11.750998+07:00</t>
+          <t>2026-10-22T09:43:58.922720+07:00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3577,7 +3589,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3586,7 +3598,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3595,7 +3607,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3605,7 +3617,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:06.344622+07:00</t>
+          <t>2026-10-22T09:43:50.853033+07:00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3618,7 +3630,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3627,7 +3639,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3636,7 +3648,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-20 00Z</t>
+          <t>2026-10-21 00Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3646,7 +3658,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-21T09:43:04.348109+07:00</t>
+          <t>2026-10-22T09:43:48.043917+07:00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3747,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I155"/>
+  <dimension ref="A1:I232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10110,8 +10122,3165 @@
       </c>
       <c r="I155" t="inlineStr"/>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>กระบี่</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>250</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:23.834381+07:00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_566202.png</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>875</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:43.686013+07:00</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_455301.png</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>375</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:16.222253+07:00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_450201.png</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>กาฬสินธุ์</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>2875</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:02.024196+07:00</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_388401.png</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>กำแพงเพชร</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>625</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:53.560960+07:00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_380201.png</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ขอนแก่น</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:56.361941+07:00</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_381201.png</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>จันทบุรี</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>500</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:19.451646+07:00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_480201.png</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ฉะเชิงเทรา</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>625</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:16.415797+07:00</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_423301.png</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ชลบุรี</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>625</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:16.649608+07:00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_459201.png</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ชัยนาท</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>750</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:10.922684+07:00</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_402301.png</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ชัยภูมิ</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:04.855944+07:00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_403201.png</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>125</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:21.719633+07:00</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ตรัง</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>375</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:26.064700+07:00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_567201.png</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>ตราด</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>375</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:19.481744+07:00</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_501201.png</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ตาก</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>625</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:51.186310+07:00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_376201.png</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>750</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:12.878835+07:00</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_417201.png</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>625</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:46.037025+07:00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>นครพนม</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:59.174478+07:00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_357201.png</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>นครราชสีมา</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:08.033356+07:00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_431201.png</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>นครศรีธรรมราช</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:23.555766+07:00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_552201.png</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>นครสวรรค์</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>375</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:09.805249+07:00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_400201.png</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:43.686843+07:00</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_411000.png</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>นราธิวาส</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>625</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:28.260154+07:00</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_583201.png</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>น่าน</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>125</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:48.803759+07:00</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_331201.png</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>บึงกาฬ</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>500</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:56.610240+07:00</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_363201.png</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>บุรีรัมย์</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:07.742743+07:00</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_436201.png</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>ปทุมธานี</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:43.687358+07:00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_419301.png</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>ประจวบคีรีขันธ์</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>250</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:21.339850+07:00</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_500201.png</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>ปราจีนบุรี</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>375</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:18.029847+07:00</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_430201.png</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:26.085033+07:00</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>พระนครศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:12.611685+07:00</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>พะเยา</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>750</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:48.589750+07:00</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_310201.png</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>พังงา</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:23.161155+07:00</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_561201.png</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>พัทลุง</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:26.037910+07:00</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_560301.png</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>พิจิตร</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>250</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:54.801885+07:00</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_386301.png</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>375</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:53.559340+07:00</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_378201.png</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>ภูเก็ต</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:20.241825+07:00</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_564201.png</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>มหาสารคาม</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:02.637226+07:00</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_387401.png</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>มุกดาหาร</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>2625</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:01.847840+07:00</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>ยะลา</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:27.972797+07:00</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_581301.png</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ยโสธร</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:04.863243+07:00</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_406201.png</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>ระนอง</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:22.031921+07:00</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_532201.png</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>ระยอง</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>750</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:17.160198+07:00</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>ราชบุรี</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>500</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:14.416804+07:00</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>2625</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:04.839375+07:00</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_405201.png</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>ลพบุรี</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:14.800697+07:00</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_426201.png</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>ลำปาง</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>250</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:50.574688+07:00</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_328201.png</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>ลำพูน</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>125</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:49.284936+07:00</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_329201.png</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>ศรีสะเกษ</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>625</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:07.989307+07:00</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_409301.png</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>สกลนคร</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:01.845590+07:00</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_356201.png</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>สงขลา</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>750</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:19.892963+07:00</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_568501.png</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>สตูล</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>375</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:26.098389+07:00</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_570201.png</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>สมุทรปราการ</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>375</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:43.688201+07:00</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_429301.png</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>สมุทรสงคราม</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>625</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:15.083278+07:00</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_438201.png</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>สมุทรสาคร</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>625</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:46.064811+07:00</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_474000.png</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>สระบุรี</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:13.247022+07:00</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_418000.png</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>สระแก้ว</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>625</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:18.454593+07:00</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_440401.png</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>สิงห์บุรี</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>875</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:12.718024+07:00</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_416000.png</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:14.591587+07:00</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_425201.png</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>สุราษฎร์ธานี</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:23.081378+07:00</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_551201.png</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>สุรินทร์</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:08.080297+07:00</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_432201.png</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>สุโขทัย</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>500</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:53.381817+07:00</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_373201.png</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>หนองคาย</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>250</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:57.839405+07:00</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_352201.png</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>หนองบัวลำภู</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>125</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:00.360544+07:00</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_360201.png</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>อำนาจเจริญ</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:04.854700+07:00</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>อุดรธานี</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>125</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:59.200939+07:00</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>อุตรดิตถ์</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>375</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:52.020636+07:00</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_351201.png</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>อุทัยธานี</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>875</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:10.631018+07:00</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_410201.png</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>อุบลราชธานี</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>500</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:56.094227+07:00</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_407501.png</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>อ่างทอง</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:10.950039+07:00</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_414000.png</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>เชียงราย</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:46.722014+07:00</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_303201.png</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>เชียงใหม่</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>625</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:46.514997+07:00</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_327501.png</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>เพชรบุรี</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>375</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:44:21.276760+07:00</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_465201.png</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>250</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:56.062926+07:00</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_379201.png</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>เลย</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>625</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:58.922720+07:00</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_353201.png</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>แพร่</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>375</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:50.853033+07:00</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_330201.png</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>แม่ฮ่องสอน</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>500</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>2026-10-21 00Z</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:43:48.043917+07:00</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_300201.png</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I155"/>
+  <autoFilter ref="A1:I232"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -10267,6 +13436,83 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId231"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ventilation.xlsx
+++ b/data/ventilation.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ล่าสุด'!$A$1:$I$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$309</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:23.834381+07:00</t>
+          <t>2026-10-23T09:44:20.352786+07:00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>875</v>
+        <v>1500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:43.686013+07:00</t>
+          <t>2026-10-23T09:43:40.348724+07:00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:16.222253+07:00</t>
+          <t>2026-10-23T09:44:12.745743+07:00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2875</v>
+        <v>500</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:02.024196+07:00</t>
+          <t>2026-10-23T09:43:59.143264+07:00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>625</v>
+        <v>125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:53.560960+07:00</t>
+          <t>2026-10-23T09:43:51.616481+07:00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1250</v>
+        <v>625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:56.361941+07:00</t>
+          <t>2026-10-23T09:43:53.966997+07:00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:19.451646+07:00</t>
+          <t>2026-10-23T09:44:14.782620+07:00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:16.415797+07:00</t>
+          <t>2026-10-23T09:44:12.779702+07:00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>625</v>
+        <v>375</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:16.649608+07:00</t>
+          <t>2026-10-23T09:44:12.838874+07:00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>750</v>
+        <v>125</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:10.922684+07:00</t>
+          <t>2026-10-23T09:44:05.680630+07:00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1625</v>
+        <v>375</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:04.855944+07:00</t>
+          <t>2026-10-23T09:44:01.582123+07:00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>1125</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:21.719633+07:00</t>
+          <t>2026-10-23T09:44:17.984402+07:00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:26.064700+07:00</t>
+          <t>2026-10-23T09:44:21.302745+07:00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>375</v>
+        <v>875</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:19.481744+07:00</t>
+          <t>2026-10-23T09:44:16.132112+07:00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>625</v>
+        <v>250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:51.186310+07:00</t>
+          <t>2026-10-23T09:43:49.362527+07:00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>750</v>
+        <v>125</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:12.878835+07:00</t>
+          <t>2026-10-23T09:44:07.535049+07:00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:46.037025+07:00</t>
+          <t>2026-10-23T09:43:43.928534+07:00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1000</v>
+        <v>1625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:59.174478+07:00</t>
+          <t>2026-10-23T09:43:56.410113+07:00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:08.033356+07:00</t>
+          <t>2026-10-23T09:44:03.486975+07:00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1250</v>
+        <v>750</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:23.555766+07:00</t>
+          <t>2026-10-23T09:44:19.637637+07:00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:09.805249+07:00</t>
+          <t>2026-10-23T09:44:05.418216+07:00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:43.686843+07:00</t>
+          <t>2026-10-23T09:43:40.349667+07:00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:28.260154+07:00</t>
+          <t>2026-10-23T09:44:22.960336+07:00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:48.803759+07:00</t>
+          <t>2026-10-23T09:43:46.014822+07:00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:56.610240+07:00</t>
+          <t>2026-10-23T09:43:54.133230+07:00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1539,7 +1539,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1625</v>
+        <v>500</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:07.742743+07:00</t>
+          <t>2026-10-23T09:44:03.004762+07:00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:43.687358+07:00</t>
+          <t>2026-10-23T09:43:40.350197+07:00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:21.339850+07:00</t>
+          <t>2026-10-23T09:44:17.768698+07:00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>375</v>
+        <v>875</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:18.029847+07:00</t>
+          <t>2026-10-23T09:44:14.492883+07:00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1125</v>
+        <v>1250</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:26.085033+07:00</t>
+          <t>2026-10-23T09:44:21.303084+07:00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1750</v>
+        <v>750</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:12.611685+07:00</t>
+          <t>2026-10-23T09:44:07.511583+07:00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:48.589750+07:00</t>
+          <t>2026-10-23T09:43:45.993139+07:00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1835,16 +1835,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1125</v>
+        <v>2125</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:23.161155+07:00</t>
+          <t>2026-10-23T09:44:19.441900+07:00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:26.037910+07:00</t>
+          <t>2026-10-23T09:44:20.373295+07:00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:54.801885+07:00</t>
+          <t>2026-10-23T09:43:51.675940+07:00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:53.559340+07:00</t>
+          <t>2026-10-23T09:43:51.322424+07:00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1999,16 +1999,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1000</v>
+        <v>3125</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:20.241825+07:00</t>
+          <t>2026-10-23T09:44:16.868632+07:00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2040,16 +2040,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2125</v>
+        <v>750</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:02.637226+07:00</t>
+          <t>2026-10-23T09:44:00.567256+07:00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2072,7 +2072,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2081,16 +2081,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2625</v>
+        <v>500</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:01.847840+07:00</t>
+          <t>2026-10-23T09:43:59.142606+07:00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1000</v>
+        <v>625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:27.972797+07:00</t>
+          <t>2026-10-23T09:44:22.496408+07:00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1750</v>
+        <v>250</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:04.863243+07:00</t>
+          <t>2026-10-23T09:44:02.940049+07:00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1250</v>
+        <v>1625</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:22.031921+07:00</t>
+          <t>2026-10-23T09:44:18.700195+07:00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:17.160198+07:00</t>
+          <t>2026-10-23T09:44:14.467773+07:00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:14.416804+07:00</t>
+          <t>2026-10-23T09:44:10.038830+07:00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2318,7 +2318,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2327,16 +2327,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2625</v>
+        <v>375</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:04.839375+07:00</t>
+          <t>2026-10-23T09:44:01.362332+07:00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1500</v>
+        <v>375</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:14.800697+07:00</t>
+          <t>2026-10-23T09:44:10.275537+07:00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2400,7 +2400,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:50.574688+07:00</t>
+          <t>2026-10-23T09:43:48.959690+07:00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:49.284936+07:00</t>
+          <t>2026-10-23T09:43:46.174093+07:00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>625</v>
+        <v>250</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:07.989307+07:00</t>
+          <t>2026-10-23T09:44:03.486562+07:00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:01.845590+07:00</t>
+          <t>2026-10-23T09:43:58.941599+07:00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2564,7 +2564,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>750</v>
+        <v>125</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:19.892963+07:00</t>
+          <t>2026-10-23T09:44:16.136514+07:00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>375</v>
+        <v>875</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:26.098389+07:00</t>
+          <t>2026-10-23T09:44:22.212476+07:00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>375</v>
+        <v>875</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:43.688201+07:00</t>
+          <t>2026-10-23T09:43:40.350797+07:00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>625</v>
+        <v>750</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:15.083278+07:00</t>
+          <t>2026-10-23T09:44:12.518104+07:00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>625</v>
+        <v>1000</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:46.064811+07:00</t>
+          <t>2026-10-23T09:43:43.929309+07:00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1000</v>
+        <v>875</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:13.247022+07:00</t>
+          <t>2026-10-23T09:44:10.023820+07:00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:18.454593+07:00</t>
+          <t>2026-10-23T09:44:14.751037+07:00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>875</v>
+        <v>375</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:12.718024+07:00</t>
+          <t>2026-10-23T09:44:07.512742+07:00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:14.591587+07:00</t>
+          <t>2026-10-23T09:44:10.269821+07:00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:23.081378+07:00</t>
+          <t>2026-10-23T09:44:18.724340+07:00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:08.080297+07:00</t>
+          <t>2026-10-23T09:44:05.416044+07:00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3015,7 +3015,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:53.381817+07:00</t>
+          <t>2026-10-23T09:43:51.056020+07:00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>250</v>
+        <v>625</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:57.839405+07:00</t>
+          <t>2026-10-23T09:43:56.183884+07:00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>125</v>
+        <v>625</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:00.360544+07:00</t>
+          <t>2026-10-23T09:43:58.922129+07:00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3147,16 +3147,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2500</v>
+        <v>375</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:04.854700+07:00</t>
+          <t>2026-10-23T09:44:01.409781+07:00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>125</v>
+        <v>750</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:59.200939+07:00</t>
+          <t>2026-10-23T09:43:56.414116+07:00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:52.020636+07:00</t>
+          <t>2026-10-23T09:43:49.440542+07:00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>875</v>
+        <v>375</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:10.631018+07:00</t>
+          <t>2026-10-23T09:44:05.645931+07:00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>500</v>
+        <v>625</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:56.094227+07:00</t>
+          <t>2026-10-23T09:43:53.795264+07:00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3343,7 +3343,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1500</v>
+        <v>625</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:10.950039+07:00</t>
+          <t>2026-10-23T09:44:07.494737+07:00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:46.722014+07:00</t>
+          <t>2026-10-23T09:43:43.931475+07:00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3425,7 +3425,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>625</v>
+        <v>375</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:46.514997+07:00</t>
+          <t>2026-10-23T09:43:43.930765+07:00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-22T09:44:21.276760+07:00</t>
+          <t>2026-10-23T09:44:17.073001+07:00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3507,7 +3507,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:56.062926+07:00</t>
+          <t>2026-10-23T09:43:53.674760+07:00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>625</v>
+        <v>375</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:58.922720+07:00</t>
+          <t>2026-10-23T09:43:56.184339+07:00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3589,7 +3589,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>375</v>
+        <v>625</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:50.853033+07:00</t>
+          <t>2026-10-23T09:43:49.198587+07:00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-21 00Z</t>
+          <t>2026-10-22 00Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-22T09:43:48.043917+07:00</t>
+          <t>2026-10-23T09:43:45.966751+07:00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I232"/>
+  <dimension ref="A1:I309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13279,8 +13279,3165 @@
       </c>
       <c r="I232" t="inlineStr"/>
     </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>กระบี่</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:20.352786+07:00</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_566202.png</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:40.348724+07:00</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_455301.png</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>375</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:12.745743+07:00</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_450201.png</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>กาฬสินธุ์</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>500</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:59.143264+07:00</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_388401.png</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>กำแพงเพชร</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>125</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:51.616481+07:00</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_380201.png</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>ขอนแก่น</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>625</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:53.966997+07:00</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_381201.png</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>จันทบุรี</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>250</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:14.782620+07:00</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_480201.png</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>ฉะเชิงเทรา</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>625</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:12.779702+07:00</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_423301.png</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>ชลบุรี</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>375</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:12.838874+07:00</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_459201.png</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>ชัยนาท</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>125</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:05.680630+07:00</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_402301.png</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>ชัยภูมิ</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>375</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:01.582123+07:00</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_403201.png</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:17.984402+07:00</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>ตรัง</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>500</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:21.302745+07:00</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_567201.png</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>ตราด</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>875</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:16.132112+07:00</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_501201.png</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ตาก</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>250</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:49.362527+07:00</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_376201.png</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>125</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:07.535049+07:00</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_417201.png</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>500</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:43.928534+07:00</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>นครพนม</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:56.410113+07:00</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_357201.png</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>นครราชสีมา</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>500</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:03.486975+07:00</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_431201.png</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>นครศรีธรรมราช</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>750</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:19.637637+07:00</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_552201.png</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>นครสวรรค์</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>375</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:05.418216+07:00</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_400201.png</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:40.349667+07:00</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_411000.png</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>นราธิวาส</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>625</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:22.960336+07:00</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_583201.png</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>น่าน</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>250</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:46.014822+07:00</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_331201.png</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>บึงกาฬ</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>750</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:54.133230+07:00</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_363201.png</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>บุรีรัมย์</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>500</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:03.004762+07:00</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_436201.png</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>ปทุมธานี</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:40.350197+07:00</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_419301.png</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>ประจวบคีรีขันธ์</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>375</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:17.768698+07:00</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_500201.png</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>ปราจีนบุรี</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>875</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:14.492883+07:00</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_430201.png</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:21.303084+07:00</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>พระนครศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>750</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:07.511583+07:00</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>พะเยา</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>500</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:45.993139+07:00</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_310201.png</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>พังงา</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:19.441900+07:00</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_561201.png</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>พัทลุง</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>250</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:20.373295+07:00</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_560301.png</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>พิจิตร</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>500</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:51.675940+07:00</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_386301.png</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>375</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:51.322424+07:00</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_378201.png</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>ภูเก็ต</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>3125</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:16.868632+07:00</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_564201.png</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>มหาสารคาม</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>750</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:00.567256+07:00</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_387401.png</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>มุกดาหาร</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>500</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:59.142606+07:00</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>ยะลา</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>625</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:22.496408+07:00</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_581301.png</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>ยโสธร</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>250</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:02.940049+07:00</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_406201.png</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ระนอง</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:18.700195+07:00</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_532201.png</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>ระยอง</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>375</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:14.467773+07:00</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>ราชบุรี</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>750</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:10.038830+07:00</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>375</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:01.362332+07:00</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_405201.png</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>ลพบุรี</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>375</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:10.275537+07:00</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_426201.png</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>ลำปาง</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>375</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:48.959690+07:00</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_328201.png</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>ลำพูน</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>250</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:46.174093+07:00</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_329201.png</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>ศรีสะเกษ</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>250</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:03.486562+07:00</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_409301.png</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>สกลนคร</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:58.941599+07:00</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_356201.png</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>สงขลา</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>125</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:16.136514+07:00</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_568501.png</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>สตูล</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>875</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:22.212476+07:00</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_570201.png</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>สมุทรปราการ</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>875</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:40.350797+07:00</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_429301.png</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>สมุทรสงคราม</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>750</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:12.518104+07:00</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_438201.png</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>สมุทรสาคร</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:43.929309+07:00</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_474000.png</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>สระบุรี</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>875</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:10.023820+07:00</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_418000.png</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>สระแก้ว</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>500</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:14.751037+07:00</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_440401.png</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>สิงห์บุรี</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>375</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:07.512742+07:00</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_416000.png</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>375</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:10.269821+07:00</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_425201.png</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>สุราษฎร์ธานี</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>375</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:18.724340+07:00</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_551201.png</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>สุรินทร์</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>375</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:05.416044+07:00</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_432201.png</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>สุโขทัย</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>250</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:51.056020+07:00</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_373201.png</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>หนองคาย</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>625</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:56.183884+07:00</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_352201.png</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>หนองบัวลำภู</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>625</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:58.922129+07:00</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_360201.png</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>อำนาจเจริญ</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>375</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:01.409781+07:00</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>อุดรธานี</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>750</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:56.414116+07:00</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>อุตรดิตถ์</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>375</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:49.440542+07:00</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_351201.png</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>อุทัยธานี</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>375</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:05.645931+07:00</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_410201.png</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>อุบลราชธานี</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>625</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:53.795264+07:00</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_407501.png</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>อ่างทอง</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>625</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:07.494737+07:00</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_414000.png</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>เชียงราย</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:43.931475+07:00</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_303201.png</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>เชียงใหม่</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>375</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:43.930765+07:00</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_327501.png</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>เพชรบุรี</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>500</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:44:17.073001+07:00</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_465201.png</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>375</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:53.674760+07:00</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_379201.png</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>เลย</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>375</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:56.184339+07:00</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_353201.png</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>แพร่</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>625</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:49.198587+07:00</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_330201.png</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>แม่ฮ่องสอน</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>2026-10-22 00Z</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:43:45.966751+07:00</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_300201.png</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I232"/>
+  <autoFilter ref="A1:I309"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -13513,6 +16670,83 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId229"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId308"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ventilation.xlsx
+++ b/data/ventilation.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ล่าสุด'!$A$1:$I$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$309</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$386</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -523,16 +523,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1250</v>
+        <v>2625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:20.352786+07:00</t>
+          <t>2026-10-24T09:42:58.162549+07:00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1500</v>
+        <v>1375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:40.348724+07:00</t>
+          <t>2026-10-24T09:42:29.614913+07:00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:12.745743+07:00</t>
+          <t>2026-10-24T09:42:51.708848+07:00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:59.143264+07:00</t>
+          <t>2026-10-24T09:42:42.657662+07:00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>125</v>
+        <v>750</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:51.616481+07:00</t>
+          <t>2026-10-24T09:42:37.601735+07:00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>625</v>
+        <v>1500</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:53.966997+07:00</t>
+          <t>2026-10-24T09:42:39.273758+07:00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>250</v>
+        <v>1125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:14.782620+07:00</t>
+          <t>2026-10-24T09:42:53.709975+07:00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>625</v>
+        <v>750</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:12.779702+07:00</t>
+          <t>2026-10-24T09:42:52.003011+07:00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>375</v>
+        <v>625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:12.838874+07:00</t>
+          <t>2026-10-24T09:42:52.158667+07:00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:05.680630+07:00</t>
+          <t>2026-10-24T09:42:47.315420+07:00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>375</v>
+        <v>875</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:01.582123+07:00</t>
+          <t>2026-10-24T09:42:44.137322+07:00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -963,50 +963,44 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>ชุมพร</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>1125</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-10-22 00Z</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-10-23T09:44:17.984402+07:00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:56.208800+07:00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1015,7 +1009,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1024,7 +1018,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1034,7 +1028,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:21.302745+07:00</t>
+          <t>2026-10-24T09:42:58.632856+07:00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1047,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1056,7 +1050,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>875</v>
+        <v>750</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1065,7 +1059,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1075,7 +1069,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:16.132112+07:00</t>
+          <t>2026-10-24T09:42:53.948318+07:00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1088,7 +1082,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1097,7 +1091,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1106,7 +1100,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1116,7 +1110,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:49.362527+07:00</t>
+          <t>2026-10-24T09:42:35.595624+07:00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1129,7 +1123,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1138,7 +1132,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>125</v>
+        <v>500</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1147,7 +1141,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1157,7 +1151,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:07.535049+07:00</t>
+          <t>2026-10-24T09:42:48.861215+07:00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1170,7 +1164,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1179,7 +1173,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1188,7 +1182,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1198,7 +1192,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:43.928534+07:00</t>
+          <t>2026-10-24T09:42:31.724014+07:00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1211,7 +1205,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1220,7 +1214,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1625</v>
+        <v>1250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1229,7 +1223,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1239,7 +1233,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:56.410113+07:00</t>
+          <t>2026-10-24T09:42:40.764247+07:00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1252,7 +1246,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1261,7 +1255,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1270,7 +1264,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1280,7 +1274,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:03.486975+07:00</t>
+          <t>2026-10-24T09:42:45.709865+07:00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1293,7 +1287,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1302,7 +1296,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1311,7 +1305,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1321,7 +1315,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:19.637637+07:00</t>
+          <t>2026-10-24T09:42:57.568763+07:00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1334,7 +1328,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1343,7 +1337,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1352,7 +1346,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1362,7 +1356,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:05.418216+07:00</t>
+          <t>2026-10-24T09:42:47.085004+07:00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1375,7 +1369,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1384,7 +1378,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1125</v>
+        <v>750</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1393,7 +1387,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1403,7 +1397,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:40.349667+07:00</t>
+          <t>2026-10-24T09:42:29.615949+07:00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1416,7 +1410,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1425,7 +1419,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>625</v>
+        <v>875</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1434,7 +1428,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1444,7 +1438,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:22.960336+07:00</t>
+          <t>2026-10-24T09:43:00.128013+07:00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1457,7 +1451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1466,7 +1460,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1475,7 +1469,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1485,7 +1479,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:46.014822+07:00</t>
+          <t>2026-10-24T09:42:33.745456+07:00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1498,7 +1492,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1507,7 +1501,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>750</v>
+        <v>625</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1516,7 +1510,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1526,7 +1520,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:54.133230+07:00</t>
+          <t>2026-10-24T09:42:39.276000+07:00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1539,7 +1533,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1548,7 +1542,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>500</v>
+        <v>875</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1557,7 +1551,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1567,7 +1561,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:03.004762+07:00</t>
+          <t>2026-10-24T09:42:45.485320+07:00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1580,7 +1574,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1589,7 +1583,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1125</v>
+        <v>750</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1598,7 +1592,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1608,7 +1602,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:40.350197+07:00</t>
+          <t>2026-10-24T09:42:29.616482+07:00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1621,7 +1615,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1639,7 +1633,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1649,7 +1643,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:17.768698+07:00</t>
+          <t>2026-10-24T09:42:55.635512+07:00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1662,7 +1656,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1671,7 +1665,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>875</v>
+        <v>625</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1680,7 +1674,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1690,7 +1684,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:14.492883+07:00</t>
+          <t>2026-10-24T09:42:53.212027+07:00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1701,50 +1695,44 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>ปัตตานี</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>1250</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026-10-22 00Z</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-10-23T09:44:21.303084+07:00</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:59.031133+07:00</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1762,7 +1750,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1772,7 +1760,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:07.511583+07:00</t>
+          <t>2026-10-24T09:42:48.683432+07:00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1785,7 +1773,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1794,7 +1782,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1803,7 +1791,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1813,7 +1801,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:45.993139+07:00</t>
+          <t>2026-10-24T09:42:33.720292+07:00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1826,7 +1814,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1835,7 +1823,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2125</v>
+        <v>2500</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1844,7 +1832,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1854,7 +1842,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:19.441900+07:00</t>
+          <t>2026-10-24T09:42:57.140178+07:00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1867,7 +1855,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1876,7 +1864,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>250</v>
+        <v>625</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1885,7 +1873,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1895,7 +1883,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:20.373295+07:00</t>
+          <t>2026-10-24T09:42:58.268136+07:00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1908,7 +1896,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1917,7 +1905,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>500</v>
+        <v>875</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1926,7 +1914,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1936,7 +1924,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:51.675940+07:00</t>
+          <t>2026-10-24T09:42:37.623449+07:00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1949,7 +1937,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1958,7 +1946,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>375</v>
+        <v>625</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1967,7 +1955,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1977,7 +1965,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:51.322424+07:00</t>
+          <t>2026-10-24T09:42:37.313656+07:00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1990,7 +1978,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1999,16 +1987,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3125</v>
+        <v>5750</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2018,7 +2006,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:16.868632+07:00</t>
+          <t>2026-10-24T09:42:54.974285+07:00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2031,7 +2019,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2040,7 +2028,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>750</v>
+        <v>1250</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2049,7 +2037,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2059,7 +2047,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:00.567256+07:00</t>
+          <t>2026-10-24T09:42:43.277508+07:00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2072,7 +2060,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2081,7 +2069,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>500</v>
+        <v>1250</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2090,7 +2078,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2100,7 +2088,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:59.142606+07:00</t>
+          <t>2026-10-24T09:42:42.439708+07:00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2113,7 +2101,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2122,16 +2110,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>625</v>
+        <v>2000</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2141,7 +2129,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:22.496408+07:00</t>
+          <t>2026-10-24T09:42:59.750565+07:00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2154,7 +2142,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2163,7 +2151,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>250</v>
+        <v>875</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2172,7 +2160,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2182,7 +2170,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:02.940049+07:00</t>
+          <t>2026-10-24T09:42:44.739279+07:00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2195,7 +2183,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2204,16 +2192,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1625</v>
+        <v>2250</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2223,7 +2211,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:18.700195+07:00</t>
+          <t>2026-10-24T09:42:56.669288+07:00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2236,7 +2224,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2245,7 +2233,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>375</v>
+        <v>1250</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2254,7 +2242,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2264,7 +2252,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:14.467773+07:00</t>
+          <t>2026-10-24T09:42:52.426433+07:00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2277,7 +2265,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2286,7 +2274,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2295,7 +2283,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2305,7 +2293,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:10.038830+07:00</t>
+          <t>2026-10-24T09:42:50.212111+07:00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2318,7 +2306,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2327,7 +2315,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>375</v>
+        <v>1125</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2336,7 +2324,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2346,7 +2334,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:01.362332+07:00</t>
+          <t>2026-10-24T09:42:43.599996+07:00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2359,7 +2347,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2368,7 +2356,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>375</v>
+        <v>625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2377,7 +2365,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2387,7 +2375,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:10.275537+07:00</t>
+          <t>2026-10-24T09:42:50.651284+07:00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2400,7 +2388,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2409,7 +2397,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2418,7 +2406,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2428,7 +2416,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:48.959690+07:00</t>
+          <t>2026-10-24T09:42:35.401706+07:00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2441,7 +2429,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2459,7 +2447,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2469,7 +2457,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:46.174093+07:00</t>
+          <t>2026-10-24T09:42:33.770904+07:00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2482,7 +2470,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2491,7 +2479,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2500,7 +2488,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2510,7 +2498,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:03.486562+07:00</t>
+          <t>2026-10-24T09:42:45.602362+07:00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2523,7 +2511,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2532,7 +2520,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1000</v>
+        <v>1125</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2541,7 +2529,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2551,7 +2539,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:58.941599+07:00</t>
+          <t>2026-10-24T09:42:42.130083+07:00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2564,7 +2552,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2573,7 +2561,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>125</v>
+        <v>375</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2582,7 +2570,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2592,7 +2580,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:16.136514+07:00</t>
+          <t>2026-10-24T09:42:54.744941+07:00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2605,7 +2593,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2614,7 +2602,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>875</v>
+        <v>1750</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2623,7 +2611,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2633,7 +2621,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:22.212476+07:00</t>
+          <t>2026-10-24T09:42:59.658052+07:00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2646,7 +2634,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2655,7 +2643,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>875</v>
+        <v>1375</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2664,7 +2652,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2674,7 +2662,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:40.350797+07:00</t>
+          <t>2026-10-24T09:42:29.617261+07:00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2687,7 +2675,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2696,7 +2684,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2705,7 +2693,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2715,7 +2703,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:12.518104+07:00</t>
+          <t>2026-10-24T09:42:50.734356+07:00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2728,7 +2716,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2746,7 +2734,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2756,7 +2744,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:43.929309+07:00</t>
+          <t>2026-10-24T09:42:31.764748+07:00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2769,7 +2757,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2778,7 +2766,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>875</v>
+        <v>625</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2787,7 +2775,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2797,7 +2785,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:10.023820+07:00</t>
+          <t>2026-10-24T09:42:49.230257+07:00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2810,7 +2798,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2819,7 +2807,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2828,7 +2816,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2838,7 +2826,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:14.751037+07:00</t>
+          <t>2026-10-24T09:42:53.481618+07:00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2851,7 +2839,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2860,7 +2848,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2869,7 +2857,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2879,7 +2867,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:07.512742+07:00</t>
+          <t>2026-10-24T09:42:48.723445+07:00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2892,7 +2880,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2901,7 +2889,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>375</v>
+        <v>875</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2910,7 +2898,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2920,7 +2908,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:10.269821+07:00</t>
+          <t>2026-10-24T09:42:50.257426+07:00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2933,7 +2921,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2951,7 +2939,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2961,7 +2949,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:18.724340+07:00</t>
+          <t>2026-10-24T09:42:56.746981+07:00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2974,7 +2962,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2983,7 +2971,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>375</v>
+        <v>875</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2992,7 +2980,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3002,7 +2990,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:05.416044+07:00</t>
+          <t>2026-10-24T09:42:46.217912+07:00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3015,7 +3003,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3024,7 +3012,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>250</v>
+        <v>625</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3033,7 +3021,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3043,7 +3031,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:51.056020+07:00</t>
+          <t>2026-10-24T09:42:37.147371+07:00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3056,7 +3044,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3065,7 +3053,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>625</v>
+        <v>750</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3074,7 +3062,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3084,7 +3072,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:56.183884+07:00</t>
+          <t>2026-10-24T09:42:40.113393+07:00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3097,7 +3085,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3106,7 +3094,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>625</v>
+        <v>750</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3115,7 +3103,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3125,7 +3113,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:58.922129+07:00</t>
+          <t>2026-10-24T09:42:41.570996+07:00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3138,7 +3126,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3147,7 +3135,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3156,7 +3144,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3166,7 +3154,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:01.409781+07:00</t>
+          <t>2026-10-24T09:42:44.108749+07:00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3179,7 +3167,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3188,7 +3176,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>750</v>
+        <v>875</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3197,7 +3185,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3207,7 +3195,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:56.414116+07:00</t>
+          <t>2026-10-24T09:42:40.990122+07:00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3220,7 +3208,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3229,7 +3217,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>375</v>
+        <v>875</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3238,7 +3226,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3248,7 +3236,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:49.440542+07:00</t>
+          <t>2026-10-24T09:42:35.640508+07:00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3261,7 +3249,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3270,7 +3258,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>375</v>
+        <v>875</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3279,7 +3267,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3289,7 +3277,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:05.645931+07:00</t>
+          <t>2026-10-24T09:42:47.106290+07:00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3302,7 +3290,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3311,7 +3299,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>625</v>
+        <v>875</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3320,7 +3308,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3330,7 +3318,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:53.795264+07:00</t>
+          <t>2026-10-24T09:42:39.131015+07:00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3343,7 +3331,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3352,7 +3340,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3361,7 +3349,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3371,7 +3359,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:07.494737+07:00</t>
+          <t>2026-10-24T09:42:47.689244+07:00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3384,7 +3372,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3393,7 +3381,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1000</v>
+        <v>1125</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3402,7 +3390,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3412,7 +3400,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:43.931475+07:00</t>
+          <t>2026-10-24T09:42:32.026041+07:00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3425,7 +3413,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3434,7 +3422,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3443,7 +3431,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3453,7 +3441,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:43.930765+07:00</t>
+          <t>2026-10-24T09:42:31.913246+07:00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3466,7 +3454,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3484,7 +3472,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3494,7 +3482,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-23T09:44:17.073001+07:00</t>
+          <t>2026-10-24T09:42:55.214925+07:00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3507,7 +3495,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3516,7 +3504,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3525,7 +3513,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3535,7 +3523,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:53.674760+07:00</t>
+          <t>2026-10-24T09:42:38.630459+07:00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3548,7 +3536,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3566,7 +3554,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3576,7 +3564,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:56.184339+07:00</t>
+          <t>2026-10-24T09:42:40.657205+07:00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3589,7 +3577,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3607,7 +3595,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3617,7 +3605,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:49.198587+07:00</t>
+          <t>2026-10-24T09:42:35.431353+07:00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3630,7 +3618,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3639,7 +3627,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1000</v>
+        <v>875</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3648,7 +3636,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-22 00Z</t>
+          <t>2026-10-23 00Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3658,7 +3646,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-23T09:43:45.966751+07:00</t>
+          <t>2026-10-24T09:42:33.550674+07:00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3759,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I309"/>
+  <dimension ref="A1:I386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16436,8 +16424,3153 @@
       </c>
       <c r="I309" t="inlineStr"/>
     </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>กระบี่</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>2625</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:58.162549+07:00</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_566202.png</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:29.614913+07:00</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_455301.png</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>500</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:51.708848+07:00</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_450201.png</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>กาฬสินธุ์</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:42.657662+07:00</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_388401.png</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>กำแพงเพชร</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>750</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:37.601735+07:00</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_380201.png</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>ขอนแก่น</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:39.273758+07:00</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_381201.png</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>จันทบุรี</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:53.709975+07:00</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_480201.png</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>ฉะเชิงเทรา</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>750</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:52.003011+07:00</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_423301.png</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>ชลบุรี</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>625</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:52.158667+07:00</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_459201.png</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>ชัยนาท</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>625</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:47.315420+07:00</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_402301.png</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>ชัยภูมิ</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>875</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:44.137322+07:00</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_403201.png</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="n"/>
+      <c r="D321" s="3" t="inlineStr"/>
+      <c r="E321" s="3" t="inlineStr"/>
+      <c r="F321" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G321" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:56.208800+07:00</t>
+        </is>
+      </c>
+      <c r="H321" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
+        </is>
+      </c>
+      <c r="I321" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>ตรัง</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:58.632856+07:00</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_567201.png</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>ตราด</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>750</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:53.948318+07:00</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_501201.png</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>ตาก</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>750</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:35.595624+07:00</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_376201.png</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>500</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:48.861215+07:00</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_417201.png</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>250</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:31.724014+07:00</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>นครพนม</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:40.764247+07:00</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_357201.png</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>นครราชสีมา</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>375</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:45.709865+07:00</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_431201.png</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>นครศรีธรรมราช</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>250</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:57.568763+07:00</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_552201.png</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>นครสวรรค์</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>500</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:47.085004+07:00</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_400201.png</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>750</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:29.615949+07:00</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_411000.png</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>นราธิวาส</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>875</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:43:00.128013+07:00</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_583201.png</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>น่าน</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>375</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:33.745456+07:00</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_331201.png</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>บึงกาฬ</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>625</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:39.276000+07:00</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_363201.png</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>บุรีรัมย์</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>875</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:45.485320+07:00</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_436201.png</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>ปทุมธานี</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>750</v>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:29.616482+07:00</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_419301.png</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>ประจวบคีรีขันธ์</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>375</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:55.635512+07:00</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_500201.png</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>ปราจีนบุรี</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>625</v>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:53.212027+07:00</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_430201.png</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="n"/>
+      <c r="D339" s="3" t="inlineStr"/>
+      <c r="E339" s="3" t="inlineStr"/>
+      <c r="F339" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G339" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:59.031133+07:00</t>
+        </is>
+      </c>
+      <c r="H339" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
+        </is>
+      </c>
+      <c r="I339" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>พระนครศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>750</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:48.683432+07:00</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>พะเยา</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:33.720292+07:00</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_310201.png</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>พังงา</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:57.140178+07:00</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_561201.png</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>พัทลุง</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>625</v>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:58.268136+07:00</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_560301.png</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>พิจิตร</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>875</v>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:37.623449+07:00</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_386301.png</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>625</v>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:37.313656+07:00</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_378201.png</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>ภูเก็ต</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>5750</v>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:54.974285+07:00</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_564201.png</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>มหาสารคาม</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:43.277508+07:00</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_387401.png</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>มุกดาหาร</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:42.439708+07:00</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>ยะลา</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:59.750565+07:00</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_581301.png</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>ยโสธร</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>875</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:44.739279+07:00</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_406201.png</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>ระนอง</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:56.669288+07:00</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_532201.png</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>ระยอง</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:52.426433+07:00</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>ราชบุรี</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>250</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:50.212111+07:00</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:43.599996+07:00</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_405201.png</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>ลพบุรี</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>625</v>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:50.651284+07:00</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_426201.png</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>ลำปาง</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>500</v>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:35.401706+07:00</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_328201.png</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>ลำพูน</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>250</v>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:33.770904+07:00</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_329201.png</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>ศรีสะเกษ</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:45.602362+07:00</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_409301.png</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>สกลนคร</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:42.130083+07:00</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_356201.png</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>สงขลา</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>375</v>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:54.744941+07:00</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_568501.png</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>สตูล</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:59.658052+07:00</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_570201.png</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>สมุทรปราการ</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:29.617261+07:00</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_429301.png</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>สมุทรสงคราม</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>375</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:50.734356+07:00</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_438201.png</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>สมุทรสาคร</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:31.764748+07:00</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_474000.png</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>สระบุรี</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>625</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:49.230257+07:00</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_418000.png</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>สระแก้ว</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>375</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:53.481618+07:00</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_440401.png</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>สิงห์บุรี</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>750</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:48.723445+07:00</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_416000.png</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>875</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:50.257426+07:00</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_425201.png</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>สุราษฎร์ธานี</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>375</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:56.746981+07:00</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_551201.png</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>สุรินทร์</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>875</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:46.217912+07:00</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_432201.png</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>สุโขทัย</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>625</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:37.147371+07:00</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_373201.png</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>หนองคาย</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>750</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:40.113393+07:00</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_352201.png</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>หนองบัวลำภู</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>750</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:41.570996+07:00</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_360201.png</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>อำนาจเจริญ</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>750</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:44.108749+07:00</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>อุดรธานี</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>875</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:40.990122+07:00</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>อุตรดิตถ์</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>875</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:35.640508+07:00</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_351201.png</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>อุทัยธานี</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>875</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:47.106290+07:00</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_410201.png</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>อุบลราชธานี</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>875</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:39.131015+07:00</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_407501.png</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>อ่างทอง</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>500</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:47.689244+07:00</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_414000.png</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>เชียงราย</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:32.026041+07:00</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_303201.png</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>เชียงใหม่</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>500</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:31.913246+07:00</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_327501.png</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>เพชรบุรี</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>500</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:55.214925+07:00</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_465201.png</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>500</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:38.630459+07:00</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_379201.png</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>เลย</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>375</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:40.657205+07:00</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_353201.png</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>แพร่</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>625</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:35.431353+07:00</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_330201.png</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>แม่ฮ่องสอน</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>875</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>2026-10-23 00Z</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:33.550674+07:00</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_300201.png</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I309"/>
+  <autoFilter ref="A1:I386"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -16747,6 +19880,83 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId306"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId307"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H386" r:id="rId385"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16758,7 +19968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16889,11 +20099,83 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:56.208800+07:00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:42:59.031133+07:00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I3"/>
+  <autoFilter ref="A1:I5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ventilation.xlsx
+++ b/data/ventilation.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ล่าสุด'!$A$1:$I$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$386</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$463</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -523,16 +523,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2625</v>
+        <v>1000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:58.162549+07:00</t>
+          <t>2026-10-25T09:43:28.387675+07:00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,16 +564,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1375</v>
+        <v>2000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:29.614913+07:00</t>
+          <t>2026-10-25T09:42:59.641918+07:00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>500</v>
+        <v>875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:51.708848+07:00</t>
+          <t>2026-10-25T09:43:22.398707+07:00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1000</v>
+        <v>1375</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:42.657662+07:00</t>
+          <t>2026-10-25T09:43:13.958846+07:00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:37.601735+07:00</t>
+          <t>2026-10-25T09:43:08.159898+07:00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:39.273758+07:00</t>
+          <t>2026-10-25T09:43:10.022774+07:00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1125</v>
+        <v>1000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:53.709975+07:00</t>
+          <t>2026-10-25T09:43:24.900133+07:00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>750</v>
+        <v>625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:52.003011+07:00</t>
+          <t>2026-10-25T09:43:23.059132+07:00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>625</v>
+        <v>750</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:52.158667+07:00</t>
+          <t>2026-10-25T09:43:23.572236+07:00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>625</v>
+        <v>1000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:47.315420+07:00</t>
+          <t>2026-10-25T09:43:18.920809+07:00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>875</v>
+        <v>1750</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:44.137322+07:00</t>
+          <t>2026-10-25T09:43:15.723386+07:00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -963,44 +963,50 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>ชุมพร</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T09:42:56.208800+07:00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="C13" t="n">
+        <v>250</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:26.416876+07:00</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1009,7 +1015,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1750</v>
+        <v>375</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1018,7 +1024,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1028,7 +1034,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:58.632856+07:00</t>
+          <t>2026-10-25T09:43:29.454152+07:00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1041,7 +1047,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1059,7 +1065,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1069,7 +1075,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:53.948318+07:00</t>
+          <t>2026-10-25T09:43:25.003446+07:00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1082,7 +1088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1091,7 +1097,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>750</v>
+        <v>1125</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1100,7 +1106,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1110,7 +1116,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:35.595624+07:00</t>
+          <t>2026-10-25T09:43:05.875217+07:00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1123,7 +1129,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1132,7 +1138,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1141,7 +1147,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1151,7 +1157,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:48.861215+07:00</t>
+          <t>2026-10-25T09:43:20.255927+07:00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1164,7 +1170,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1173,7 +1179,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>250</v>
+        <v>1125</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1182,7 +1188,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1192,7 +1198,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:31.724014+07:00</t>
+          <t>2026-10-25T09:43:01.580239+07:00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1205,7 +1211,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1214,7 +1220,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1250</v>
+        <v>250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1223,7 +1229,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1233,7 +1239,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:40.764247+07:00</t>
+          <t>2026-10-25T09:43:11.488434+07:00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1246,7 +1252,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1255,7 +1261,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>375</v>
+        <v>1250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1264,7 +1270,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1274,7 +1280,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:45.709865+07:00</t>
+          <t>2026-10-25T09:43:17.168588+07:00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1287,7 +1293,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1296,7 +1302,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1305,7 +1311,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1315,7 +1321,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:57.568763+07:00</t>
+          <t>2026-10-25T09:43:27.790317+07:00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1328,7 +1334,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1337,7 +1343,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>500</v>
+        <v>1125</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1346,7 +1352,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1356,7 +1362,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:47.085004+07:00</t>
+          <t>2026-10-25T09:43:18.436327+07:00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1369,7 +1375,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1378,7 +1384,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>750</v>
+        <v>1375</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1387,7 +1393,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1397,7 +1403,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:29.615949+07:00</t>
+          <t>2026-10-25T09:42:59.642529+07:00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1410,7 +1416,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1419,7 +1425,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>875</v>
+        <v>375</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1428,7 +1434,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1438,7 +1444,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-24T09:43:00.128013+07:00</t>
+          <t>2026-10-25T09:43:30.838742+07:00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1451,7 +1457,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1469,7 +1475,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1479,7 +1485,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:33.745456+07:00</t>
+          <t>2026-10-25T09:43:03.588319+07:00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1492,7 +1498,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1501,7 +1507,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1510,7 +1516,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1520,7 +1526,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:39.276000+07:00</t>
+          <t>2026-10-25T09:43:10.026079+07:00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1533,7 +1539,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1551,7 +1557,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1561,7 +1567,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:45.485320+07:00</t>
+          <t>2026-10-25T09:43:17.137976+07:00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1574,7 +1580,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1583,7 +1589,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>750</v>
+        <v>1375</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1592,7 +1598,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1602,7 +1608,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:29.616482+07:00</t>
+          <t>2026-10-25T09:42:59.642977+07:00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1615,7 +1621,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1624,7 +1630,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>375</v>
+        <v>875</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1633,7 +1639,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1643,7 +1649,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:55.635512+07:00</t>
+          <t>2026-10-25T09:43:26.334195+07:00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1656,7 +1662,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1665,74 +1671,80 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:23.749336+07:00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_430201.png</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>625</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2026-10-23 00Z</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-10-24T09:42:53.212027+07:00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_430201.png</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>ปัตตานี</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T09:42:59.031133+07:00</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:29.491093+07:00</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1741,7 +1753,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1750,7 +1762,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1760,7 +1772,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:48.683432+07:00</t>
+          <t>2026-10-25T09:43:19.732245+07:00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1773,7 +1785,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1791,7 +1803,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1801,7 +1813,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:33.720292+07:00</t>
+          <t>2026-10-25T09:43:03.575001+07:00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1814,7 +1826,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1823,16 +1835,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2500</v>
+        <v>875</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1842,7 +1854,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:57.140178+07:00</t>
+          <t>2026-10-25T09:43:27.653639+07:00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1855,7 +1867,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1864,7 +1876,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1873,7 +1885,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1883,7 +1895,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:58.268136+07:00</t>
+          <t>2026-10-25T09:43:29.355418+07:00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1896,7 +1908,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1914,7 +1926,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1924,7 +1936,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:37.623449+07:00</t>
+          <t>2026-10-25T09:43:08.161862+07:00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1937,7 +1949,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1946,7 +1958,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>625</v>
+        <v>1000</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1955,7 +1967,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1965,7 +1977,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:37.313656+07:00</t>
+          <t>2026-10-25T09:43:07.996870+07:00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1978,7 +1990,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1987,16 +1999,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5750</v>
+        <v>3000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2006,7 +2018,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:54.974285+07:00</t>
+          <t>2026-10-25T09:43:25.735620+07:00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2019,7 +2031,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2028,16 +2040,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1250</v>
+        <v>2125</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2047,7 +2059,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:43.277508+07:00</t>
+          <t>2026-10-25T09:43:15.261353+07:00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2060,7 +2072,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2069,7 +2081,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2078,7 +2090,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2088,7 +2100,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:42.439708+07:00</t>
+          <t>2026-10-25T09:43:13.814255+07:00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2101,7 +2113,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2110,16 +2122,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2129,7 +2141,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:59.750565+07:00</t>
+          <t>2026-10-25T09:43:30.736954+07:00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2142,7 +2154,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2151,7 +2163,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>875</v>
+        <v>750</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2160,7 +2172,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2170,7 +2182,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:44.739279+07:00</t>
+          <t>2026-10-25T09:43:17.106358+07:00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2183,7 +2195,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2192,16 +2204,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2250</v>
+        <v>1125</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2211,7 +2223,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:56.669288+07:00</t>
+          <t>2026-10-25T09:43:27.043101+07:00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2224,7 +2236,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2233,7 +2245,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1250</v>
+        <v>1750</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2242,7 +2254,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2252,7 +2264,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:52.426433+07:00</t>
+          <t>2026-10-25T09:43:23.640452+07:00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2265,7 +2277,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2274,7 +2286,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2283,7 +2295,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2293,7 +2305,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:50.212111+07:00</t>
+          <t>2026-10-25T09:43:21.067847+07:00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2306,7 +2318,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2324,7 +2336,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2334,7 +2346,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:43.599996+07:00</t>
+          <t>2026-10-25T09:43:15.518980+07:00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2347,7 +2359,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2356,7 +2368,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>625</v>
+        <v>875</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2365,7 +2377,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2375,7 +2387,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:50.651284+07:00</t>
+          <t>2026-10-25T09:43:21.799232+07:00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2388,7 +2400,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2397,7 +2409,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2406,7 +2418,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2416,7 +2428,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:35.401706+07:00</t>
+          <t>2026-10-25T09:43:05.691146+07:00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2429,7 +2441,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2438,7 +2450,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>250</v>
+        <v>625</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2447,7 +2459,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2457,7 +2469,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:33.770904+07:00</t>
+          <t>2026-10-25T09:43:03.628611+07:00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2470,7 +2482,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2479,7 +2491,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2488,7 +2500,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2498,7 +2510,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:45.602362+07:00</t>
+          <t>2026-10-25T09:43:17.162305+07:00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2511,7 +2523,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2520,7 +2532,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1125</v>
+        <v>625</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2529,7 +2541,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2539,7 +2551,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:42.130083+07:00</t>
+          <t>2026-10-25T09:43:13.786100+07:00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2552,7 +2564,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2561,7 +2573,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2570,7 +2582,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2580,7 +2592,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:54.744941+07:00</t>
+          <t>2026-10-25T09:43:25.071134+07:00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2593,7 +2605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2602,7 +2614,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1750</v>
+        <v>625</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2611,7 +2623,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2621,7 +2633,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:59.658052+07:00</t>
+          <t>2026-10-25T09:43:29.741575+07:00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2634,7 +2646,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2643,7 +2655,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1375</v>
+        <v>1125</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2652,7 +2664,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2662,7 +2674,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:29.617261+07:00</t>
+          <t>2026-10-25T09:42:59.643551+07:00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2675,7 +2687,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2684,7 +2696,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>375</v>
+        <v>1250</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2693,7 +2705,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2703,7 +2715,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:50.734356+07:00</t>
+          <t>2026-10-25T09:43:22.300286+07:00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2714,50 +2726,44 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>สมุทรสาคร</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-10-23 00Z</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2026-10-24T09:42:31.764748+07:00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="inlineStr"/>
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:01.587343+07:00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_474000.png</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2766,7 +2772,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>625</v>
+        <v>875</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2775,7 +2781,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2785,7 +2791,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:49.230257+07:00</t>
+          <t>2026-10-25T09:43:21.003095+07:00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2798,7 +2804,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2807,7 +2813,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>375</v>
+        <v>1250</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2816,7 +2822,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2826,7 +2832,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:53.481618+07:00</t>
+          <t>2026-10-25T09:43:24.390947+07:00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2839,7 +2845,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2848,7 +2854,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>750</v>
+        <v>875</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2857,7 +2863,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2867,7 +2873,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:48.723445+07:00</t>
+          <t>2026-10-25T09:43:20.233896+07:00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2880,7 +2886,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2889,7 +2895,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>875</v>
+        <v>1250</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2898,7 +2904,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2908,7 +2914,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:50.257426+07:00</t>
+          <t>2026-10-25T09:43:21.740585+07:00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2921,7 +2927,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2930,7 +2936,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2939,7 +2945,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2949,7 +2955,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:56.746981+07:00</t>
+          <t>2026-10-25T09:43:27.566109+07:00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2962,7 +2968,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2971,7 +2977,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>875</v>
+        <v>1000</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2980,7 +2986,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2990,7 +2996,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:46.217912+07:00</t>
+          <t>2026-10-25T09:43:18.412889+07:00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3003,7 +3009,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3012,7 +3018,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>625</v>
+        <v>1000</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3021,7 +3027,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3031,7 +3037,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:37.147371+07:00</t>
+          <t>2026-10-25T09:43:07.995192+07:00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3044,7 +3050,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3053,7 +3059,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>750</v>
+        <v>875</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3062,7 +3068,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3072,7 +3078,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:40.113393+07:00</t>
+          <t>2026-10-25T09:43:11.444916+07:00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3085,7 +3091,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3094,7 +3100,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>750</v>
+        <v>625</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3103,7 +3109,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3113,7 +3119,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:41.570996+07:00</t>
+          <t>2026-10-25T09:43:13.763532+07:00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3126,7 +3132,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3135,7 +3141,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3144,7 +3150,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3154,7 +3160,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:44.108749+07:00</t>
+          <t>2026-10-25T09:43:15.722602+07:00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3167,7 +3173,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3176,7 +3182,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>875</v>
+        <v>1000</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3185,7 +3191,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3195,7 +3201,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:40.990122+07:00</t>
+          <t>2026-10-25T09:43:11.627503+07:00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3208,7 +3214,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3217,7 +3223,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>875</v>
+        <v>750</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3226,7 +3232,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3236,7 +3242,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:35.640508+07:00</t>
+          <t>2026-10-25T09:43:05.876034+07:00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3249,7 +3255,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3258,7 +3264,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>875</v>
+        <v>1250</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3267,7 +3273,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3277,7 +3283,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:47.106290+07:00</t>
+          <t>2026-10-25T09:43:18.920014+07:00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3290,7 +3296,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3299,7 +3305,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>875</v>
+        <v>750</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3308,7 +3314,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3318,7 +3324,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:39.131015+07:00</t>
+          <t>2026-10-25T09:43:09.862286+07:00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3331,7 +3337,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3340,7 +3346,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3349,7 +3355,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3359,7 +3365,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:47.689244+07:00</t>
+          <t>2026-10-25T09:43:19.708224+07:00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3372,7 +3378,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3381,7 +3387,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1125</v>
+        <v>1000</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3390,7 +3396,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3400,7 +3406,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:32.026041+07:00</t>
+          <t>2026-10-25T09:43:01.750316+07:00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3413,7 +3419,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3422,7 +3428,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3431,7 +3437,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3441,7 +3447,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:31.913246+07:00</t>
+          <t>2026-10-25T09:43:01.748975+07:00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3454,7 +3460,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3463,7 +3469,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>500</v>
+        <v>1250</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3472,7 +3478,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3482,7 +3488,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:55.214925+07:00</t>
+          <t>2026-10-25T09:43:26.231948+07:00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3495,7 +3501,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3504,7 +3510,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>500</v>
+        <v>125</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3513,7 +3519,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3523,7 +3529,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:38.630459+07:00</t>
+          <t>2026-10-25T09:43:09.817960+07:00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3536,7 +3542,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3545,7 +3551,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3554,7 +3560,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3564,7 +3570,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:40.657205+07:00</t>
+          <t>2026-10-25T09:43:11.478502+07:00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3577,7 +3583,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3586,7 +3592,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3595,7 +3601,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3605,7 +3611,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:35.431353+07:00</t>
+          <t>2026-10-25T09:43:05.696068+07:00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3618,7 +3624,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3627,7 +3633,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>875</v>
+        <v>250</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3636,7 +3642,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-23 00Z</t>
+          <t>2026-10-24 00Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3646,7 +3652,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-24T09:42:33.550674+07:00</t>
+          <t>2026-10-25T09:43:03.386724+07:00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3747,7 +3753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I386"/>
+  <dimension ref="A1:I463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19569,8 +19575,3159 @@
       </c>
       <c r="I386" t="inlineStr"/>
     </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>กระบี่</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:28.387675+07:00</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_566202.png</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:42:59.641918+07:00</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_455301.png</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>875</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:22.398707+07:00</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_450201.png</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>กาฬสินธุ์</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:13.958846+07:00</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_388401.png</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>กำแพงเพชร</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:08.159898+07:00</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_380201.png</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>ขอนแก่น</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:10.022774+07:00</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_381201.png</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>จันทบุรี</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:24.900133+07:00</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_480201.png</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>ฉะเชิงเทรา</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>625</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:23.059132+07:00</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_423301.png</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>ชลบุรี</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>750</v>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:23.572236+07:00</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_459201.png</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>ชัยนาท</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:18.920809+07:00</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_402301.png</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>ชัยภูมิ</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:15.723386+07:00</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_403201.png</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>250</v>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:26.416876+07:00</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>ตรัง</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>375</v>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:29.454152+07:00</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_567201.png</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>ตราด</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>750</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:25.003446+07:00</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_501201.png</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>ตาก</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:05.875217+07:00</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_376201.png</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>750</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:20.255927+07:00</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_417201.png</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:01.580239+07:00</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>นครพนม</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>250</v>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:11.488434+07:00</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_357201.png</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>นครราชสีมา</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:17.168588+07:00</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_431201.png</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>นครศรีธรรมราช</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>375</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:27.790317+07:00</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_552201.png</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>นครสวรรค์</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:18.436327+07:00</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_400201.png</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:42:59.642529+07:00</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_411000.png</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>นราธิวาส</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>375</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:30.838742+07:00</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_583201.png</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>น่าน</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>375</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:03.588319+07:00</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_331201.png</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>บึงกาฬ</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>500</v>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:10.026079+07:00</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_363201.png</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>บุรีรัมย์</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>875</v>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:17.137976+07:00</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_436201.png</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>ปทุมธานี</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:42:59.642977+07:00</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_419301.png</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>ประจวบคีรีขันธ์</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>875</v>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:26.334195+07:00</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_500201.png</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>ปราจีนบุรี</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:23.749336+07:00</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_430201.png</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>625</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:29.491093+07:00</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>พระนครศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:19.732245+07:00</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>พะเยา</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:03.575001+07:00</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_310201.png</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>พังงา</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>875</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:27.653639+07:00</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_561201.png</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>พัทลุง</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>500</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:29.355418+07:00</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_560301.png</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>พิจิตร</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>875</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:08.161862+07:00</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_386301.png</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:07.996870+07:00</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_378201.png</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>ภูเก็ต</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:25.735620+07:00</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_564201.png</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>มหาสารคาม</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:15.261353+07:00</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_387401.png</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>มุกดาหาร</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>500</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:13.814255+07:00</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>ยะลา</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>250</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:30.736954+07:00</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_581301.png</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>ยโสธร</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>750</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:17.106358+07:00</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_406201.png</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>ระนอง</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:27.043101+07:00</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_532201.png</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>ระยอง</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:23.640452+07:00</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>ราชบุรี</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:21.067847+07:00</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:15.518980+07:00</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_405201.png</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>ลพบุรี</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>875</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:21.799232+07:00</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_426201.png</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>ลำปาง</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>750</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:05.691146+07:00</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_328201.png</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>ลำพูน</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>625</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:03.628611+07:00</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_329201.png</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>ศรีสะเกษ</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>500</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:17.162305+07:00</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_409301.png</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>สกลนคร</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>625</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:13.786100+07:00</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_356201.png</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>สงขลา</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>500</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:25.071134+07:00</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_568501.png</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>สตูล</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>625</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:29.741575+07:00</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_570201.png</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>สมุทรปราการ</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:42:59.643551+07:00</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_429301.png</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>สมุทรสงคราม</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:22.300286+07:00</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_438201.png</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B441" s="3" t="inlineStr">
+        <is>
+          <t>สมุทรสาคร</t>
+        </is>
+      </c>
+      <c r="C441" s="3" t="n"/>
+      <c r="D441" s="3" t="inlineStr"/>
+      <c r="E441" s="3" t="inlineStr"/>
+      <c r="F441" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G441" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:01.587343+07:00</t>
+        </is>
+      </c>
+      <c r="H441" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_474000.png</t>
+        </is>
+      </c>
+      <c r="I441" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>สระบุรี</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>875</v>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:21.003095+07:00</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_418000.png</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>สระแก้ว</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:24.390947+07:00</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_440401.png</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>สิงห์บุรี</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>875</v>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:20.233896+07:00</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_416000.png</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:21.740585+07:00</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_425201.png</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>สุราษฎร์ธานี</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>250</v>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:27.566109+07:00</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_551201.png</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>สุรินทร์</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:18.412889+07:00</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_432201.png</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>สุโขทัย</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:07.995192+07:00</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_373201.png</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>หนองคาย</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>875</v>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:11.444916+07:00</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_352201.png</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>หนองบัวลำภู</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>625</v>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:13.763532+07:00</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_360201.png</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>อำนาจเจริญ</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:15.722602+07:00</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>อุดรธานี</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:11.627503+07:00</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>อุตรดิตถ์</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>750</v>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:05.876034+07:00</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_351201.png</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>อุทัยธานี</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:18.920014+07:00</t>
+        </is>
+      </c>
+      <c r="H454" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_410201.png</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>อุบลราชธานี</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>750</v>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:09.862286+07:00</t>
+        </is>
+      </c>
+      <c r="H455" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_407501.png</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>อ่างทอง</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:19.708224+07:00</t>
+        </is>
+      </c>
+      <c r="H456" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_414000.png</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>เชียงราย</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:01.750316+07:00</t>
+        </is>
+      </c>
+      <c r="H457" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_303201.png</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>เชียงใหม่</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>750</v>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:01.748975+07:00</t>
+        </is>
+      </c>
+      <c r="H458" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_327501.png</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>เพชรบุรี</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:26.231948+07:00</t>
+        </is>
+      </c>
+      <c r="H459" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_465201.png</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>125</v>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:09.817960+07:00</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_379201.png</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>เลย</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>750</v>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:11.478502+07:00</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_353201.png</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>แพร่</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>500</v>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:05.696068+07:00</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_330201.png</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>แม่ฮ่องสอน</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>250</v>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>2026-10-24 00Z</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:03.386724+07:00</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_300201.png</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I386"/>
+  <autoFilter ref="A1:I463"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -19957,6 +23114,83 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId383"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId384"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H463" r:id="rId462"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19968,7 +23202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -20169,13 +23403,49 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>สมุทรสาคร</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:43:01.587343+07:00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_474000.png</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I5"/>
+  <autoFilter ref="A1:I6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ventilation.xlsx
+++ b/data/ventilation.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ล่าสุด'!$A$1:$I$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$463</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$540</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:28.387675+07:00</t>
+          <t>2026-10-26T09:46:49.960194+07:00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,16 +564,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2000</v>
+        <v>1375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-25T09:42:59.641918+07:00</t>
+          <t>2026-10-26T09:46:20.224119+07:00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>875</v>
+        <v>1000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:22.398707+07:00</t>
+          <t>2026-10-26T09:46:43.684283+07:00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1375</v>
+        <v>4000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:13.958846+07:00</t>
+          <t>2026-10-26T09:46:35.158984+07:00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:08.159898+07:00</t>
+          <t>2026-10-26T09:46:29.115774+07:00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1750</v>
+        <v>3875</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:10.022774+07:00</t>
+          <t>2026-10-26T09:46:30.722721+07:00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:24.900133+07:00</t>
+          <t>2026-10-26T09:46:45.381236+07:00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:23.059132+07:00</t>
+          <t>2026-10-26T09:46:43.827670+07:00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:23.572236+07:00</t>
+          <t>2026-10-26T09:46:43.841593+07:00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:18.920809+07:00</t>
+          <t>2026-10-26T09:46:39.525828+07:00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1750</v>
+        <v>1375</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:15.723386+07:00</t>
+          <t>2026-10-26T09:46:36.611523+07:00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>250</v>
+        <v>4125</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:26.416876+07:00</t>
+          <t>2026-10-26T09:46:48.089324+07:00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>375</v>
+        <v>875</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:29.454152+07:00</t>
+          <t>2026-10-26T09:46:50.142989+07:00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:25.003446+07:00</t>
+          <t>2026-10-26T09:46:45.762250+07:00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1125</v>
+        <v>875</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:05.875217+07:00</t>
+          <t>2026-10-26T09:46:27.106686+07:00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>750</v>
+        <v>625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:20.255927+07:00</t>
+          <t>2026-10-26T09:46:40.973994+07:00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1125</v>
+        <v>1000</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:01.580239+07:00</t>
+          <t>2026-10-26T09:46:22.501601+07:00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1220,16 +1220,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>250</v>
+        <v>4000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:11.488434+07:00</t>
+          <t>2026-10-26T09:46:32.730534+07:00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1250</v>
+        <v>875</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:17.168588+07:00</t>
+          <t>2026-10-26T09:46:38.120105+07:00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1291,50 +1291,44 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>นครศรีธรรมราช</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>375</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-10-24 00Z</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-10-25T09:43:27.790317+07:00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:49.534116+07:00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_552201.png</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>cannot_locate_bar</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1343,7 +1337,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1125</v>
+        <v>625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1352,7 +1346,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1362,7 +1356,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:18.436327+07:00</t>
+          <t>2026-10-26T09:46:38.948553+07:00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1375,7 +1369,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1384,7 +1378,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1375</v>
+        <v>1000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1393,7 +1387,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1403,7 +1397,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-25T09:42:59.642529+07:00</t>
+          <t>2026-10-26T09:46:20.224827+07:00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1416,7 +1410,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1434,7 +1428,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1444,7 +1438,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:30.838742+07:00</t>
+          <t>2026-10-26T09:46:51.590070+07:00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1457,7 +1451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1466,7 +1460,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>375</v>
+        <v>125</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1475,7 +1469,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1485,7 +1479,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:03.588319+07:00</t>
+          <t>2026-10-26T09:46:25.224958+07:00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1498,7 +1492,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1507,7 +1501,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1516,7 +1510,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1526,7 +1520,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:10.026079+07:00</t>
+          <t>2026-10-26T09:46:31.014590+07:00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1539,7 +1533,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1548,7 +1542,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>875</v>
+        <v>1250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1557,7 +1551,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1567,7 +1561,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:17.137976+07:00</t>
+          <t>2026-10-26T09:46:37.532114+07:00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1580,7 +1574,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1589,7 +1583,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1375</v>
+        <v>1000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1598,7 +1592,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1608,7 +1602,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-25T09:42:59.642977+07:00</t>
+          <t>2026-10-26T09:46:20.225218+07:00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1621,7 +1615,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1630,16 +1624,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>875</v>
+        <v>2000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1649,7 +1643,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:26.334195+07:00</t>
+          <t>2026-10-26T09:46:47.177261+07:00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1662,7 +1656,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1671,7 +1665,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1000</v>
+        <v>625</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1680,7 +1674,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1690,7 +1684,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:23.749336+07:00</t>
+          <t>2026-10-26T09:46:45.175824+07:00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1703,7 +1697,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1712,7 +1706,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1721,7 +1715,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1731,7 +1725,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:29.491093+07:00</t>
+          <t>2026-10-26T09:46:50.718128+07:00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1744,7 +1738,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1753,7 +1747,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1762,7 +1756,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1772,7 +1766,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:19.732245+07:00</t>
+          <t>2026-10-26T09:46:40.350234+07:00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1785,7 +1779,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1794,7 +1788,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1803,7 +1797,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1813,7 +1807,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:03.575001+07:00</t>
+          <t>2026-10-26T09:46:25.130347+07:00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1826,7 +1820,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1835,7 +1829,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>875</v>
+        <v>1000</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1844,7 +1838,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1854,7 +1848,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:27.653639+07:00</t>
+          <t>2026-10-26T09:46:48.626744+07:00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1867,7 +1861,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1876,7 +1870,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>500</v>
+        <v>125</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1885,7 +1879,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1895,7 +1889,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:29.355418+07:00</t>
+          <t>2026-10-26T09:46:50.040793+07:00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1908,7 +1902,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1917,7 +1911,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>875</v>
+        <v>500</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1926,7 +1920,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1936,7 +1930,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:08.161862+07:00</t>
+          <t>2026-10-26T09:46:29.118677+07:00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1949,7 +1943,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1958,7 +1952,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1967,7 +1961,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1977,7 +1971,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:07.996870+07:00</t>
+          <t>2026-10-26T09:46:29.000677+07:00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1990,7 +1984,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1999,16 +1993,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3000</v>
+        <v>1750</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2018,7 +2012,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:25.735620+07:00</t>
+          <t>2026-10-26T09:46:46.782793+07:00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2031,7 +2025,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2040,16 +2034,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2125</v>
+        <v>4125</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2059,7 +2053,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:15.261353+07:00</t>
+          <t>2026-10-26T09:46:35.229124+07:00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2072,7 +2066,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2081,16 +2075,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>500</v>
+        <v>4375</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2100,7 +2094,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:13.814255+07:00</t>
+          <t>2026-10-26T09:46:35.094387+07:00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2113,7 +2107,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2122,7 +2116,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2131,7 +2125,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2141,7 +2135,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:30.736954+07:00</t>
+          <t>2026-10-26T09:46:51.537512+07:00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2154,7 +2148,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2163,16 +2157,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>750</v>
+        <v>2500</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2182,7 +2176,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:17.106358+07:00</t>
+          <t>2026-10-26T09:46:36.745870+07:00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2195,7 +2189,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2204,7 +2198,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1125</v>
+        <v>1000</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2213,7 +2207,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2223,7 +2217,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:27.043101+07:00</t>
+          <t>2026-10-26T09:46:48.272179+07:00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2236,7 +2230,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2245,7 +2239,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1750</v>
+        <v>1375</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2254,7 +2248,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2264,7 +2258,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:23.640452+07:00</t>
+          <t>2026-10-26T09:46:44.333971+07:00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2277,7 +2271,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2286,7 +2280,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1500</v>
+        <v>1375</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2295,7 +2289,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2305,7 +2299,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:21.067847+07:00</t>
+          <t>2026-10-26T09:46:41.760712+07:00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2318,7 +2312,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2327,16 +2321,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1125</v>
+        <v>3375</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2346,7 +2340,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:15.518980+07:00</t>
+          <t>2026-10-26T09:46:35.858061+07:00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2359,7 +2353,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2368,7 +2362,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>875</v>
+        <v>500</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2377,7 +2371,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2387,7 +2381,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:21.799232+07:00</t>
+          <t>2026-10-26T09:46:42.390127+07:00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2400,7 +2394,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2409,7 +2403,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2418,7 +2412,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2428,7 +2422,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:05.691146+07:00</t>
+          <t>2026-10-26T09:46:26.860462+07:00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2441,7 +2435,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2450,7 +2444,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>625</v>
+        <v>375</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2459,7 +2453,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2469,7 +2463,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:03.628611+07:00</t>
+          <t>2026-10-26T09:46:25.331124+07:00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2482,7 +2476,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2491,7 +2485,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>500</v>
+        <v>875</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2500,7 +2494,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2510,7 +2504,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:17.162305+07:00</t>
+          <t>2026-10-26T09:46:38.028230+07:00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2523,7 +2517,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2532,16 +2526,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>625</v>
+        <v>4125</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2551,7 +2545,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:13.786100+07:00</t>
+          <t>2026-10-26T09:46:33.974623+07:00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2564,7 +2558,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2573,7 +2567,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2582,7 +2576,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2592,7 +2586,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:25.071134+07:00</t>
+          <t>2026-10-26T09:46:46.662057+07:00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2605,7 +2599,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2614,7 +2608,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>625</v>
+        <v>875</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2623,7 +2617,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2633,7 +2627,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:29.741575+07:00</t>
+          <t>2026-10-26T09:46:51.434932+07:00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2646,7 +2640,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2655,7 +2649,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1125</v>
+        <v>875</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2664,7 +2658,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2674,7 +2668,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-25T09:42:59.643551+07:00</t>
+          <t>2026-10-26T09:46:20.225870+07:00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2687,7 +2681,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2696,7 +2690,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2705,7 +2699,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2715,7 +2709,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:22.300286+07:00</t>
+          <t>2026-10-26T09:46:42.921439+07:00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2726,44 +2720,50 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>สมุทรสาคร</t>
         </is>
       </c>
-      <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-25T09:43:01.587343+07:00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="C56" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:22.504978+07:00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_474000.png</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>875</v>
+        <v>125</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:21.003095+07:00</t>
+          <t>2026-10-26T09:46:41.514431+07:00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2804,7 +2804,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1250</v>
+        <v>625</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:24.390947+07:00</t>
+          <t>2026-10-26T09:46:45.349259+07:00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>875</v>
+        <v>500</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:20.233896+07:00</t>
+          <t>2026-10-26T09:46:40.913739+07:00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1250</v>
+        <v>750</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:21.740585+07:00</t>
+          <t>2026-10-26T09:46:42.317503+07:00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2927,7 +2927,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>250</v>
+        <v>625</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:27.566109+07:00</t>
+          <t>2026-10-26T09:46:48.399995+07:00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:18.412889+07:00</t>
+          <t>2026-10-26T09:46:38.248612+07:00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3009,7 +3009,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:07.995192+07:00</t>
+          <t>2026-10-26T09:46:28.713600+07:00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3050,7 +3050,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>875</v>
+        <v>1625</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:11.444916+07:00</t>
+          <t>2026-10-26T09:46:32.073613+07:00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3100,16 +3100,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>625</v>
+        <v>2750</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:13.763532+07:00</t>
+          <t>2026-10-26T09:46:33.685699+07:00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3141,16 +3141,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1000</v>
+        <v>4250</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:15.722602+07:00</t>
+          <t>2026-10-26T09:46:36.589514+07:00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3171,50 +3171,44 @@
       <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>อุดรธานี</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2026-10-24 00Z</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2026-10-25T09:43:11.627503+07:00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="C67" s="3" t="n"/>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:32.887754+07:00</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3223,7 +3217,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3232,7 +3226,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3242,7 +3236,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:05.876034+07:00</t>
+          <t>2026-10-26T09:46:27.110216+07:00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3255,7 +3249,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3264,7 +3258,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1250</v>
+        <v>625</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3273,7 +3267,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3283,7 +3277,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:18.920014+07:00</t>
+          <t>2026-10-26T09:46:39.452771+07:00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3296,7 +3290,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3305,7 +3299,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3314,7 +3308,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3324,7 +3318,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:09.862286+07:00</t>
+          <t>2026-10-26T09:46:30.709934+07:00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3337,7 +3331,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3346,7 +3340,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3355,7 +3349,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3365,7 +3359,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:19.708224+07:00</t>
+          <t>2026-10-26T09:46:40.098932+07:00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3378,7 +3372,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3387,7 +3381,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1000</v>
+        <v>625</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3396,7 +3390,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3406,7 +3400,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:01.750316+07:00</t>
+          <t>2026-10-26T09:46:22.662026+07:00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3419,7 +3413,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3428,7 +3422,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3437,7 +3431,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3447,7 +3441,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:01.748975+07:00</t>
+          <t>2026-10-26T09:46:22.633095+07:00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3460,7 +3454,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3469,7 +3463,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3478,7 +3472,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3488,7 +3482,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:26.231948+07:00</t>
+          <t>2026-10-26T09:46:46.878745+07:00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3501,7 +3495,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3519,7 +3513,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3529,7 +3523,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:09.817960+07:00</t>
+          <t>2026-10-26T09:46:30.667974+07:00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3542,7 +3536,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3551,7 +3545,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>750</v>
+        <v>875</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3560,7 +3554,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3570,7 +3564,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:11.478502+07:00</t>
+          <t>2026-10-26T09:46:32.544779+07:00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3583,7 +3577,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3592,7 +3586,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3601,7 +3595,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3611,7 +3605,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:05.696068+07:00</t>
+          <t>2026-10-26T09:46:27.106293+07:00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3624,7 +3618,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3633,7 +3627,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3642,7 +3636,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-24 00Z</t>
+          <t>2026-10-25 00Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3652,7 +3646,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-25T09:43:03.386724+07:00</t>
+          <t>2026-10-26T09:46:24.906797+07:00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3753,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I463"/>
+  <dimension ref="A1:I540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22726,8 +22720,3153 @@
       </c>
       <c r="I463" t="inlineStr"/>
     </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>กระบี่</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:49.960194+07:00</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_566202.png</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:20.224119+07:00</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_455301.png</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:43.684283+07:00</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_450201.png</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>กาฬสินธุ์</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:35.158984+07:00</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_388401.png</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>กำแพงเพชร</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>750</v>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:29.115774+07:00</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_380201.png</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>ขอนแก่น</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>3875</v>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:30.722721+07:00</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_381201.png</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>จันทบุรี</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>500</v>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:45.381236+07:00</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_480201.png</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>ฉะเชิงเทรา</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>625</v>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:43.827670+07:00</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_423301.png</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>ชลบุรี</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>375</v>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:43.841593+07:00</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_459201.png</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>ชัยนาท</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>250</v>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:39.525828+07:00</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_402301.png</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>ชัยภูมิ</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:36.611523+07:00</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_403201.png</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>4125</v>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:48.089324+07:00</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>ตรัง</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>875</v>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:50.142989+07:00</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_567201.png</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>ตราด</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>375</v>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:45.762250+07:00</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_501201.png</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>ตาก</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>875</v>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:27.106686+07:00</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_376201.png</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>625</v>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:40.973994+07:00</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_417201.png</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:22.501601+07:00</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>นครพนม</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:32.730534+07:00</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_357201.png</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>นครราชสีมา</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>875</v>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:38.120105+07:00</t>
+        </is>
+      </c>
+      <c r="H482" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_431201.png</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B483" s="3" t="inlineStr">
+        <is>
+          <t>นครศรีธรรมราช</t>
+        </is>
+      </c>
+      <c r="C483" s="3" t="n"/>
+      <c r="D483" s="3" t="inlineStr"/>
+      <c r="E483" s="3" t="inlineStr"/>
+      <c r="F483" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G483" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:49.534116+07:00</t>
+        </is>
+      </c>
+      <c r="H483" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_552201.png</t>
+        </is>
+      </c>
+      <c r="I483" s="3" t="inlineStr">
+        <is>
+          <t>cannot_locate_bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>นครสวรรค์</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>625</v>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:38.948553+07:00</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_400201.png</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:20.224827+07:00</t>
+        </is>
+      </c>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_411000.png</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>นราธิวาส</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>375</v>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:51.590070+07:00</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_583201.png</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>น่าน</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>125</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:25.224958+07:00</t>
+        </is>
+      </c>
+      <c r="H487" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_331201.png</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>บึงกาฬ</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:31.014590+07:00</t>
+        </is>
+      </c>
+      <c r="H488" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_363201.png</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>บุรีรัมย์</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:37.532114+07:00</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_436201.png</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>ปทุมธานี</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:20.225218+07:00</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_419301.png</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>ประจวบคีรีขันธ์</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:47.177261+07:00</t>
+        </is>
+      </c>
+      <c r="H491" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_500201.png</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>ปราจีนบุรี</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>625</v>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:45.175824+07:00</t>
+        </is>
+      </c>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_430201.png</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>500</v>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:50.718128+07:00</t>
+        </is>
+      </c>
+      <c r="H493" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>พระนครศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>250</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:40.350234+07:00</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>พะเยา</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>750</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:25.130347+07:00</t>
+        </is>
+      </c>
+      <c r="H495" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_310201.png</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>พังงา</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:48.626744+07:00</t>
+        </is>
+      </c>
+      <c r="H496" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_561201.png</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>พัทลุง</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>125</v>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:50.040793+07:00</t>
+        </is>
+      </c>
+      <c r="H497" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_560301.png</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>พิจิตร</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>500</v>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:29.118677+07:00</t>
+        </is>
+      </c>
+      <c r="H498" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_386301.png</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>375</v>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:29.000677+07:00</t>
+        </is>
+      </c>
+      <c r="H499" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_378201.png</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>ภูเก็ต</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:46.782793+07:00</t>
+        </is>
+      </c>
+      <c r="H500" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_564201.png</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>มหาสารคาม</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>4125</v>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:35.229124+07:00</t>
+        </is>
+      </c>
+      <c r="H501" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_387401.png</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>มุกดาหาร</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>4375</v>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:35.094387+07:00</t>
+        </is>
+      </c>
+      <c r="H502" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>ยะลา</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>375</v>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:51.537512+07:00</t>
+        </is>
+      </c>
+      <c r="H503" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_581301.png</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>ยโสธร</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:36.745870+07:00</t>
+        </is>
+      </c>
+      <c r="H504" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_406201.png</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>ระนอง</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:48.272179+07:00</t>
+        </is>
+      </c>
+      <c r="H505" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_532201.png</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>ระยอง</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:44.333971+07:00</t>
+        </is>
+      </c>
+      <c r="H506" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>ราชบุรี</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:41.760712+07:00</t>
+        </is>
+      </c>
+      <c r="H507" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>3375</v>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:35.858061+07:00</t>
+        </is>
+      </c>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_405201.png</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>ลพบุรี</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>500</v>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:42.390127+07:00</t>
+        </is>
+      </c>
+      <c r="H509" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_426201.png</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>ลำปาง</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>375</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:26.860462+07:00</t>
+        </is>
+      </c>
+      <c r="H510" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_328201.png</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>ลำพูน</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>375</v>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:25.331124+07:00</t>
+        </is>
+      </c>
+      <c r="H511" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_329201.png</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>ศรีสะเกษ</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>875</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:38.028230+07:00</t>
+        </is>
+      </c>
+      <c r="H512" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_409301.png</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>สกลนคร</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>4125</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:33.974623+07:00</t>
+        </is>
+      </c>
+      <c r="H513" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_356201.png</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>สงขลา</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>750</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:46.662057+07:00</t>
+        </is>
+      </c>
+      <c r="H514" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_568501.png</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>สตูล</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>875</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:51.434932+07:00</t>
+        </is>
+      </c>
+      <c r="H515" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_570201.png</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>สมุทรปราการ</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>875</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:20.225870+07:00</t>
+        </is>
+      </c>
+      <c r="H516" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_429301.png</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>สมุทรสงคราม</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:42.921439+07:00</t>
+        </is>
+      </c>
+      <c r="H517" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_438201.png</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>สมุทรสาคร</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:22.504978+07:00</t>
+        </is>
+      </c>
+      <c r="H518" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_474000.png</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>สระบุรี</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>125</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:41.514431+07:00</t>
+        </is>
+      </c>
+      <c r="H519" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_418000.png</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>สระแก้ว</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>625</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:45.349259+07:00</t>
+        </is>
+      </c>
+      <c r="H520" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_440401.png</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>สิงห์บุรี</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>500</v>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:40.913739+07:00</t>
+        </is>
+      </c>
+      <c r="H521" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_416000.png</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>750</v>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:42.317503+07:00</t>
+        </is>
+      </c>
+      <c r="H522" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_425201.png</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>สุราษฎร์ธานี</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>625</v>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:48.399995+07:00</t>
+        </is>
+      </c>
+      <c r="H523" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_551201.png</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>สุรินทร์</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:38.248612+07:00</t>
+        </is>
+      </c>
+      <c r="H524" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_432201.png</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>สุโขทัย</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>500</v>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:28.713600+07:00</t>
+        </is>
+      </c>
+      <c r="H525" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_373201.png</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>หนองคาย</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:32.073613+07:00</t>
+        </is>
+      </c>
+      <c r="H526" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_352201.png</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>หนองบัวลำภู</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:33.685699+07:00</t>
+        </is>
+      </c>
+      <c r="H527" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_360201.png</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>อำนาจเจริญ</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>4250</v>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:36.589514+07:00</t>
+        </is>
+      </c>
+      <c r="H528" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B529" s="3" t="inlineStr">
+        <is>
+          <t>อุดรธานี</t>
+        </is>
+      </c>
+      <c r="C529" s="3" t="n"/>
+      <c r="D529" s="3" t="inlineStr"/>
+      <c r="E529" s="3" t="inlineStr"/>
+      <c r="F529" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G529" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:32.887754+07:00</t>
+        </is>
+      </c>
+      <c r="H529" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
+        </is>
+      </c>
+      <c r="I529" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>อุตรดิตถ์</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>250</v>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:27.110216+07:00</t>
+        </is>
+      </c>
+      <c r="H530" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_351201.png</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>อุทัยธานี</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>625</v>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:39.452771+07:00</t>
+        </is>
+      </c>
+      <c r="H531" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_410201.png</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>อุบลราชธานี</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:30.709934+07:00</t>
+        </is>
+      </c>
+      <c r="H532" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_407501.png</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>อ่างทอง</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>375</v>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:40.098932+07:00</t>
+        </is>
+      </c>
+      <c r="H533" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_414000.png</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>เชียงราย</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>625</v>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:22.662026+07:00</t>
+        </is>
+      </c>
+      <c r="H534" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_303201.png</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>เชียงใหม่</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>500</v>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:22.633095+07:00</t>
+        </is>
+      </c>
+      <c r="H535" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_327501.png</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>เพชรบุรี</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:46.878745+07:00</t>
+        </is>
+      </c>
+      <c r="H536" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_465201.png</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>125</v>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:30.667974+07:00</t>
+        </is>
+      </c>
+      <c r="H537" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_379201.png</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>เลย</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>875</v>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:32.544779+07:00</t>
+        </is>
+      </c>
+      <c r="H538" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_353201.png</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>แพร่</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>250</v>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:27.106293+07:00</t>
+        </is>
+      </c>
+      <c r="H539" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_330201.png</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>แม่ฮ่องสอน</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>125</v>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>2026-10-25 00Z</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:24.906797+07:00</t>
+        </is>
+      </c>
+      <c r="H540" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_300201.png</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I463"/>
+  <autoFilter ref="A1:I540"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -23191,6 +26330,83 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H461" r:id="rId460"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H462" r:id="rId461"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H502" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H503" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H504" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H505" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H506" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H507" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H508" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H509" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H510" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H511" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H512" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H513" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H514" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H515" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H516" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H517" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H518" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H519" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H520" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H521" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H522" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H523" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H524" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H525" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H526" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H527" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H528" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H529" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H530" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H531" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H532" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H533" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H534" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H535" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H536" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H537" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H538" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H539" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H540" r:id="rId539"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23202,7 +26418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -23438,14 +26654,86 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>นครศรีธรรมราช</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:49.534116+07:00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_552201.png</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>cannot_locate_bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>อุดรธานี</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:46:32.887754+07:00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I6"/>
+  <autoFilter ref="A1:I8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ventilation.xlsx
+++ b/data/ventilation.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ล่าสุด'!$A$1:$I$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$540</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$617</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -523,16 +523,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1000</v>
+        <v>2375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:49.960194+07:00</t>
+          <t>2026-10-27T09:46:35.839954+07:00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,16 +564,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1375</v>
+        <v>4375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:20.224119+07:00</t>
+          <t>2026-10-27T09:46:07.889214+07:00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1000</v>
+        <v>2125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:43.684283+07:00</t>
+          <t>2026-10-27T09:46:29.522118+07:00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4000</v>
+        <v>6125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:35.158984+07:00</t>
+          <t>2026-10-27T09:46:20.895111+07:00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>750</v>
+        <v>1125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:29.115774+07:00</t>
+          <t>2026-10-27T09:46:15.485526+07:00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3875</v>
+        <v>4875</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:30.722721+07:00</t>
+          <t>2026-10-27T09:46:17.032232+07:00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>500</v>
+        <v>1250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:45.381236+07:00</t>
+          <t>2026-10-27T09:46:32.166301+07:00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -810,16 +810,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>625</v>
+        <v>2875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:43.827670+07:00</t>
+          <t>2026-10-27T09:46:29.798382+07:00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>375</v>
+        <v>2750</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:43.841593+07:00</t>
+          <t>2026-10-27T09:46:30.854625+07:00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -892,16 +892,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>250</v>
+        <v>2375</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:39.525828+07:00</t>
+          <t>2026-10-27T09:46:26.563720+07:00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -933,16 +933,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1375</v>
+        <v>5125</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:36.611523+07:00</t>
+          <t>2026-10-27T09:46:22.970668+07:00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4125</v>
+        <v>5875</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:48.089324+07:00</t>
+          <t>2026-10-27T09:46:34.144811+07:00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>875</v>
+        <v>1250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:50.142989+07:00</t>
+          <t>2026-10-27T09:46:36.460138+07:00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>375</v>
+        <v>875</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:45.762250+07:00</t>
+          <t>2026-10-27T09:46:32.168967+07:00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>875</v>
+        <v>625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:27.106686+07:00</t>
+          <t>2026-10-27T09:46:13.212446+07:00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>625</v>
+        <v>2000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:40.973994+07:00</t>
+          <t>2026-10-27T09:46:27.992418+07:00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1168,50 +1168,44 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>นครปฐม</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-10-25 00Z</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-10-26T09:46:22.501601+07:00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:10.023452+07:00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1220,7 +1214,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4000</v>
+        <v>5375</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1229,7 +1223,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1239,7 +1233,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:32.730534+07:00</t>
+          <t>2026-10-27T09:46:19.275021+07:00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1252,7 +1246,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1261,16 +1255,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>875</v>
+        <v>2875</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1280,7 +1274,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:38.120105+07:00</t>
+          <t>2026-10-27T09:46:24.469644+07:00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1291,44 +1285,50 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>นครศรีธรรมราช</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T09:46:49.534116+07:00</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="C21" t="n">
+        <v>375</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:35.651043+07:00</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_552201.png</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>cannot_locate_bar</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>625</v>
+        <v>2750</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:38.948553+07:00</t>
+          <t>2026-10-27T09:46:24.660480+07:00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1378,16 +1378,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1000</v>
+        <v>2250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:20.224827+07:00</t>
+          <t>2026-10-27T09:46:07.889747+07:00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:51.590070+07:00</t>
+          <t>2026-10-27T09:46:37.791540+07:00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>125</v>
+        <v>625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:25.224958+07:00</t>
+          <t>2026-10-27T09:46:11.786521+07:00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1501,16 +1501,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1500</v>
+        <v>3125</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:31.014590+07:00</t>
+          <t>2026-10-27T09:46:17.048827+07:00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1542,16 +1542,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1250</v>
+        <v>3000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:37.532114+07:00</t>
+          <t>2026-10-27T09:46:23.010278+07:00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1574,7 +1574,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1583,16 +1583,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1000</v>
+        <v>2250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:20.225218+07:00</t>
+          <t>2026-10-27T09:46:07.890068+07:00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2000</v>
+        <v>3875</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:47.177261+07:00</t>
+          <t>2026-10-27T09:46:33.648167+07:00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>625</v>
+        <v>1500</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:45.175824+07:00</t>
+          <t>2026-10-27T09:46:31.106425+07:00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1695,50 +1695,44 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>ปัตตานี</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>500</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026-10-25 00Z</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-10-26T09:46:50.718128+07:00</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:36.945038+07:00</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>cannot_locate_bar</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1747,7 +1741,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>250</v>
+        <v>1625</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1756,7 +1750,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1766,7 +1760,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:40.350234+07:00</t>
+          <t>2026-10-27T09:46:26.743228+07:00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1779,7 +1773,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1788,7 +1782,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1797,7 +1791,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1807,7 +1801,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:25.130347+07:00</t>
+          <t>2026-10-27T09:46:11.757493+07:00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1820,7 +1814,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1829,7 +1823,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1000</v>
+        <v>1125</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1838,7 +1832,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1848,7 +1842,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:48.626744+07:00</t>
+          <t>2026-10-27T09:46:35.132823+07:00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1861,7 +1855,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1870,7 +1864,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>125</v>
+        <v>875</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1879,7 +1873,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1889,7 +1883,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:50.040793+07:00</t>
+          <t>2026-10-27T09:46:36.217564+07:00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1902,7 +1896,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1920,7 +1914,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1930,7 +1924,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:29.118677+07:00</t>
+          <t>2026-10-27T09:46:15.521722+07:00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1943,7 +1937,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1952,7 +1946,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1961,7 +1955,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1971,7 +1965,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:29.000677+07:00</t>
+          <t>2026-10-27T09:46:15.426762+07:00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1984,7 +1978,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1993,16 +1987,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1750</v>
+        <v>4500</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2012,7 +2006,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:46.782793+07:00</t>
+          <t>2026-10-27T09:46:33.051121+07:00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2025,7 +2019,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2034,7 +2028,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4125</v>
+        <v>6125</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2043,7 +2037,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2053,7 +2047,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:35.229124+07:00</t>
+          <t>2026-10-27T09:46:20.929818+07:00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2064,50 +2058,44 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>มุกดาหาร</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>4375</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2026-10-25 00Z</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2026-10-26T09:46:35.094387+07:00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:20.878919+07:00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: ''/''</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2116,7 +2104,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2125,7 +2113,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2135,7 +2123,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:51.537512+07:00</t>
+          <t>2026-10-27T09:46:37.701708+07:00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2148,7 +2136,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2157,16 +2145,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2500</v>
+        <v>5750</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2176,7 +2164,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:36.745870+07:00</t>
+          <t>2026-10-27T09:46:22.992594+07:00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2189,7 +2177,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2198,16 +2186,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1000</v>
+        <v>2375</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2217,7 +2205,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:48.272179+07:00</t>
+          <t>2026-10-27T09:46:34.358840+07:00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2228,91 +2216,79 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>ระยอง</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>1375</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026-10-25 00Z</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2026-10-26T09:46:44.333971+07:00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:30.937622+07:00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>ราชบุรี</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>1375</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-10-25 00Z</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-10-26T09:46:41.760712+07:00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:28.114780+07:00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2321,16 +2297,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3375</v>
+        <v>5875</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2340,7 +2316,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:35.858061+07:00</t>
+          <t>2026-10-27T09:46:21.019607+07:00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2353,7 +2329,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2362,16 +2338,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2381,7 +2357,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:42.390127+07:00</t>
+          <t>2026-10-27T09:46:29.360116+07:00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2394,7 +2370,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2403,7 +2379,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2412,7 +2388,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2422,7 +2398,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:26.860462+07:00</t>
+          <t>2026-10-27T09:46:13.191655+07:00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2435,7 +2411,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2444,7 +2420,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>375</v>
+        <v>625</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2453,7 +2429,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2463,7 +2439,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:25.331124+07:00</t>
+          <t>2026-10-27T09:46:11.853911+07:00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2476,7 +2452,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2485,16 +2461,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>875</v>
+        <v>2125</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2504,7 +2480,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:38.028230+07:00</t>
+          <t>2026-10-27T09:46:24.456509+07:00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2517,7 +2493,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2526,7 +2502,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4125</v>
+        <v>4875</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2535,7 +2511,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2545,7 +2521,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:33.974623+07:00</t>
+          <t>2026-10-27T09:46:19.534424+07:00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2558,7 +2534,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2567,16 +2543,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>750</v>
+        <v>2125</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2586,7 +2562,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:46.662057+07:00</t>
+          <t>2026-10-27T09:46:32.853057+07:00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2599,7 +2575,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2608,7 +2584,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>875</v>
+        <v>1375</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2627,7 +2603,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:51.434932+07:00</t>
+          <t>2026-10-27T09:46:37.142253+07:00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2640,7 +2616,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2649,16 +2625,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>875</v>
+        <v>3750</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2668,7 +2644,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:20.225870+07:00</t>
+          <t>2026-10-27T09:46:07.890399+07:00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2681,7 +2657,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2690,7 +2666,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1000</v>
+        <v>1750</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2699,7 +2675,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2709,7 +2685,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:42.921439+07:00</t>
+          <t>2026-10-27T09:46:29.398513+07:00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2722,7 +2698,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2731,16 +2707,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1375</v>
+        <v>2125</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2750,7 +2726,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:22.504978+07:00</t>
+          <t>2026-10-27T09:46:10.088057+07:00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2763,7 +2739,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2772,7 +2748,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>125</v>
+        <v>1000</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2781,7 +2757,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2791,7 +2767,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:41.514431+07:00</t>
+          <t>2026-10-27T09:46:28.053141+07:00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2804,7 +2780,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2813,16 +2789,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>625</v>
+        <v>2375</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2832,7 +2808,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:45.349259+07:00</t>
+          <t>2026-10-27T09:46:31.149775+07:00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2845,7 +2821,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2854,16 +2830,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>500</v>
+        <v>2250</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2873,7 +2849,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:40.913739+07:00</t>
+          <t>2026-10-27T09:46:27.021316+07:00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2886,7 +2862,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2895,16 +2871,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>750</v>
+        <v>2125</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2914,7 +2890,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:42.317503+07:00</t>
+          <t>2026-10-27T09:46:28.502186+07:00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2927,7 +2903,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2936,7 +2912,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>625</v>
+        <v>1500</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2945,7 +2921,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2955,7 +2931,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:48.399995+07:00</t>
+          <t>2026-10-27T09:46:34.936261+07:00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2968,7 +2944,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2977,16 +2953,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1000</v>
+        <v>2125</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2996,7 +2972,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:38.248612+07:00</t>
+          <t>2026-10-27T09:46:24.657807+07:00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3009,7 +2985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3027,7 +3003,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3037,7 +3013,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:28.713600+07:00</t>
+          <t>2026-10-27T09:46:14.476381+07:00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3050,7 +3026,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3059,16 +3035,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1625</v>
+        <v>3250</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3078,7 +3054,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:32.073613+07:00</t>
+          <t>2026-10-27T09:46:17.915401+07:00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3091,7 +3067,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3100,7 +3076,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2750</v>
+        <v>3375</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3109,7 +3085,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3119,7 +3095,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:33.685699+07:00</t>
+          <t>2026-10-27T09:46:19.497062+07:00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3130,85 +3106,85 @@
       <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>อำนาจเจริญ</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v>4250</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2026-10-25 00Z</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2026-10-26T09:46:36.589514+07:00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr"/>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:22.916195+07:00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: ''/''</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>อุดรธานี</t>
         </is>
       </c>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T09:46:32.887754+07:00</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
+      <c r="C67" t="n">
+        <v>3125</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:19.280511+07:00</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3226,7 +3202,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3236,7 +3212,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:27.110216+07:00</t>
+          <t>2026-10-27T09:46:13.255186+07:00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3249,7 +3225,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3258,16 +3234,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>625</v>
+        <v>2250</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3277,7 +3253,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:39.452771+07:00</t>
+          <t>2026-10-27T09:46:25.734827+07:00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3288,50 +3264,44 @@
       <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>อุบลราชธานี</t>
         </is>
       </c>
-      <c r="C70" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2026-10-25 00Z</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>2026-10-26T09:46:30.709934+07:00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:16.964840+07:00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_407501.png</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3340,16 +3310,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>375</v>
+        <v>2000</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3359,7 +3329,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:40.098932+07:00</t>
+          <t>2026-10-27T09:46:26.620359+07:00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3372,7 +3342,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3381,7 +3351,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>625</v>
+        <v>375</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3390,7 +3360,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3400,7 +3370,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:22.662026+07:00</t>
+          <t>2026-10-27T09:46:10.271916+07:00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3413,7 +3383,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3422,7 +3392,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3431,7 +3401,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3441,7 +3411,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:22.633095+07:00</t>
+          <t>2026-10-27T09:46:10.145553+07:00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3454,7 +3424,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3463,7 +3433,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1000</v>
+        <v>1125</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3472,7 +3442,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3482,7 +3452,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:46.878745+07:00</t>
+          <t>2026-10-27T09:46:33.453385+07:00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3495,7 +3465,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3504,16 +3474,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>125</v>
+        <v>2500</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3523,7 +3493,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:30.667974+07:00</t>
+          <t>2026-10-27T09:46:16.054765+07:00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3536,7 +3506,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3545,16 +3515,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>875</v>
+        <v>2375</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3564,7 +3534,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:32.544779+07:00</t>
+          <t>2026-10-27T09:46:18.196666+07:00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3577,7 +3547,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3586,16 +3556,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>250</v>
+        <v>2375</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3605,7 +3575,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:27.106293+07:00</t>
+          <t>2026-10-27T09:46:13.206586+07:00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3618,7 +3588,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3627,7 +3597,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>125</v>
+        <v>750</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3636,7 +3606,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-25 00Z</t>
+          <t>2026-10-26 00Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3646,7 +3616,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-26T09:46:24.906797+07:00</t>
+          <t>2026-10-27T09:46:11.586915+07:00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3747,7 +3717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I540"/>
+  <dimension ref="A1:I617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -25865,8 +25835,3123 @@
       </c>
       <c r="I540" t="inlineStr"/>
     </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>กระบี่</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:35.839954+07:00</t>
+        </is>
+      </c>
+      <c r="H541" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_566202.png</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>4375</v>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:07.889214+07:00</t>
+        </is>
+      </c>
+      <c r="H542" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_455301.png</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:29.522118+07:00</t>
+        </is>
+      </c>
+      <c r="H543" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_450201.png</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>กาฬสินธุ์</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>6125</v>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:20.895111+07:00</t>
+        </is>
+      </c>
+      <c r="H544" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_388401.png</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>กำแพงเพชร</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:15.485526+07:00</t>
+        </is>
+      </c>
+      <c r="H545" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_380201.png</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>ขอนแก่น</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>4875</v>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:17.032232+07:00</t>
+        </is>
+      </c>
+      <c r="H546" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_381201.png</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>จันทบุรี</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:32.166301+07:00</t>
+        </is>
+      </c>
+      <c r="H547" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_480201.png</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>ฉะเชิงเทรา</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>2875</v>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:29.798382+07:00</t>
+        </is>
+      </c>
+      <c r="H548" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_423301.png</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>ชลบุรี</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:30.854625+07:00</t>
+        </is>
+      </c>
+      <c r="H549" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_459201.png</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>ชัยนาท</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:26.563720+07:00</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_402301.png</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>ชัยภูมิ</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>5125</v>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:22.970668+07:00</t>
+        </is>
+      </c>
+      <c r="H551" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_403201.png</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>5875</v>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:34.144811+07:00</t>
+        </is>
+      </c>
+      <c r="H552" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>ตรัง</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:36.460138+07:00</t>
+        </is>
+      </c>
+      <c r="H553" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_567201.png</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>ตราด</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>875</v>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:32.168967+07:00</t>
+        </is>
+      </c>
+      <c r="H554" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_501201.png</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>ตาก</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>625</v>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:13.212446+07:00</t>
+        </is>
+      </c>
+      <c r="H555" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_376201.png</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:27.992418+07:00</t>
+        </is>
+      </c>
+      <c r="H556" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_417201.png</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B557" s="3" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="C557" s="3" t="n"/>
+      <c r="D557" s="3" t="inlineStr"/>
+      <c r="E557" s="3" t="inlineStr"/>
+      <c r="F557" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G557" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:10.023452+07:00</t>
+        </is>
+      </c>
+      <c r="H557" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
+        </is>
+      </c>
+      <c r="I557" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>นครพนม</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>5375</v>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:19.275021+07:00</t>
+        </is>
+      </c>
+      <c r="H558" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_357201.png</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>นครราชสีมา</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>2875</v>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:24.469644+07:00</t>
+        </is>
+      </c>
+      <c r="H559" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_431201.png</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>นครศรีธรรมราช</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>375</v>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:35.651043+07:00</t>
+        </is>
+      </c>
+      <c r="H560" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_552201.png</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>นครสวรรค์</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:24.660480+07:00</t>
+        </is>
+      </c>
+      <c r="H561" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_400201.png</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:07.889747+07:00</t>
+        </is>
+      </c>
+      <c r="H562" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_411000.png</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>นราธิวาส</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>500</v>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:37.791540+07:00</t>
+        </is>
+      </c>
+      <c r="H563" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_583201.png</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>น่าน</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>625</v>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:11.786521+07:00</t>
+        </is>
+      </c>
+      <c r="H564" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_331201.png</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>บึงกาฬ</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>3125</v>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:17.048827+07:00</t>
+        </is>
+      </c>
+      <c r="H565" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_363201.png</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>บุรีรัมย์</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:23.010278+07:00</t>
+        </is>
+      </c>
+      <c r="H566" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_436201.png</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>ปทุมธานี</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:07.890068+07:00</t>
+        </is>
+      </c>
+      <c r="H567" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_419301.png</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>ประจวบคีรีขันธ์</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>3875</v>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:33.648167+07:00</t>
+        </is>
+      </c>
+      <c r="H568" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_500201.png</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>ปราจีนบุรี</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:31.106425+07:00</t>
+        </is>
+      </c>
+      <c r="H569" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_430201.png</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B570" s="3" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="C570" s="3" t="n"/>
+      <c r="D570" s="3" t="inlineStr"/>
+      <c r="E570" s="3" t="inlineStr"/>
+      <c r="F570" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G570" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:36.945038+07:00</t>
+        </is>
+      </c>
+      <c r="H570" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
+        </is>
+      </c>
+      <c r="I570" s="3" t="inlineStr">
+        <is>
+          <t>cannot_locate_bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>พระนครศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:26.743228+07:00</t>
+        </is>
+      </c>
+      <c r="H571" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>พะเยา</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>375</v>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:11.757493+07:00</t>
+        </is>
+      </c>
+      <c r="H572" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_310201.png</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>พังงา</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:35.132823+07:00</t>
+        </is>
+      </c>
+      <c r="H573" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_561201.png</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>พัทลุง</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>875</v>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:36.217564+07:00</t>
+        </is>
+      </c>
+      <c r="H574" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_560301.png</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>พิจิตร</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>500</v>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:15.521722+07:00</t>
+        </is>
+      </c>
+      <c r="H575" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_386301.png</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>250</v>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:15.426762+07:00</t>
+        </is>
+      </c>
+      <c r="H576" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_378201.png</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>ภูเก็ต</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:33.051121+07:00</t>
+        </is>
+      </c>
+      <c r="H577" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_564201.png</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>มหาสารคาม</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>6125</v>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:20.929818+07:00</t>
+        </is>
+      </c>
+      <c r="H578" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_387401.png</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B579" s="3" t="inlineStr">
+        <is>
+          <t>มุกดาหาร</t>
+        </is>
+      </c>
+      <c r="C579" s="3" t="n"/>
+      <c r="D579" s="3" t="inlineStr"/>
+      <c r="E579" s="3" t="inlineStr"/>
+      <c r="F579" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G579" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:20.878919+07:00</t>
+        </is>
+      </c>
+      <c r="H579" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
+        </is>
+      </c>
+      <c r="I579" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: ''/''</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>ยะลา</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>500</v>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:37.701708+07:00</t>
+        </is>
+      </c>
+      <c r="H580" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_581301.png</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>ยโสธร</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>5750</v>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:22.992594+07:00</t>
+        </is>
+      </c>
+      <c r="H581" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_406201.png</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>ระนอง</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:34.358840+07:00</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_532201.png</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B583" s="3" t="inlineStr">
+        <is>
+          <t>ระยอง</t>
+        </is>
+      </c>
+      <c r="C583" s="3" t="n"/>
+      <c r="D583" s="3" t="inlineStr"/>
+      <c r="E583" s="3" t="inlineStr"/>
+      <c r="F583" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G583" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:30.937622+07:00</t>
+        </is>
+      </c>
+      <c r="H583" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
+        </is>
+      </c>
+      <c r="I583" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B584" s="3" t="inlineStr">
+        <is>
+          <t>ราชบุรี</t>
+        </is>
+      </c>
+      <c r="C584" s="3" t="n"/>
+      <c r="D584" s="3" t="inlineStr"/>
+      <c r="E584" s="3" t="inlineStr"/>
+      <c r="F584" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G584" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:28.114780+07:00</t>
+        </is>
+      </c>
+      <c r="H584" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
+        </is>
+      </c>
+      <c r="I584" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>5875</v>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:21.019607+07:00</t>
+        </is>
+      </c>
+      <c r="H585" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_405201.png</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>ลพบุรี</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:29.360116+07:00</t>
+        </is>
+      </c>
+      <c r="H586" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_426201.png</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>ลำปาง</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>250</v>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:13.191655+07:00</t>
+        </is>
+      </c>
+      <c r="H587" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_328201.png</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>ลำพูน</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>625</v>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:11.853911+07:00</t>
+        </is>
+      </c>
+      <c r="H588" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_329201.png</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>ศรีสะเกษ</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:24.456509+07:00</t>
+        </is>
+      </c>
+      <c r="H589" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_409301.png</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>สกลนคร</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>4875</v>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:19.534424+07:00</t>
+        </is>
+      </c>
+      <c r="H590" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_356201.png</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>สงขลา</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:32.853057+07:00</t>
+        </is>
+      </c>
+      <c r="H591" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_568501.png</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>สตูล</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:37.142253+07:00</t>
+        </is>
+      </c>
+      <c r="H592" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_570201.png</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>สมุทรปราการ</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>3750</v>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:07.890399+07:00</t>
+        </is>
+      </c>
+      <c r="H593" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_429301.png</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>สมุทรสงคราม</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:29.398513+07:00</t>
+        </is>
+      </c>
+      <c r="H594" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_438201.png</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>สมุทรสาคร</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:10.088057+07:00</t>
+        </is>
+      </c>
+      <c r="H595" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_474000.png</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>สระบุรี</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:28.053141+07:00</t>
+        </is>
+      </c>
+      <c r="H596" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_418000.png</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>สระแก้ว</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:31.149775+07:00</t>
+        </is>
+      </c>
+      <c r="H597" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_440401.png</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>สิงห์บุรี</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:27.021316+07:00</t>
+        </is>
+      </c>
+      <c r="H598" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_416000.png</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:28.502186+07:00</t>
+        </is>
+      </c>
+      <c r="H599" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_425201.png</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>สุราษฎร์ธานี</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:34.936261+07:00</t>
+        </is>
+      </c>
+      <c r="H600" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_551201.png</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>สุรินทร์</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:24.657807+07:00</t>
+        </is>
+      </c>
+      <c r="H601" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_432201.png</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>สุโขทัย</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>500</v>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:14.476381+07:00</t>
+        </is>
+      </c>
+      <c r="H602" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_373201.png</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>หนองคาย</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>3250</v>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:17.915401+07:00</t>
+        </is>
+      </c>
+      <c r="H603" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_352201.png</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>หนองบัวลำภู</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>3375</v>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:19.497062+07:00</t>
+        </is>
+      </c>
+      <c r="H604" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_360201.png</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B605" s="3" t="inlineStr">
+        <is>
+          <t>อำนาจเจริญ</t>
+        </is>
+      </c>
+      <c r="C605" s="3" t="n"/>
+      <c r="D605" s="3" t="inlineStr"/>
+      <c r="E605" s="3" t="inlineStr"/>
+      <c r="F605" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G605" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:22.916195+07:00</t>
+        </is>
+      </c>
+      <c r="H605" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
+        </is>
+      </c>
+      <c r="I605" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: ''/''</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>อุดรธานี</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>3125</v>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:19.280511+07:00</t>
+        </is>
+      </c>
+      <c r="H606" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>อุตรดิตถ์</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>250</v>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:13.255186+07:00</t>
+        </is>
+      </c>
+      <c r="H607" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_351201.png</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>อุทัยธานี</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:25.734827+07:00</t>
+        </is>
+      </c>
+      <c r="H608" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_410201.png</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B609" s="3" t="inlineStr">
+        <is>
+          <t>อุบลราชธานี</t>
+        </is>
+      </c>
+      <c r="C609" s="3" t="n"/>
+      <c r="D609" s="3" t="inlineStr"/>
+      <c r="E609" s="3" t="inlineStr"/>
+      <c r="F609" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G609" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:16.964840+07:00</t>
+        </is>
+      </c>
+      <c r="H609" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_407501.png</t>
+        </is>
+      </c>
+      <c r="I609" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>อ่างทอง</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:26.620359+07:00</t>
+        </is>
+      </c>
+      <c r="H610" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_414000.png</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>เชียงราย</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>375</v>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:10.271916+07:00</t>
+        </is>
+      </c>
+      <c r="H611" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_303201.png</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>เชียงใหม่</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>375</v>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:10.145553+07:00</t>
+        </is>
+      </c>
+      <c r="H612" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_327501.png</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr"/>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>เพชรบุรี</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:33.453385+07:00</t>
+        </is>
+      </c>
+      <c r="H613" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_465201.png</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr"/>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:16.054765+07:00</t>
+        </is>
+      </c>
+      <c r="H614" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_379201.png</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr"/>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>เลย</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:18.196666+07:00</t>
+        </is>
+      </c>
+      <c r="H615" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_353201.png</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>แพร่</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:13.206586+07:00</t>
+        </is>
+      </c>
+      <c r="H616" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_330201.png</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr"/>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>แม่ฮ่องสอน</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>750</v>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>2026-10-26 00Z</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:11.586915+07:00</t>
+        </is>
+      </c>
+      <c r="H617" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_300201.png</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I540"/>
+  <autoFilter ref="A1:I617"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -26407,6 +29492,83 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H538" r:id="rId537"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H539" r:id="rId538"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H540" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H541" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H542" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H543" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H544" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H545" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H546" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H547" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H548" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H549" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H550" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H551" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H552" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H553" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H554" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H555" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H556" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H557" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H558" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H559" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H560" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H561" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H562" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H563" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H564" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H565" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H566" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H567" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H568" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H569" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H570" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H571" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H572" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H573" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H574" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H575" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H576" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H577" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H578" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H579" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H580" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H581" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H582" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H583" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H584" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H585" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H586" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H587" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H588" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H589" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H590" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H591" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H592" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H593" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H594" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H595" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H596" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H597" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H598" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H599" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H600" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H601" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H602" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H603" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H604" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H605" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H606" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H607" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H608" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H609" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H610" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H611" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H612" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H613" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H614" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H615" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H616" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H617" r:id="rId616"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26418,7 +29580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -26724,8 +29886,253 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:10.023452+07:00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:36.945038+07:00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>cannot_locate_bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>มุกดาหาร</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:20.878919+07:00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: ''/''</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>ระยอง</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:30.937622+07:00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>ราชบุรี</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:28.114780+07:00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>อำนาจเจริญ</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:22.916195+07:00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: ''/''</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>อุบลราชธานี</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:46:16.964840+07:00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_407501.png</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I8"/>
+  <autoFilter ref="A1:I15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -26734,6 +30141,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ventilation.xlsx
+++ b/data/ventilation.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ล่าสุด'!$A$1:$I$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$617</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$694</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2375</v>
+        <v>2000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:35.839954+07:00</t>
+          <t>2026-10-28T09:55:49.176291+07:00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,16 +564,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4375</v>
+        <v>2500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:07.889214+07:00</t>
+          <t>2026-10-28T09:55:16.282233+07:00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2125</v>
+        <v>2375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:29.522118+07:00</t>
+          <t>2026-10-28T09:55:42.251453+07:00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6125</v>
+        <v>5625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:20.895111+07:00</t>
+          <t>2026-10-28T09:55:31.433411+07:00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1125</v>
+        <v>1250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:15.485526+07:00</t>
+          <t>2026-10-28T09:55:25.151032+07:00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4875</v>
+        <v>3125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:17.032232+07:00</t>
+          <t>2026-10-28T09:55:27.025512+07:00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1250</v>
+        <v>875</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:32.166301+07:00</t>
+          <t>2026-10-28T09:55:44.623448+07:00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2875</v>
+        <v>2375</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:29.798382+07:00</t>
+          <t>2026-10-28T09:55:42.332895+07:00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2750</v>
+        <v>1375</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:30.854625+07:00</t>
+          <t>2026-10-28T09:55:42.524931+07:00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2375</v>
+        <v>3125</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:26.563720+07:00</t>
+          <t>2026-10-28T09:55:36.982290+07:00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5125</v>
+        <v>4375</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:22.970668+07:00</t>
+          <t>2026-10-28T09:55:33.723630+07:00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5875</v>
+        <v>5000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:34.144811+07:00</t>
+          <t>2026-10-28T09:55:46.620691+07:00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1250</v>
+        <v>625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:36.460138+07:00</t>
+          <t>2026-10-28T09:55:49.546541+07:00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>875</v>
+        <v>125</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:32.168967+07:00</t>
+          <t>2026-10-28T09:55:44.696465+07:00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>625</v>
+        <v>1000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:13.212446+07:00</t>
+          <t>2026-10-28T09:55:22.949852+07:00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1127,50 +1127,44 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>นครนายก</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2026-10-26 00Z</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-10-27T09:46:27.992418+07:00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:38.927192+07:00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_417201.png</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1188,7 +1182,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:10.023452+07:00</t>
+          <t>2026-10-28T09:55:18.356323+07:00</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1205,7 +1199,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1214,7 +1208,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5375</v>
+        <v>4875</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1223,7 +1217,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1233,7 +1227,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:19.275021+07:00</t>
+          <t>2026-10-28T09:55:29.265984+07:00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1246,7 +1240,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1255,7 +1249,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2875</v>
+        <v>2375</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1264,7 +1258,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1274,7 +1268,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:24.469644+07:00</t>
+          <t>2026-10-28T09:55:35.416811+07:00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1287,7 +1281,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1296,7 +1290,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>375</v>
+        <v>1625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1305,7 +1299,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1315,7 +1309,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:35.651043+07:00</t>
+          <t>2026-10-28T09:55:48.155398+07:00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1328,7 +1322,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1337,7 +1331,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2750</v>
+        <v>2625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1346,7 +1340,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1356,7 +1350,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:24.660480+07:00</t>
+          <t>2026-10-28T09:55:36.863298+07:00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1369,7 +1363,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1378,16 +1372,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2250</v>
+        <v>1750</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1397,7 +1391,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:07.889747+07:00</t>
+          <t>2026-10-28T09:55:16.283203+07:00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1410,7 +1404,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1419,7 +1413,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>500</v>
+        <v>125</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1428,7 +1422,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1438,7 +1432,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:37.791540+07:00</t>
+          <t>2026-10-28T09:55:51.300669+07:00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1451,7 +1445,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1460,7 +1454,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>625</v>
+        <v>125</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1469,7 +1463,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1479,7 +1473,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:11.786521+07:00</t>
+          <t>2026-10-28T09:55:20.985904+07:00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1492,7 +1486,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1501,16 +1495,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3125</v>
+        <v>1250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1520,7 +1514,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:17.048827+07:00</t>
+          <t>2026-10-28T09:55:27.037964+07:00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1533,7 +1527,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1542,7 +1536,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3000</v>
+        <v>3375</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1551,7 +1545,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1561,7 +1555,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:23.010278+07:00</t>
+          <t>2026-10-28T09:55:35.271259+07:00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1574,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1583,16 +1577,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2250</v>
+        <v>1750</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1602,7 +1596,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:07.890068+07:00</t>
+          <t>2026-10-28T09:55:16.283715+07:00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1615,7 +1609,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1624,7 +1618,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3875</v>
+        <v>2250</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1633,7 +1627,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1643,7 +1637,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:33.648167+07:00</t>
+          <t>2026-10-28T09:55:46.351499+07:00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1656,7 +1650,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1665,7 +1659,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1674,7 +1668,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1684,7 +1678,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:31.106425+07:00</t>
+          <t>2026-10-28T09:55:43.698973+07:00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1695,85 +1689,85 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>ปัตตานี</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="C31" t="n">
+        <v>500</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:49.681392+07:00</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>พระนครศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>รอตรวจสอบ</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27T09:46:36.945038+07:00</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>cannot_locate_bar</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>พระนครศรีอยุธยา</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1625</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2026-10-26 00Z</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-10-27T09:46:26.743228+07:00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:38.769609+07:00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1782,7 +1776,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1791,7 +1785,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1801,7 +1795,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:11.757493+07:00</t>
+          <t>2026-10-28T09:55:20.980259+07:00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1814,7 +1808,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1823,16 +1817,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1125</v>
+        <v>3125</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1842,7 +1836,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:35.132823+07:00</t>
+          <t>2026-10-28T09:55:47.974517+07:00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1855,7 +1849,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1864,7 +1858,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>875</v>
+        <v>1125</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1873,7 +1867,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1883,7 +1877,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:36.217564+07:00</t>
+          <t>2026-10-28T09:55:49.396925+07:00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1896,7 +1890,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1905,7 +1899,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>500</v>
+        <v>875</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1914,7 +1908,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1924,7 +1918,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:15.521722+07:00</t>
+          <t>2026-10-28T09:55:25.171194+07:00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1937,7 +1931,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1946,7 +1940,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>250</v>
+        <v>875</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1955,7 +1949,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1965,7 +1959,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:15.426762+07:00</t>
+          <t>2026-10-28T09:55:24.969707+07:00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1978,7 +1972,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1987,16 +1981,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2006,7 +2000,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:33.051121+07:00</t>
+          <t>2026-10-28T09:55:46.106157+07:00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2019,7 +2013,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2028,16 +2022,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6125</v>
+        <v>3875</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2047,7 +2041,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:20.929818+07:00</t>
+          <t>2026-10-28T09:55:32.733197+07:00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2060,7 +2054,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2078,7 +2072,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:20.878919+07:00</t>
+          <t>2026-10-28T09:55:31.289535+07:00</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2095,7 +2089,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2104,7 +2098,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2113,7 +2107,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2123,7 +2117,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:37.701708+07:00</t>
+          <t>2026-10-28T09:55:51.299321+07:00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2136,7 +2130,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2145,7 +2139,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5750</v>
+        <v>7125</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2154,7 +2148,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2164,7 +2158,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:22.992594+07:00</t>
+          <t>2026-10-28T09:55:34.186317+07:00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2177,7 +2171,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2186,16 +2180,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2375</v>
+        <v>1375</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2205,7 +2199,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:34.358840+07:00</t>
+          <t>2026-10-28T09:55:47.672683+07:00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2216,120 +2210,126 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>ระยอง</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="C44" t="n">
+        <v>750</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:42.947050+07:00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ราชบุรี</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:40.747002+07:00</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>รอตรวจสอบ</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27T09:46:30.937622+07:00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>ราชบุรี</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27T09:46:28.114780+07:00</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>ร้อยเอ็ด</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>5875</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-10-26 00Z</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-10-27T09:46:21.019607+07:00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:32.762451+07:00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_405201.png</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: ''/''</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2338,16 +2338,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:29.360116+07:00</t>
+          <t>2026-10-28T09:55:40.805749+07:00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2368,50 +2368,44 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>ลำปาง</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>250</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2026-10-26 00Z</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-10-27T09:46:13.191655+07:00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:22.933807+07:00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_328201.png</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2420,7 +2414,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>625</v>
+        <v>1500</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2429,7 +2423,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2439,7 +2433,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:11.853911+07:00</t>
+          <t>2026-10-28T09:55:21.101483+07:00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2452,7 +2446,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2461,7 +2455,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2125</v>
+        <v>2875</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2470,7 +2464,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2480,7 +2474,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:24.456509+07:00</t>
+          <t>2026-10-28T09:55:35.333157+07:00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2493,7 +2487,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2502,7 +2496,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4875</v>
+        <v>4375</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2511,7 +2505,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2521,7 +2515,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:19.534424+07:00</t>
+          <t>2026-10-28T09:55:31.278420+07:00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2534,7 +2528,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2543,16 +2537,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2125</v>
+        <v>1125</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2562,7 +2556,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:32.853057+07:00</t>
+          <t>2026-10-28T09:55:45.148566+07:00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2575,7 +2569,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2584,7 +2578,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1375</v>
+        <v>500</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2593,7 +2587,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2603,7 +2597,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:37.142253+07:00</t>
+          <t>2026-10-28T09:55:51.279556+07:00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2616,7 +2610,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2625,7 +2619,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3750</v>
+        <v>2250</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2634,7 +2628,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2644,7 +2638,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:07.890399+07:00</t>
+          <t>2026-10-28T09:55:16.284260+07:00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2657,7 +2651,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2666,7 +2660,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1750</v>
+        <v>625</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2675,7 +2669,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2685,7 +2679,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:29.398513+07:00</t>
+          <t>2026-10-28T09:55:41.037706+07:00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2698,7 +2692,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2707,16 +2701,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2125</v>
+        <v>875</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2726,7 +2720,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:10.088057+07:00</t>
+          <t>2026-10-28T09:55:18.450986+07:00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2739,7 +2733,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2748,7 +2742,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1000</v>
+        <v>1250</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2757,7 +2751,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2767,7 +2761,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:28.053141+07:00</t>
+          <t>2026-10-28T09:55:39.502362+07:00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2780,7 +2774,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2789,7 +2783,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2375</v>
+        <v>2500</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2798,7 +2792,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2808,7 +2802,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:31.149775+07:00</t>
+          <t>2026-10-28T09:55:44.611323+07:00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2821,7 +2815,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2830,7 +2824,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2250</v>
+        <v>3625</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2839,7 +2833,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2849,7 +2843,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:27.021316+07:00</t>
+          <t>2026-10-28T09:55:38.909296+07:00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2862,7 +2856,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2871,7 +2865,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2125</v>
+        <v>2750</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2880,7 +2874,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2890,7 +2884,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:28.502186+07:00</t>
+          <t>2026-10-28T09:55:40.770098+07:00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2903,7 +2897,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2912,16 +2906,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2931,7 +2925,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:34.936261+07:00</t>
+          <t>2026-10-28T09:55:47.800428+07:00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2944,7 +2938,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2953,7 +2947,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2125</v>
+        <v>3250</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2962,7 +2956,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2972,7 +2966,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:24.657807+07:00</t>
+          <t>2026-10-28T09:55:36.434884+07:00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -2985,7 +2979,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2994,7 +2988,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3003,7 +2997,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3013,7 +3007,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:14.476381+07:00</t>
+          <t>2026-10-28T09:55:24.909871+07:00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3026,7 +3020,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3035,7 +3029,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3250</v>
+        <v>2250</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3044,7 +3038,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3054,7 +3048,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:17.915401+07:00</t>
+          <t>2026-10-28T09:55:29.203886+07:00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3067,7 +3061,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3076,7 +3070,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3375</v>
+        <v>2125</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3085,7 +3079,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3095,7 +3089,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:19.497062+07:00</t>
+          <t>2026-10-28T09:55:31.115856+07:00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3108,7 +3102,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3126,7 +3120,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:22.916195+07:00</t>
+          <t>2026-10-28T09:55:33.619001+07:00</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -3143,7 +3137,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3152,7 +3146,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3125</v>
+        <v>2375</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3161,7 +3155,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3171,7 +3165,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:19.280511+07:00</t>
+          <t>2026-10-28T09:55:29.379674+07:00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3184,7 +3178,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3193,7 +3187,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>250</v>
+        <v>625</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3202,7 +3196,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3212,7 +3206,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:13.255186+07:00</t>
+          <t>2026-10-28T09:55:22.967138+07:00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3225,7 +3219,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3234,7 +3228,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2250</v>
+        <v>2875</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3243,7 +3237,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3253,7 +3247,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:25.734827+07:00</t>
+          <t>2026-10-28T09:55:36.953286+07:00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3264,44 +3258,50 @@
       <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>อุบลราชธานี</t>
         </is>
       </c>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="inlineStr"/>
-      <c r="E70" s="3" t="inlineStr"/>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27T09:46:16.964840+07:00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="C70" t="n">
+        <v>2875</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:26.665977+07:00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_407501.png</t>
         </is>
       </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2000</v>
+        <v>2375</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:26.620359+07:00</t>
+          <t>2026-10-28T09:55:38.060471+07:00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3342,7 +3342,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:10.271916+07:00</t>
+          <t>2026-10-28T09:55:18.839641+07:00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3392,16 +3392,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>375</v>
+        <v>2000</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:10.145553+07:00</t>
+          <t>2026-10-28T09:55:18.585938+07:00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:33.453385+07:00</t>
+          <t>2026-10-28T09:55:46.276428+07:00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:16.054765+07:00</t>
+          <t>2026-10-28T09:55:26.620284+07:00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3504,50 +3504,44 @@
       <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>เลย</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>2375</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>2026-10-26 00Z</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2026-10-27T09:46:18.196666+07:00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="C76" s="3" t="n"/>
+      <c r="D76" s="3" t="inlineStr"/>
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:29.212437+07:00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_353201.png</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3556,7 +3550,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2375</v>
+        <v>2250</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3565,7 +3559,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3575,7 +3569,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:13.206586+07:00</t>
+          <t>2026-10-28T09:55:22.937134+07:00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3588,7 +3582,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3597,16 +3591,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>750</v>
+        <v>3250</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-26 00Z</t>
+          <t>2026-10-27 00Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3616,7 +3610,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-27T09:46:11.586915+07:00</t>
+          <t>2026-10-28T09:55:20.830985+07:00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3717,7 +3711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I617"/>
+  <dimension ref="A1:I694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -28950,8 +28944,3117 @@
       </c>
       <c r="I617" t="inlineStr"/>
     </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>กระบี่</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:49.176291+07:00</t>
+        </is>
+      </c>
+      <c r="H618" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_566202.png</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr"/>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:16.282233+07:00</t>
+        </is>
+      </c>
+      <c r="H619" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_455301.png</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:42.251453+07:00</t>
+        </is>
+      </c>
+      <c r="H620" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_450201.png</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>กาฬสินธุ์</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>5625</v>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:31.433411+07:00</t>
+        </is>
+      </c>
+      <c r="H621" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_388401.png</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr"/>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>กำแพงเพชร</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:25.151032+07:00</t>
+        </is>
+      </c>
+      <c r="H622" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_380201.png</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr"/>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>ขอนแก่น</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>3125</v>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:27.025512+07:00</t>
+        </is>
+      </c>
+      <c r="H623" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_381201.png</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>จันทบุรี</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>875</v>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:44.623448+07:00</t>
+        </is>
+      </c>
+      <c r="H624" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_480201.png</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>ฉะเชิงเทรา</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:42.332895+07:00</t>
+        </is>
+      </c>
+      <c r="H625" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_423301.png</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>ชลบุรี</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:42.524931+07:00</t>
+        </is>
+      </c>
+      <c r="H626" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_459201.png</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>ชัยนาท</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>3125</v>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:36.982290+07:00</t>
+        </is>
+      </c>
+      <c r="H627" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_402301.png</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>ชัยภูมิ</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>4375</v>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:33.723630+07:00</t>
+        </is>
+      </c>
+      <c r="H628" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_403201.png</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:46.620691+07:00</t>
+        </is>
+      </c>
+      <c r="H629" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>ตรัง</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>625</v>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:49.546541+07:00</t>
+        </is>
+      </c>
+      <c r="H630" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_567201.png</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>ตราด</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>125</v>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:44.696465+07:00</t>
+        </is>
+      </c>
+      <c r="H631" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_501201.png</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr"/>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>ตาก</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:22.949852+07:00</t>
+        </is>
+      </c>
+      <c r="H632" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_376201.png</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B633" s="3" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="C633" s="3" t="n"/>
+      <c r="D633" s="3" t="inlineStr"/>
+      <c r="E633" s="3" t="inlineStr"/>
+      <c r="F633" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G633" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:38.927192+07:00</t>
+        </is>
+      </c>
+      <c r="H633" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_417201.png</t>
+        </is>
+      </c>
+      <c r="I633" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B634" s="3" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="C634" s="3" t="n"/>
+      <c r="D634" s="3" t="inlineStr"/>
+      <c r="E634" s="3" t="inlineStr"/>
+      <c r="F634" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G634" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:18.356323+07:00</t>
+        </is>
+      </c>
+      <c r="H634" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
+        </is>
+      </c>
+      <c r="I634" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>นครพนม</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>4875</v>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:29.265984+07:00</t>
+        </is>
+      </c>
+      <c r="H635" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_357201.png</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>นครราชสีมา</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:35.416811+07:00</t>
+        </is>
+      </c>
+      <c r="H636" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_431201.png</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>นครศรีธรรมราช</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:48.155398+07:00</t>
+        </is>
+      </c>
+      <c r="H637" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_552201.png</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>นครสวรรค์</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>2625</v>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:36.863298+07:00</t>
+        </is>
+      </c>
+      <c r="H638" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_400201.png</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:16.283203+07:00</t>
+        </is>
+      </c>
+      <c r="H639" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_411000.png</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>นราธิวาส</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>125</v>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:51.300669+07:00</t>
+        </is>
+      </c>
+      <c r="H640" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_583201.png</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>น่าน</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>125</v>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:20.985904+07:00</t>
+        </is>
+      </c>
+      <c r="H641" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_331201.png</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>บึงกาฬ</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:27.037964+07:00</t>
+        </is>
+      </c>
+      <c r="H642" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_363201.png</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>บุรีรัมย์</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>3375</v>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:35.271259+07:00</t>
+        </is>
+      </c>
+      <c r="H643" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_436201.png</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>ปทุมธานี</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:16.283715+07:00</t>
+        </is>
+      </c>
+      <c r="H644" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_419301.png</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>ประจวบคีรีขันธ์</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:46.351499+07:00</t>
+        </is>
+      </c>
+      <c r="H645" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_500201.png</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>ปราจีนบุรี</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:43.698973+07:00</t>
+        </is>
+      </c>
+      <c r="H646" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_430201.png</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>500</v>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:49.681392+07:00</t>
+        </is>
+      </c>
+      <c r="H647" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B648" s="3" t="inlineStr">
+        <is>
+          <t>พระนครศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="C648" s="3" t="n"/>
+      <c r="D648" s="3" t="inlineStr"/>
+      <c r="E648" s="3" t="inlineStr"/>
+      <c r="F648" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G648" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:38.769609+07:00</t>
+        </is>
+      </c>
+      <c r="H648" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
+        </is>
+      </c>
+      <c r="I648" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>พะเยา</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>250</v>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:20.980259+07:00</t>
+        </is>
+      </c>
+      <c r="H649" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_310201.png</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>พังงา</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>3125</v>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:47.974517+07:00</t>
+        </is>
+      </c>
+      <c r="H650" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_561201.png</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>พัทลุง</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:49.396925+07:00</t>
+        </is>
+      </c>
+      <c r="H651" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_560301.png</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>พิจิตร</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>875</v>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:25.171194+07:00</t>
+        </is>
+      </c>
+      <c r="H652" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_386301.png</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>875</v>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:24.969707+07:00</t>
+        </is>
+      </c>
+      <c r="H653" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_378201.png</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>ภูเก็ต</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:46.106157+07:00</t>
+        </is>
+      </c>
+      <c r="H654" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_564201.png</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>มหาสารคาม</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>3875</v>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:32.733197+07:00</t>
+        </is>
+      </c>
+      <c r="H655" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_387401.png</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B656" s="3" t="inlineStr">
+        <is>
+          <t>มุกดาหาร</t>
+        </is>
+      </c>
+      <c r="C656" s="3" t="n"/>
+      <c r="D656" s="3" t="inlineStr"/>
+      <c r="E656" s="3" t="inlineStr"/>
+      <c r="F656" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G656" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:31.289535+07:00</t>
+        </is>
+      </c>
+      <c r="H656" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
+        </is>
+      </c>
+      <c r="I656" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: ''/''</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>ยะลา</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>250</v>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:51.299321+07:00</t>
+        </is>
+      </c>
+      <c r="H657" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_581301.png</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>ยโสธร</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>7125</v>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:34.186317+07:00</t>
+        </is>
+      </c>
+      <c r="H658" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_406201.png</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>ระนอง</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:47.672683+07:00</t>
+        </is>
+      </c>
+      <c r="H659" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_532201.png</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>ระยอง</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>750</v>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:42.947050+07:00</t>
+        </is>
+      </c>
+      <c r="H660" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>ราชบุรี</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:40.747002+07:00</t>
+        </is>
+      </c>
+      <c r="H661" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B662" s="3" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="C662" s="3" t="n"/>
+      <c r="D662" s="3" t="inlineStr"/>
+      <c r="E662" s="3" t="inlineStr"/>
+      <c r="F662" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G662" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:32.762451+07:00</t>
+        </is>
+      </c>
+      <c r="H662" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_405201.png</t>
+        </is>
+      </c>
+      <c r="I662" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: ''/''</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>ลพบุรี</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:40.805749+07:00</t>
+        </is>
+      </c>
+      <c r="H663" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_426201.png</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B664" s="3" t="inlineStr">
+        <is>
+          <t>ลำปาง</t>
+        </is>
+      </c>
+      <c r="C664" s="3" t="n"/>
+      <c r="D664" s="3" t="inlineStr"/>
+      <c r="E664" s="3" t="inlineStr"/>
+      <c r="F664" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G664" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:22.933807+07:00</t>
+        </is>
+      </c>
+      <c r="H664" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_328201.png</t>
+        </is>
+      </c>
+      <c r="I664" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>ลำพูน</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:21.101483+07:00</t>
+        </is>
+      </c>
+      <c r="H665" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_329201.png</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>ศรีสะเกษ</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>2875</v>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:35.333157+07:00</t>
+        </is>
+      </c>
+      <c r="H666" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_409301.png</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>สกลนคร</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>4375</v>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:31.278420+07:00</t>
+        </is>
+      </c>
+      <c r="H667" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_356201.png</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>สงขลา</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:45.148566+07:00</t>
+        </is>
+      </c>
+      <c r="H668" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_568501.png</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>สตูล</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>500</v>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:51.279556+07:00</t>
+        </is>
+      </c>
+      <c r="H669" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_570201.png</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>สมุทรปราการ</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:16.284260+07:00</t>
+        </is>
+      </c>
+      <c r="H670" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_429301.png</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>สมุทรสงคราม</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>625</v>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:41.037706+07:00</t>
+        </is>
+      </c>
+      <c r="H671" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_438201.png</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>สมุทรสาคร</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>875</v>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:18.450986+07:00</t>
+        </is>
+      </c>
+      <c r="H672" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_474000.png</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>สระบุรี</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:39.502362+07:00</t>
+        </is>
+      </c>
+      <c r="H673" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_418000.png</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>สระแก้ว</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:44.611323+07:00</t>
+        </is>
+      </c>
+      <c r="H674" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_440401.png</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr"/>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>สิงห์บุรี</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>3625</v>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:38.909296+07:00</t>
+        </is>
+      </c>
+      <c r="H675" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_416000.png</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr"/>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:40.770098+07:00</t>
+        </is>
+      </c>
+      <c r="H676" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_425201.png</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr"/>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>สุราษฎร์ธานี</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:47.800428+07:00</t>
+        </is>
+      </c>
+      <c r="H677" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_551201.png</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr"/>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>สุรินทร์</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>3250</v>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:36.434884+07:00</t>
+        </is>
+      </c>
+      <c r="H678" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_432201.png</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr"/>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>สุโขทัย</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>750</v>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:24.909871+07:00</t>
+        </is>
+      </c>
+      <c r="H679" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_373201.png</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr"/>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>หนองคาย</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:29.203886+07:00</t>
+        </is>
+      </c>
+      <c r="H680" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_352201.png</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr"/>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>หนองบัวลำภู</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:31.115856+07:00</t>
+        </is>
+      </c>
+      <c r="H681" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_360201.png</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B682" s="3" t="inlineStr">
+        <is>
+          <t>อำนาจเจริญ</t>
+        </is>
+      </c>
+      <c r="C682" s="3" t="n"/>
+      <c r="D682" s="3" t="inlineStr"/>
+      <c r="E682" s="3" t="inlineStr"/>
+      <c r="F682" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G682" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:33.619001+07:00</t>
+        </is>
+      </c>
+      <c r="H682" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
+        </is>
+      </c>
+      <c r="I682" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: ''/''</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>อุดรธานี</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:29.379674+07:00</t>
+        </is>
+      </c>
+      <c r="H683" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr"/>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>อุตรดิตถ์</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>625</v>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:22.967138+07:00</t>
+        </is>
+      </c>
+      <c r="H684" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_351201.png</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr"/>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>อุทัยธานี</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>2875</v>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:36.953286+07:00</t>
+        </is>
+      </c>
+      <c r="H685" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_410201.png</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr"/>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>อุบลราชธานี</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>2875</v>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:26.665977+07:00</t>
+        </is>
+      </c>
+      <c r="H686" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_407501.png</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr"/>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>อ่างทอง</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:38.060471+07:00</t>
+        </is>
+      </c>
+      <c r="H687" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_414000.png</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr"/>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>เชียงราย</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>375</v>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:18.839641+07:00</t>
+        </is>
+      </c>
+      <c r="H688" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_303201.png</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr"/>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>เชียงใหม่</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:18.585938+07:00</t>
+        </is>
+      </c>
+      <c r="H689" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_327501.png</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr"/>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>เพชรบุรี</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:46.276428+07:00</t>
+        </is>
+      </c>
+      <c r="H690" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_465201.png</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr"/>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:26.620284+07:00</t>
+        </is>
+      </c>
+      <c r="H691" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_379201.png</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr"/>
+    </row>
+    <row r="692">
+      <c r="A692" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B692" s="3" t="inlineStr">
+        <is>
+          <t>เลย</t>
+        </is>
+      </c>
+      <c r="C692" s="3" t="n"/>
+      <c r="D692" s="3" t="inlineStr"/>
+      <c r="E692" s="3" t="inlineStr"/>
+      <c r="F692" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G692" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:29.212437+07:00</t>
+        </is>
+      </c>
+      <c r="H692" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_353201.png</t>
+        </is>
+      </c>
+      <c r="I692" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>แพร่</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:22.937134+07:00</t>
+        </is>
+      </c>
+      <c r="H693" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_330201.png</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr"/>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>แม่ฮ่องสอน</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>3250</v>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>2026-10-27 00Z</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:20.830985+07:00</t>
+        </is>
+      </c>
+      <c r="H694" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_300201.png</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I617"/>
+  <autoFilter ref="A1:I694"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -29569,6 +32672,83 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H615" r:id="rId614"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H616" r:id="rId615"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H617" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H618" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H619" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H620" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H621" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H622" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H623" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H624" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H625" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H626" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H627" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H628" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H629" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H630" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H631" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H632" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H633" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H634" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H635" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H636" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H637" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H638" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H639" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H640" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H641" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H642" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H643" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H644" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H645" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H646" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H647" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H648" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H649" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H650" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H651" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H652" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H653" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H654" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H655" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H656" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H657" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H658" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H659" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H660" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H661" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H662" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H663" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H664" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H665" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H666" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H667" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H668" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H669" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H670" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H671" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H672" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H673" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H674" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H675" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H676" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H677" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H678" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H679" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H680" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H681" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H682" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H683" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H684" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H685" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H686" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H687" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H688" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H689" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H690" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H691" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H692" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H693" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H694" r:id="rId693"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29580,7 +32760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -30131,8 +33311,288 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:38.927192+07:00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_417201.png</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:18.356323+07:00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>พระนครศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:38.769609+07:00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>มุกดาหาร</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:31.289535+07:00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: ''/''</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:32.762451+07:00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_405201.png</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: ''/''</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>ลำปาง</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:22.933807+07:00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_328201.png</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>อำนาจเจริญ</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:33.619001+07:00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: ''/''</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>เลย</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:55:29.212437+07:00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_353201.png</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I15"/>
+  <autoFilter ref="A1:I23"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -30148,6 +33608,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ventilation.xlsx
+++ b/data/ventilation.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ล่าสุด'!$A$1:$I$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$694</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$771</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2000</v>
+        <v>3875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:49.176291+07:00</t>
+          <t>2026-10-29T09:57:20.603317+07:00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,16 +564,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:16.282233+07:00</t>
+          <t>2026-10-29T09:56:50.140442+07:00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2375</v>
+        <v>750</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:42.251453+07:00</t>
+          <t>2026-10-29T09:57:14.123964+07:00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5625</v>
+        <v>2125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:31.433411+07:00</t>
+          <t>2026-10-29T09:57:05.003952+07:00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:25.151032+07:00</t>
+          <t>2026-10-29T09:56:59.509215+07:00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3125</v>
+        <v>2250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:27.025512+07:00</t>
+          <t>2026-10-29T09:57:01.439891+07:00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>875</v>
+        <v>125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:44.623448+07:00</t>
+          <t>2026-10-29T09:57:16.320664+07:00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -810,16 +810,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2375</v>
+        <v>1125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:42.332895+07:00</t>
+          <t>2026-10-29T09:57:14.647241+07:00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1375</v>
+        <v>375</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:42.524931+07:00</t>
+          <t>2026-10-29T09:57:14.854948+07:00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -892,16 +892,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3125</v>
+        <v>1750</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:36.982290+07:00</t>
+          <t>2026-10-29T09:57:10.193389+07:00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -933,16 +933,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4375</v>
+        <v>3000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:33.723630+07:00</t>
+          <t>2026-10-29T09:57:06.948290+07:00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5000</v>
+        <v>2625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:46.620691+07:00</t>
+          <t>2026-10-29T09:57:18.545104+07:00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>625</v>
+        <v>2250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:49.546541+07:00</t>
+          <t>2026-10-29T09:57:21.419650+07:00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:44.696465+07:00</t>
+          <t>2026-10-29T09:57:16.992628+07:00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:22.949852+07:00</t>
+          <t>2026-10-29T09:56:57.018460+07:00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1127,79 +1127,91 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>นครนายก</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28T09:55:38.927192+07:00</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="C17" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:11.886977+07:00</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_417201.png</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>นครปฐม</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28T09:55:18.356323+07:00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="C18" t="n">
+        <v>875</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:53.047382+07:00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1208,16 +1220,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4875</v>
+        <v>2750</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1227,7 +1239,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:29.265984+07:00</t>
+          <t>2026-10-29T09:57:03.052347+07:00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1249,16 +1261,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2375</v>
+        <v>1500</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1268,7 +1280,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:35.416811+07:00</t>
+          <t>2026-10-29T09:57:08.423096+07:00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1281,7 +1293,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1290,7 +1302,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1625</v>
+        <v>875</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1299,7 +1311,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1309,7 +1321,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:48.155398+07:00</t>
+          <t>2026-10-29T09:57:20.031255+07:00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1322,7 +1334,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1331,16 +1343,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2625</v>
+        <v>1375</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1350,7 +1362,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:36.863298+07:00</t>
+          <t>2026-10-29T09:57:09.183352+07:00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1363,7 +1375,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1372,7 +1384,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1750</v>
+        <v>500</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1381,7 +1393,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1391,7 +1403,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:16.283203+07:00</t>
+          <t>2026-10-29T09:56:50.141319+07:00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1404,7 +1416,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1413,7 +1425,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>125</v>
+        <v>375</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1422,7 +1434,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1432,7 +1444,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:51.300669+07:00</t>
+          <t>2026-10-29T09:57:22.916853+07:00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1445,7 +1457,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1463,7 +1475,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1473,7 +1485,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:20.985904+07:00</t>
+          <t>2026-10-29T09:56:55.061063+07:00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1486,7 +1498,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1495,7 +1507,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1504,7 +1516,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1514,7 +1526,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:27.037964+07:00</t>
+          <t>2026-10-29T09:57:01.456730+07:00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1527,7 +1539,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1536,7 +1548,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3375</v>
+        <v>2000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1545,7 +1557,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1555,7 +1567,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:35.271259+07:00</t>
+          <t>2026-10-29T09:57:07.705693+07:00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1568,7 +1580,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1577,7 +1589,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1750</v>
+        <v>500</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1586,7 +1598,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1596,7 +1608,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:16.283715+07:00</t>
+          <t>2026-10-29T09:56:50.142585+07:00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1609,7 +1621,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1618,7 +1630,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2250</v>
+        <v>3125</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1627,7 +1639,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1637,7 +1649,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:46.351499+07:00</t>
+          <t>2026-10-29T09:57:18.464571+07:00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1650,7 +1662,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1659,7 +1671,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1750</v>
+        <v>125</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1668,7 +1680,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1678,7 +1690,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:43.698973+07:00</t>
+          <t>2026-10-29T09:57:15.592210+07:00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1691,7 +1703,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1700,7 +1712,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1709,7 +1721,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1719,7 +1731,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:49.681392+07:00</t>
+          <t>2026-10-29T09:57:21.514807+07:00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1732,7 +1744,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1750,7 +1762,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:38.769609+07:00</t>
+          <t>2026-10-29T09:57:11.266071+07:00</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1767,7 +1779,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1776,7 +1788,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1785,7 +1797,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1795,7 +1807,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:20.980259+07:00</t>
+          <t>2026-10-29T09:56:55.051761+07:00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1808,7 +1820,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1817,16 +1829,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3125</v>
+        <v>4625</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1836,7 +1848,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:47.974517+07:00</t>
+          <t>2026-10-29T09:57:19.936957+07:00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1849,7 +1861,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1858,7 +1870,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1125</v>
+        <v>375</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1867,7 +1879,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1877,7 +1889,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:49.396925+07:00</t>
+          <t>2026-10-29T09:57:20.747837+07:00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1890,7 +1902,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1899,7 +1911,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>875</v>
+        <v>500</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1908,7 +1920,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1918,7 +1930,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:25.171194+07:00</t>
+          <t>2026-10-29T09:56:59.509736+07:00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1931,7 +1943,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1940,7 +1952,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>875</v>
+        <v>375</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1949,7 +1961,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1959,7 +1971,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:24.969707+07:00</t>
+          <t>2026-10-29T09:56:59.507543+07:00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1972,7 +1984,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1981,16 +1993,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3000</v>
+        <v>5125</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2000,7 +2012,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:46.106157+07:00</t>
+          <t>2026-10-29T09:57:17.624355+07:00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2013,7 +2025,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2022,7 +2034,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3875</v>
+        <v>2000</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2031,7 +2043,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2041,7 +2053,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:32.733197+07:00</t>
+          <t>2026-10-29T09:57:05.799853+07:00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2052,44 +2064,50 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>มุกดาหาร</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28T09:55:31.289535+07:00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="C40" t="n">
+        <v>4250</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:04.990543+07:00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: ''/''</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,7 +2116,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2107,7 +2125,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2117,7 +2135,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:51.299321+07:00</t>
+          <t>2026-10-29T09:57:22.234691+07:00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2130,7 +2148,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,7 +2157,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7125</v>
+        <v>4125</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2148,7 +2166,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2158,7 +2176,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:34.186317+07:00</t>
+          <t>2026-10-29T09:57:07.494800+07:00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2171,7 +2189,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,16 +2198,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1375</v>
+        <v>2750</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2199,7 +2217,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:47.672683+07:00</t>
+          <t>2026-10-29T09:57:19.124599+07:00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2212,7 +2230,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,7 +2239,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2230,7 +2248,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2240,7 +2258,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:42.947050+07:00</t>
+          <t>2026-10-29T09:57:15.060169+07:00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2253,7 +2271,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,7 +2280,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2271,7 +2289,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2281,7 +2299,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:40.747002+07:00</t>
+          <t>2026-10-29T09:57:12.645068+07:00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2292,44 +2310,50 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>ร้อยเอ็ด</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28T09:55:32.762451+07:00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="C46" t="n">
+        <v>2625</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:06.201298+07:00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_405201.png</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: ''/''</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2338,16 +2362,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4000</v>
+        <v>2750</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2357,7 +2381,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:40.805749+07:00</t>
+          <t>2026-10-29T09:57:13.374405+07:00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2368,44 +2392,50 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>ลำปาง</t>
         </is>
       </c>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28T09:55:22.933807+07:00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="C48" t="n">
+        <v>750</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:56.995152+07:00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_328201.png</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2414,7 +2444,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1500</v>
+        <v>375</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2423,7 +2453,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2433,7 +2463,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:21.101483+07:00</t>
+          <t>2026-10-29T09:56:55.061867+07:00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2446,7 +2476,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2455,16 +2485,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2875</v>
+        <v>1125</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2474,7 +2504,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:35.333157+07:00</t>
+          <t>2026-10-29T09:57:08.418279+07:00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2487,7 +2517,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2496,16 +2526,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4375</v>
+        <v>3000</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2515,7 +2545,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:31.278420+07:00</t>
+          <t>2026-10-29T09:57:04.523110+07:00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2528,7 +2558,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2537,7 +2567,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1125</v>
+        <v>1375</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2546,7 +2576,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2556,7 +2586,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:45.148566+07:00</t>
+          <t>2026-10-29T09:57:17.069769+07:00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2569,7 +2599,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2578,16 +2608,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>500</v>
+        <v>2375</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2597,7 +2627,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:51.279556+07:00</t>
+          <t>2026-10-29T09:57:22.086600+07:00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2610,7 +2640,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2619,16 +2649,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2250</v>
+        <v>375</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2638,7 +2668,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:16.284260+07:00</t>
+          <t>2026-10-29T09:56:50.144603+07:00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2651,7 +2681,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2660,7 +2690,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2669,7 +2699,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2679,7 +2709,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:41.037706+07:00</t>
+          <t>2026-10-29T09:57:13.559448+07:00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2692,7 +2722,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2701,7 +2731,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>875</v>
+        <v>375</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2710,7 +2740,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2720,7 +2750,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:18.450986+07:00</t>
+          <t>2026-10-29T09:56:53.048019+07:00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2733,7 +2763,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2742,7 +2772,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2751,7 +2781,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2761,7 +2791,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:39.502362+07:00</t>
+          <t>2026-10-29T09:57:12.056027+07:00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2774,7 +2804,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2783,16 +2813,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2802,7 +2832,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:44.611323+07:00</t>
+          <t>2026-10-29T09:57:16.145009+07:00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2815,7 +2845,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2824,7 +2854,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3625</v>
+        <v>2750</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2833,7 +2863,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2843,7 +2873,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:38.909296+07:00</t>
+          <t>2026-10-29T09:57:11.653242+07:00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2856,7 +2886,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2865,7 +2895,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2750</v>
+        <v>2000</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2874,7 +2904,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2884,7 +2914,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:40.770098+07:00</t>
+          <t>2026-10-29T09:57:13.143218+07:00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2897,7 +2927,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2906,7 +2936,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2000</v>
+        <v>3125</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2915,7 +2945,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2925,7 +2955,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:47.800428+07:00</t>
+          <t>2026-10-29T09:57:19.272711+07:00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2938,7 +2968,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2947,16 +2977,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3250</v>
+        <v>1250</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2966,7 +2996,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:36.434884+07:00</t>
+          <t>2026-10-29T09:57:09.017641+07:00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -2979,7 +3009,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2988,7 +3018,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2997,7 +3027,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3007,7 +3037,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:24.909871+07:00</t>
+          <t>2026-10-29T09:56:59.501441+07:00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3020,7 +3050,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3029,16 +3059,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2250</v>
+        <v>1000</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:29.203886+07:00</t>
+          <t>2026-10-29T09:57:02.847583+07:00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3061,7 +3091,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3070,16 +3100,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2125</v>
+        <v>1500</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3089,7 +3119,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:31.115856+07:00</t>
+          <t>2026-10-29T09:57:04.319886+07:00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3100,44 +3130,50 @@
       <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>อำนาจเจริญ</t>
         </is>
       </c>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="inlineStr"/>
-      <c r="E66" s="3" t="inlineStr"/>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28T09:55:33.619001+07:00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
+      <c r="C66" t="n">
+        <v>5375</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:06.939265+07:00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: ''/''</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3146,16 +3182,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2375</v>
+        <v>1500</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3165,7 +3201,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:29.379674+07:00</t>
+          <t>2026-10-29T09:57:03.071580+07:00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3178,7 +3214,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3187,7 +3223,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>625</v>
+        <v>375</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3196,7 +3232,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3206,7 +3242,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:22.967138+07:00</t>
+          <t>2026-10-29T09:56:57.019229+07:00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3219,7 +3255,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3228,16 +3264,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2875</v>
+        <v>1125</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3247,7 +3283,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:36.953286+07:00</t>
+          <t>2026-10-29T09:57:10.157906+07:00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3260,7 +3296,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3269,16 +3305,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2875</v>
+        <v>1750</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3288,7 +3324,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:26.665977+07:00</t>
+          <t>2026-10-29T09:57:01.029265+07:00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3301,7 +3337,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3310,7 +3346,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2375</v>
+        <v>2000</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3319,7 +3355,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3329,7 +3365,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:38.060471+07:00</t>
+          <t>2026-10-29T09:57:10.546743+07:00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3342,7 +3378,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3351,7 +3387,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3360,7 +3396,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3370,7 +3406,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:18.839641+07:00</t>
+          <t>2026-10-29T09:56:53.049208+07:00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3383,7 +3419,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3392,16 +3428,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2000</v>
+        <v>750</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3411,7 +3447,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:18.585938+07:00</t>
+          <t>2026-10-29T09:56:53.048527+07:00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3424,7 +3460,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3433,7 +3469,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1125</v>
+        <v>625</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3442,7 +3478,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3452,7 +3488,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:46.276428+07:00</t>
+          <t>2026-10-29T09:57:17.804847+07:00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3465,7 +3501,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3474,16 +3510,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3493,7 +3529,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:26.620284+07:00</t>
+          <t>2026-10-29T09:57:00.987756+07:00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3504,44 +3540,50 @@
       <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
         <is>
           <t>เลย</t>
         </is>
       </c>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="inlineStr"/>
-      <c r="E76" s="3" t="inlineStr"/>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28T09:55:29.212437+07:00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
+      <c r="C76" t="n">
+        <v>750</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:02.852432+07:00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_353201.png</t>
         </is>
       </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3550,16 +3592,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2250</v>
+        <v>375</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3569,7 +3611,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:22.937134+07:00</t>
+          <t>2026-10-29T09:56:57.009120+07:00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3582,7 +3624,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3591,16 +3633,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3250</v>
+        <v>1375</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-27 00Z</t>
+          <t>2026-10-28 00Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3610,7 +3652,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-28T09:55:20.830985+07:00</t>
+          <t>2026-10-29T09:56:55.038480+07:00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3711,7 +3753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I694"/>
+  <dimension ref="A1:I771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -32053,8 +32095,3159 @@
       </c>
       <c r="I694" t="inlineStr"/>
     </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>กระบี่</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>3875</v>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:20.603317+07:00</t>
+        </is>
+      </c>
+      <c r="H695" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_566202.png</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr"/>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>500</v>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:50.140442+07:00</t>
+        </is>
+      </c>
+      <c r="H696" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_455301.png</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr"/>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>750</v>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:14.123964+07:00</t>
+        </is>
+      </c>
+      <c r="H697" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_450201.png</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr"/>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>กาฬสินธุ์</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:05.003952+07:00</t>
+        </is>
+      </c>
+      <c r="H698" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_388401.png</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr"/>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>กำแพงเพชร</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>500</v>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:59.509215+07:00</t>
+        </is>
+      </c>
+      <c r="H699" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_380201.png</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr"/>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>ขอนแก่น</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:01.439891+07:00</t>
+        </is>
+      </c>
+      <c r="H700" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_381201.png</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr"/>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>จันทบุรี</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>125</v>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:16.320664+07:00</t>
+        </is>
+      </c>
+      <c r="H701" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_480201.png</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr"/>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>ฉะเชิงเทรา</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:14.647241+07:00</t>
+        </is>
+      </c>
+      <c r="H702" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_423301.png</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr"/>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>ชลบุรี</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>375</v>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:14.854948+07:00</t>
+        </is>
+      </c>
+      <c r="H703" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_459201.png</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr"/>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>ชัยนาท</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:10.193389+07:00</t>
+        </is>
+      </c>
+      <c r="H704" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_402301.png</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr"/>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>ชัยภูมิ</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:06.948290+07:00</t>
+        </is>
+      </c>
+      <c r="H705" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_403201.png</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr"/>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>2625</v>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:18.545104+07:00</t>
+        </is>
+      </c>
+      <c r="H706" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr"/>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>ตรัง</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:21.419650+07:00</t>
+        </is>
+      </c>
+      <c r="H707" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_567201.png</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr"/>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>ตราด</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>250</v>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:16.992628+07:00</t>
+        </is>
+      </c>
+      <c r="H708" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_501201.png</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr"/>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>ตาก</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>750</v>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:57.018460+07:00</t>
+        </is>
+      </c>
+      <c r="H709" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_376201.png</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr"/>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:11.886977+07:00</t>
+        </is>
+      </c>
+      <c r="H710" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_417201.png</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr"/>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>875</v>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:53.047382+07:00</t>
+        </is>
+      </c>
+      <c r="H711" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr"/>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>นครพนม</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:03.052347+07:00</t>
+        </is>
+      </c>
+      <c r="H712" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_357201.png</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr"/>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>นครราชสีมา</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:08.423096+07:00</t>
+        </is>
+      </c>
+      <c r="H713" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_431201.png</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr"/>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>นครศรีธรรมราช</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>875</v>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:20.031255+07:00</t>
+        </is>
+      </c>
+      <c r="H714" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_552201.png</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr"/>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>นครสวรรค์</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:09.183352+07:00</t>
+        </is>
+      </c>
+      <c r="H715" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_400201.png</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr"/>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>500</v>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:50.141319+07:00</t>
+        </is>
+      </c>
+      <c r="H716" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_411000.png</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr"/>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>นราธิวาส</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>375</v>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:22.916853+07:00</t>
+        </is>
+      </c>
+      <c r="H717" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_583201.png</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr"/>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>น่าน</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>125</v>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:55.061063+07:00</t>
+        </is>
+      </c>
+      <c r="H718" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_331201.png</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr"/>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>บึงกาฬ</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>500</v>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:01.456730+07:00</t>
+        </is>
+      </c>
+      <c r="H719" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_363201.png</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr"/>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>บุรีรัมย์</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:07.705693+07:00</t>
+        </is>
+      </c>
+      <c r="H720" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_436201.png</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr"/>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>ปทุมธานี</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>500</v>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:50.142585+07:00</t>
+        </is>
+      </c>
+      <c r="H721" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_419301.png</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr"/>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>ประจวบคีรีขันธ์</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>3125</v>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:18.464571+07:00</t>
+        </is>
+      </c>
+      <c r="H722" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_500201.png</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr"/>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>ปราจีนบุรี</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>125</v>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:15.592210+07:00</t>
+        </is>
+      </c>
+      <c r="H723" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_430201.png</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr"/>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:21.514807+07:00</t>
+        </is>
+      </c>
+      <c r="H724" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B725" s="3" t="inlineStr">
+        <is>
+          <t>พระนครศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="C725" s="3" t="n"/>
+      <c r="D725" s="3" t="inlineStr"/>
+      <c r="E725" s="3" t="inlineStr"/>
+      <c r="F725" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G725" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:11.266071+07:00</t>
+        </is>
+      </c>
+      <c r="H725" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
+        </is>
+      </c>
+      <c r="I725" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>พะเยา</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>500</v>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:55.051761+07:00</t>
+        </is>
+      </c>
+      <c r="H726" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_310201.png</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr"/>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>พังงา</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>4625</v>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:19.936957+07:00</t>
+        </is>
+      </c>
+      <c r="H727" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_561201.png</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr"/>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>พัทลุง</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>375</v>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:20.747837+07:00</t>
+        </is>
+      </c>
+      <c r="H728" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_560301.png</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr"/>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>พิจิตร</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>500</v>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:59.509736+07:00</t>
+        </is>
+      </c>
+      <c r="H729" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_386301.png</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr"/>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>375</v>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:59.507543+07:00</t>
+        </is>
+      </c>
+      <c r="H730" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_378201.png</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr"/>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>ภูเก็ต</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>5125</v>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:17.624355+07:00</t>
+        </is>
+      </c>
+      <c r="H731" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_564201.png</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr"/>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>มหาสารคาม</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:05.799853+07:00</t>
+        </is>
+      </c>
+      <c r="H732" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_387401.png</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr"/>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>มุกดาหาร</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>4250</v>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:04.990543+07:00</t>
+        </is>
+      </c>
+      <c r="H733" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr"/>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>ยะลา</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:22.234691+07:00</t>
+        </is>
+      </c>
+      <c r="H734" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_581301.png</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr"/>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>ยโสธร</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>4125</v>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:07.494800+07:00</t>
+        </is>
+      </c>
+      <c r="H735" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_406201.png</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr"/>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>ระนอง</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:19.124599+07:00</t>
+        </is>
+      </c>
+      <c r="H736" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_532201.png</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr"/>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>ระยอง</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>375</v>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:15.060169+07:00</t>
+        </is>
+      </c>
+      <c r="H737" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr"/>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>ราชบุรี</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>500</v>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:12.645068+07:00</t>
+        </is>
+      </c>
+      <c r="H738" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>2625</v>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:06.201298+07:00</t>
+        </is>
+      </c>
+      <c r="H739" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_405201.png</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>ลพบุรี</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:13.374405+07:00</t>
+        </is>
+      </c>
+      <c r="H740" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_426201.png</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>ลำปาง</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>750</v>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:56.995152+07:00</t>
+        </is>
+      </c>
+      <c r="H741" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_328201.png</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr"/>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>ลำพูน</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>375</v>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:55.061867+07:00</t>
+        </is>
+      </c>
+      <c r="H742" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_329201.png</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr"/>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>ศรีสะเกษ</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:08.418279+07:00</t>
+        </is>
+      </c>
+      <c r="H743" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_409301.png</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr"/>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>สกลนคร</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:04.523110+07:00</t>
+        </is>
+      </c>
+      <c r="H744" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_356201.png</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr"/>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>สงขลา</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:17.069769+07:00</t>
+        </is>
+      </c>
+      <c r="H745" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_568501.png</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr"/>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>สตูล</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:22.086600+07:00</t>
+        </is>
+      </c>
+      <c r="H746" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_570201.png</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr"/>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>สมุทรปราการ</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>375</v>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:50.144603+07:00</t>
+        </is>
+      </c>
+      <c r="H747" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_429301.png</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr"/>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>สมุทรสงคราม</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>500</v>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:13.559448+07:00</t>
+        </is>
+      </c>
+      <c r="H748" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_438201.png</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr"/>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>สมุทรสาคร</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>375</v>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:53.048019+07:00</t>
+        </is>
+      </c>
+      <c r="H749" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_474000.png</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr"/>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>สระบุรี</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:12.056027+07:00</t>
+        </is>
+      </c>
+      <c r="H750" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_418000.png</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr"/>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>สระแก้ว</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:16.145009+07:00</t>
+        </is>
+      </c>
+      <c r="H751" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_440401.png</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr"/>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>สิงห์บุรี</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:11.653242+07:00</t>
+        </is>
+      </c>
+      <c r="H752" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_416000.png</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:13.143218+07:00</t>
+        </is>
+      </c>
+      <c r="H753" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_425201.png</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr"/>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>สุราษฎร์ธานี</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>3125</v>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:19.272711+07:00</t>
+        </is>
+      </c>
+      <c r="H754" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_551201.png</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr"/>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>สุรินทร์</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:09.017641+07:00</t>
+        </is>
+      </c>
+      <c r="H755" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_432201.png</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr"/>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>สุโขทัย</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>500</v>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:59.501441+07:00</t>
+        </is>
+      </c>
+      <c r="H756" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_373201.png</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr"/>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>หนองคาย</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:02.847583+07:00</t>
+        </is>
+      </c>
+      <c r="H757" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_352201.png</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr"/>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>หนองบัวลำภู</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:04.319886+07:00</t>
+        </is>
+      </c>
+      <c r="H758" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_360201.png</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr"/>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>อำนาจเจริญ</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>5375</v>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:06.939265+07:00</t>
+        </is>
+      </c>
+      <c r="H759" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr"/>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>อุดรธานี</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:03.071580+07:00</t>
+        </is>
+      </c>
+      <c r="H760" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr"/>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>อุตรดิตถ์</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>375</v>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:57.019229+07:00</t>
+        </is>
+      </c>
+      <c r="H761" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_351201.png</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr"/>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>อุทัยธานี</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:10.157906+07:00</t>
+        </is>
+      </c>
+      <c r="H762" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_410201.png</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr"/>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>อุบลราชธานี</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:01.029265+07:00</t>
+        </is>
+      </c>
+      <c r="H763" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_407501.png</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr"/>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>อ่างทอง</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:10.546743+07:00</t>
+        </is>
+      </c>
+      <c r="H764" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_414000.png</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr"/>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>เชียงราย</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>500</v>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:53.049208+07:00</t>
+        </is>
+      </c>
+      <c r="H765" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_303201.png</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr"/>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>เชียงใหม่</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>750</v>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:53.048527+07:00</t>
+        </is>
+      </c>
+      <c r="H766" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_327501.png</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr"/>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>เพชรบุรี</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>625</v>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:17.804847+07:00</t>
+        </is>
+      </c>
+      <c r="H767" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_465201.png</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr"/>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>500</v>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:00.987756+07:00</t>
+        </is>
+      </c>
+      <c r="H768" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_379201.png</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr"/>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>เลย</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>750</v>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:02.852432+07:00</t>
+        </is>
+      </c>
+      <c r="H769" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_353201.png</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr"/>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>แพร่</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>375</v>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:57.009120+07:00</t>
+        </is>
+      </c>
+      <c r="H770" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_330201.png</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr"/>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>แม่ฮ่องสอน</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>2026-10-28 00Z</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:56:55.038480+07:00</t>
+        </is>
+      </c>
+      <c r="H771" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_300201.png</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I694"/>
+  <autoFilter ref="A1:I771"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -32749,6 +35942,83 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H692" r:id="rId691"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H693" r:id="rId692"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H694" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H695" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H696" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H697" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H698" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H699" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H700" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H701" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H702" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H703" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H704" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H705" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H706" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H707" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H708" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H709" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H710" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H711" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H712" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H713" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H714" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H715" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H716" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H717" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H718" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H719" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H720" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H721" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H722" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H723" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H724" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H725" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H726" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H727" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H728" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H729" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H730" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H731" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H732" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H733" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H734" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H735" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H736" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H737" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H738" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H739" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H740" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H741" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H742" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H743" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H744" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H745" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H746" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H747" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H748" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H749" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H750" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H751" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H752" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H753" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H754" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H755" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H756" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H757" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H758" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H759" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H760" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H761" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H762" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H763" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H764" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H765" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H766" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H767" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H768" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H769" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H770" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H771" r:id="rId770"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -32760,7 +36030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -33591,8 +36861,43 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>พระนครศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:57:11.266071+07:00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I23"/>
+  <autoFilter ref="A1:I24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -33616,6 +36921,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ventilation.xlsx
+++ b/data/ventilation.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ล่าสุด'!$A$1:$I$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$771</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$848</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -523,16 +523,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3875</v>
+        <v>1625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:20.603317+07:00</t>
+          <t>2026-10-30T09:39:02.348156+07:00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>500</v>
+        <v>625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:50.140442+07:00</t>
+          <t>2026-10-30T09:38:25.878367+07:00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:14.123964+07:00</t>
+          <t>2026-10-30T09:38:54.898034+07:00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:05.003952+07:00</t>
+          <t>2026-10-30T09:38:42.507936+07:00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:59.509215+07:00</t>
+          <t>2026-10-30T09:38:36.149270+07:00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2250</v>
+        <v>1875</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:01.439891+07:00</t>
+          <t>2026-10-30T09:38:38.320126+07:00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:16.320664+07:00</t>
+          <t>2026-10-30T09:38:57.120352+07:00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1125</v>
+        <v>875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:14.647241+07:00</t>
+          <t>2026-10-30T09:38:54.898961+07:00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:14.854948+07:00</t>
+          <t>2026-10-30T09:38:54.902569+07:00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:10.193389+07:00</t>
+          <t>2026-10-30T09:38:49.026297+07:00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3000</v>
+        <v>2750</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:06.948290+07:00</t>
+          <t>2026-10-30T09:38:44.636144+07:00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2625</v>
+        <v>4000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:18.545104+07:00</t>
+          <t>2026-10-30T09:39:00.470505+07:00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2250</v>
+        <v>875</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:21.419650+07:00</t>
+          <t>2026-10-30T09:39:04.577304+07:00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:16.992628+07:00</t>
+          <t>2026-10-30T09:38:58.626476+07:00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:57.018460+07:00</t>
+          <t>2026-10-30T09:38:33.789485+07:00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1125</v>
+        <v>625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:11.886977+07:00</t>
+          <t>2026-10-30T09:38:50.952321+07:00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>875</v>
+        <v>625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:53.047382+07:00</t>
+          <t>2026-10-30T09:38:28.844881+07:00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1220,16 +1220,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2750</v>
+        <v>1500</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:03.052347+07:00</t>
+          <t>2026-10-30T09:38:40.189007+07:00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:08.423096+07:00</t>
+          <t>2026-10-30T09:38:47.325100+07:00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>875</v>
+        <v>1000</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:20.031255+07:00</t>
+          <t>2026-10-30T09:39:02.292980+07:00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1375</v>
+        <v>750</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:09.183352+07:00</t>
+          <t>2026-10-30T09:38:48.658010+07:00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>500</v>
+        <v>625</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:50.141319+07:00</t>
+          <t>2026-10-30T09:38:25.879040+07:00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>375</v>
+        <v>875</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:22.916853+07:00</t>
+          <t>2026-10-30T09:39:06.382959+07:00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:55.061063+07:00</t>
+          <t>2026-10-30T09:38:30.954128+07:00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>500</v>
+        <v>625</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:01.456730+07:00</t>
+          <t>2026-10-30T09:38:38.321311+07:00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1539,7 +1539,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1548,16 +1548,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2000</v>
+        <v>1375</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:07.705693+07:00</t>
+          <t>2026-10-30T09:38:46.430381+07:00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>500</v>
+        <v>625</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:50.142585+07:00</t>
+          <t>2026-10-30T09:38:25.879433+07:00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3125</v>
+        <v>1375</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:18.464571+07:00</t>
+          <t>2026-10-30T09:39:00.407963+07:00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>125</v>
+        <v>625</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:15.592210+07:00</t>
+          <t>2026-10-30T09:38:56.663643+07:00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1750</v>
+        <v>875</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:21.514807+07:00</t>
+          <t>2026-10-30T09:39:04.578390+07:00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1742,44 +1742,50 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>พระนครศรีอยุธยา</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>รอตรวจสอบ</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-29T09:57:11.266071+07:00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="C32" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:50.950800+07:00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>number_ocr_uncertain: '14875)'/'14875)'</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1788,7 +1794,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>500</v>
+        <v>125</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1797,7 +1803,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1807,7 +1813,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:55.051761+07:00</t>
+          <t>2026-10-30T09:38:30.916754+07:00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1820,7 +1826,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1829,16 +1835,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4625</v>
+        <v>3250</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1848,7 +1854,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:19.936957+07:00</t>
+          <t>2026-10-30T09:39:02.219072+07:00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1861,7 +1867,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1870,7 +1876,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>375</v>
+        <v>1250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1879,7 +1885,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1889,7 +1895,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:20.747837+07:00</t>
+          <t>2026-10-30T09:39:02.460235+07:00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1902,7 +1908,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1911,7 +1917,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1920,7 +1926,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1930,7 +1936,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:59.509736+07:00</t>
+          <t>2026-10-30T09:38:36.151040+07:00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1943,7 +1949,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1961,7 +1967,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1971,7 +1977,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:59.507543+07:00</t>
+          <t>2026-10-30T09:38:36.136269+07:00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1984,7 +1990,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1993,16 +1999,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5125</v>
+        <v>3500</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2012,7 +2018,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:17.624355+07:00</t>
+          <t>2026-10-30T09:38:58.708619+07:00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2025,7 +2031,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2034,7 +2040,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2000</v>
+        <v>2250</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2043,7 +2049,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2053,7 +2059,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:05.799853+07:00</t>
+          <t>2026-10-30T09:38:44.613919+07:00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2066,7 +2072,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2075,16 +2081,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4250</v>
+        <v>2375</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2094,7 +2100,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:04.990543+07:00</t>
+          <t>2026-10-30T09:38:42.506876+07:00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2107,7 +2113,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2116,7 +2122,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2125,7 +2131,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2135,7 +2141,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:22.234691+07:00</t>
+          <t>2026-10-30T09:39:04.615429+07:00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2148,7 +2154,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2157,16 +2163,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4125</v>
+        <v>1875</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2176,7 +2182,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:07.494800+07:00</t>
+          <t>2026-10-30T09:38:46.317606+07:00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2189,7 +2195,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2198,16 +2204,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2750</v>
+        <v>1625</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2217,7 +2223,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:19.124599+07:00</t>
+          <t>2026-10-30T09:39:00.546220+07:00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2230,7 +2236,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2239,7 +2245,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>375</v>
+        <v>625</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2248,7 +2254,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2258,7 +2264,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:15.060169+07:00</t>
+          <t>2026-10-30T09:38:56.614764+07:00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2271,7 +2277,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2280,7 +2286,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>500</v>
+        <v>625</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2289,7 +2295,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2299,7 +2305,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:12.645068+07:00</t>
+          <t>2026-10-30T09:38:53.041835+07:00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2312,7 +2318,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2321,7 +2327,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2625</v>
+        <v>2000</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2330,7 +2336,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2340,7 +2346,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:06.201298+07:00</t>
+          <t>2026-10-30T09:38:44.614845+07:00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2353,7 +2359,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2362,7 +2368,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2750</v>
+        <v>2000</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2371,7 +2377,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2381,7 +2387,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:13.374405+07:00</t>
+          <t>2026-10-30T09:38:53.043505+07:00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2394,7 +2400,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2403,7 +2409,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2412,7 +2418,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2422,7 +2428,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:56.995152+07:00</t>
+          <t>2026-10-30T09:38:33.788158+07:00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2435,7 +2441,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2444,7 +2450,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2453,7 +2459,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2463,7 +2469,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:55.061867+07:00</t>
+          <t>2026-10-30T09:38:30.954863+07:00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2476,7 +2482,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2485,7 +2491,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1125</v>
+        <v>750</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2494,7 +2500,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2504,7 +2510,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:08.418279+07:00</t>
+          <t>2026-10-30T09:38:46.431445+07:00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2517,7 +2523,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2526,7 +2532,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3000</v>
+        <v>2375</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2535,7 +2541,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2545,7 +2551,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:04.523110+07:00</t>
+          <t>2026-10-30T09:38:42.493622+07:00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2558,7 +2564,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2567,7 +2573,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1375</v>
+        <v>1625</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2576,7 +2582,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2586,7 +2592,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:17.069769+07:00</t>
+          <t>2026-10-30T09:38:58.687237+07:00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2599,7 +2605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2608,16 +2614,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2375</v>
+        <v>625</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2627,7 +2633,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:22.086600+07:00</t>
+          <t>2026-10-30T09:39:04.579683+07:00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2640,7 +2646,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2649,7 +2655,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2658,7 +2664,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2668,7 +2674,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:50.144603+07:00</t>
+          <t>2026-10-30T09:38:25.879945+07:00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2681,7 +2687,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2690,7 +2696,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2699,7 +2705,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2709,7 +2715,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:13.559448+07:00</t>
+          <t>2026-10-30T09:38:54.894727+07:00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2722,7 +2728,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2740,7 +2746,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2750,7 +2756,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:53.048019+07:00</t>
+          <t>2026-10-30T09:38:28.845442+07:00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2763,7 +2769,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2772,7 +2778,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2781,7 +2787,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2791,7 +2797,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:12.056027+07:00</t>
+          <t>2026-10-30T09:38:53.041011+07:00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2804,7 +2810,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2813,7 +2819,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1500</v>
+        <v>875</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2822,7 +2828,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2832,7 +2838,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:16.145009+07:00</t>
+          <t>2026-10-30T09:38:56.702074+07:00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2845,7 +2851,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2854,7 +2860,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2750</v>
+        <v>2125</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2863,7 +2869,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2873,7 +2879,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:11.653242+07:00</t>
+          <t>2026-10-30T09:38:50.951722+07:00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2886,7 +2892,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2895,16 +2901,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2000</v>
+        <v>1375</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2914,7 +2920,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:13.143218+07:00</t>
+          <t>2026-10-30T09:38:53.042937+07:00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2927,7 +2933,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2936,16 +2942,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3125</v>
+        <v>875</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2955,7 +2961,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:19.272711+07:00</t>
+          <t>2026-10-30T09:39:00.671439+07:00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2968,7 +2974,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2977,7 +2983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1250</v>
+        <v>875</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2986,7 +2992,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2996,7 +3002,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:09.017641+07:00</t>
+          <t>2026-10-30T09:38:48.594388+07:00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3009,7 +3015,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3027,7 +3033,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3037,7 +3043,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:59.501441+07:00</t>
+          <t>2026-10-30T09:38:36.135506+07:00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3050,7 +3056,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3059,7 +3065,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1000</v>
+        <v>1250</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3068,7 +3074,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3078,7 +3084,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:02.847583+07:00</t>
+          <t>2026-10-30T09:38:40.148730+07:00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3091,7 +3097,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3100,7 +3106,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3109,7 +3115,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3119,7 +3125,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:04.319886+07:00</t>
+          <t>2026-10-30T09:38:42.492614+07:00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3132,7 +3138,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3141,16 +3147,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5375</v>
+        <v>2250</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3160,7 +3166,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:06.939265+07:00</t>
+          <t>2026-10-30T09:38:44.615639+07:00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3173,7 +3179,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3182,7 +3188,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1500</v>
+        <v>1375</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3191,7 +3197,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3201,7 +3207,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:03.071580+07:00</t>
+          <t>2026-10-30T09:38:40.191795+07:00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3214,7 +3220,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3232,7 +3238,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3242,7 +3248,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:57.019229+07:00</t>
+          <t>2026-10-30T09:38:33.790040+07:00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3255,7 +3261,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3264,7 +3270,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1125</v>
+        <v>1250</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3273,7 +3279,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3283,7 +3289,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:10.157906+07:00</t>
+          <t>2026-10-30T09:38:48.689393+07:00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3296,7 +3302,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3305,7 +3311,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1750</v>
+        <v>875</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3314,7 +3320,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3324,7 +3330,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:01.029265+07:00</t>
+          <t>2026-10-30T09:38:37.816883+07:00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3337,7 +3343,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3346,16 +3352,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2000</v>
+        <v>1250</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3365,7 +3371,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:10.546743+07:00</t>
+          <t>2026-10-30T09:38:50.949592+07:00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3378,7 +3384,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3396,7 +3402,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3406,7 +3412,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:53.049208+07:00</t>
+          <t>2026-10-30T09:38:28.847007+07:00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3419,7 +3425,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3428,7 +3434,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3437,7 +3443,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3447,7 +3453,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:53.048527+07:00</t>
+          <t>2026-10-30T09:38:28.846368+07:00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3460,7 +3466,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3469,7 +3475,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>625</v>
+        <v>250</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3478,7 +3484,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3488,7 +3494,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:17.804847+07:00</t>
+          <t>2026-10-30T09:38:58.905897+07:00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3501,7 +3507,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3519,7 +3525,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3529,7 +3535,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:00.987756+07:00</t>
+          <t>2026-10-30T09:38:37.816068+07:00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3542,7 +3548,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3551,7 +3557,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>750</v>
+        <v>875</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3560,7 +3566,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3570,7 +3576,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-10-29T09:57:02.852432+07:00</t>
+          <t>2026-10-30T09:38:40.150024+07:00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3583,7 +3589,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3592,7 +3598,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>375</v>
+        <v>125</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3601,7 +3607,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3611,7 +3617,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:57.009120+07:00</t>
+          <t>2026-10-30T09:38:33.788912+07:00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3624,7 +3630,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3633,7 +3639,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1375</v>
+        <v>625</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3642,7 +3648,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-28 00Z</t>
+          <t>2026-10-29 00Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3652,7 +3658,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-29T09:56:55.038480+07:00</t>
+          <t>2026-10-30T09:38:30.915990+07:00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3753,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I771"/>
+  <dimension ref="A1:I848"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -35246,8 +35252,3165 @@
       </c>
       <c r="I771" t="inlineStr"/>
     </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>กระบี่</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:39:02.348156+07:00</t>
+        </is>
+      </c>
+      <c r="H772" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_566202.png</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr"/>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>625</v>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:25.878367+07:00</t>
+        </is>
+      </c>
+      <c r="H773" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_455301.png</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr"/>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:54.898034+07:00</t>
+        </is>
+      </c>
+      <c r="H774" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_450201.png</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr"/>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>กาฬสินธุ์</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:42.507936+07:00</t>
+        </is>
+      </c>
+      <c r="H775" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_388401.png</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr"/>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>กำแพงเพชร</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>250</v>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:36.149270+07:00</t>
+        </is>
+      </c>
+      <c r="H776" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_380201.png</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr"/>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>ขอนแก่น</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>1875</v>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:38.320126+07:00</t>
+        </is>
+      </c>
+      <c r="H777" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_381201.png</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr"/>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>จันทบุรี</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>0</v>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:57.120352+07:00</t>
+        </is>
+      </c>
+      <c r="H778" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_480201.png</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr"/>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>ฉะเชิงเทรา</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>875</v>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:54.898961+07:00</t>
+        </is>
+      </c>
+      <c r="H779" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_423301.png</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr"/>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>ชลบุรี</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>375</v>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:54.902569+07:00</t>
+        </is>
+      </c>
+      <c r="H780" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_459201.png</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr"/>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>ชัยนาท</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:49.026297+07:00</t>
+        </is>
+      </c>
+      <c r="H781" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_402301.png</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr"/>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>ชัยภูมิ</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:44.636144+07:00</t>
+        </is>
+      </c>
+      <c r="H782" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_403201.png</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr"/>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:39:00.470505+07:00</t>
+        </is>
+      </c>
+      <c r="H783" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr"/>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>ตรัง</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>875</v>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:39:04.577304+07:00</t>
+        </is>
+      </c>
+      <c r="H784" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_567201.png</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr"/>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>ตราด</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>125</v>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:58.626476+07:00</t>
+        </is>
+      </c>
+      <c r="H785" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_501201.png</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>ตาก</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>750</v>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:33.789485+07:00</t>
+        </is>
+      </c>
+      <c r="H786" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_376201.png</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr"/>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>625</v>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:50.952321+07:00</t>
+        </is>
+      </c>
+      <c r="H787" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_417201.png</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>625</v>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:28.844881+07:00</t>
+        </is>
+      </c>
+      <c r="H788" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>นครพนม</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:40.189007+07:00</t>
+        </is>
+      </c>
+      <c r="H789" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_357201.png</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr"/>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>นครราชสีมา</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:47.325100+07:00</t>
+        </is>
+      </c>
+      <c r="H790" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_431201.png</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr"/>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>นครศรีธรรมราช</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:39:02.292980+07:00</t>
+        </is>
+      </c>
+      <c r="H791" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_552201.png</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr"/>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>นครสวรรค์</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>750</v>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:48.658010+07:00</t>
+        </is>
+      </c>
+      <c r="H792" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_400201.png</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>625</v>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:25.879040+07:00</t>
+        </is>
+      </c>
+      <c r="H793" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_411000.png</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr"/>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>นราธิวาส</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>875</v>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:39:06.382959+07:00</t>
+        </is>
+      </c>
+      <c r="H794" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_583201.png</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr"/>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>น่าน</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>125</v>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:30.954128+07:00</t>
+        </is>
+      </c>
+      <c r="H795" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_331201.png</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr"/>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>บึงกาฬ</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>625</v>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:38.321311+07:00</t>
+        </is>
+      </c>
+      <c r="H796" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_363201.png</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr"/>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>บุรีรัมย์</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:46.430381+07:00</t>
+        </is>
+      </c>
+      <c r="H797" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_436201.png</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr"/>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>ปทุมธานี</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>625</v>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:25.879433+07:00</t>
+        </is>
+      </c>
+      <c r="H798" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_419301.png</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr"/>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>ประจวบคีรีขันธ์</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:39:00.407963+07:00</t>
+        </is>
+      </c>
+      <c r="H799" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_500201.png</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>ปราจีนบุรี</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>625</v>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:56.663643+07:00</t>
+        </is>
+      </c>
+      <c r="H800" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_430201.png</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>875</v>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:39:04.578390+07:00</t>
+        </is>
+      </c>
+      <c r="H801" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr"/>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>พระนครศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:50.950800+07:00</t>
+        </is>
+      </c>
+      <c r="H802" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>พะเยา</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>125</v>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:30.916754+07:00</t>
+        </is>
+      </c>
+      <c r="H803" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_310201.png</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr"/>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>พังงา</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>3250</v>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:39:02.219072+07:00</t>
+        </is>
+      </c>
+      <c r="H804" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_561201.png</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr"/>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>พัทลุง</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:39:02.460235+07:00</t>
+        </is>
+      </c>
+      <c r="H805" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_560301.png</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr"/>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>พิจิตร</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>250</v>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:36.151040+07:00</t>
+        </is>
+      </c>
+      <c r="H806" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_386301.png</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr"/>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>375</v>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:36.136269+07:00</t>
+        </is>
+      </c>
+      <c r="H807" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_378201.png</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>ภูเก็ต</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:58.708619+07:00</t>
+        </is>
+      </c>
+      <c r="H808" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_564201.png</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr"/>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>มหาสารคาม</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:44.613919+07:00</t>
+        </is>
+      </c>
+      <c r="H809" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_387401.png</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr"/>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>มุกดาหาร</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:42.506876+07:00</t>
+        </is>
+      </c>
+      <c r="H810" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr"/>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>ยะลา</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>500</v>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:39:04.615429+07:00</t>
+        </is>
+      </c>
+      <c r="H811" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_581301.png</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr"/>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>ยโสธร</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>1875</v>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:46.317606+07:00</t>
+        </is>
+      </c>
+      <c r="H812" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_406201.png</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr"/>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>ระนอง</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:39:00.546220+07:00</t>
+        </is>
+      </c>
+      <c r="H813" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_532201.png</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>ระยอง</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>625</v>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:56.614764+07:00</t>
+        </is>
+      </c>
+      <c r="H814" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr"/>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>ราชบุรี</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>625</v>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:53.041835+07:00</t>
+        </is>
+      </c>
+      <c r="H815" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr"/>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:44.614845+07:00</t>
+        </is>
+      </c>
+      <c r="H816" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_405201.png</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr"/>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>ลพบุรี</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:53.043505+07:00</t>
+        </is>
+      </c>
+      <c r="H817" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_426201.png</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>ลำปาง</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>250</v>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:33.788158+07:00</t>
+        </is>
+      </c>
+      <c r="H818" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_328201.png</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>ลำพูน</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>250</v>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:30.954863+07:00</t>
+        </is>
+      </c>
+      <c r="H819" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_329201.png</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr"/>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>ศรีสะเกษ</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>750</v>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:46.431445+07:00</t>
+        </is>
+      </c>
+      <c r="H820" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_409301.png</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr"/>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>สกลนคร</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:42.493622+07:00</t>
+        </is>
+      </c>
+      <c r="H821" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_356201.png</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr"/>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>สงขลา</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:58.687237+07:00</t>
+        </is>
+      </c>
+      <c r="H822" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_568501.png</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>สตูล</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>625</v>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:39:04.579683+07:00</t>
+        </is>
+      </c>
+      <c r="H823" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_570201.png</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>สมุทรปราการ</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>500</v>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:25.879945+07:00</t>
+        </is>
+      </c>
+      <c r="H824" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_429301.png</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>สมุทรสงคราม</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>375</v>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:54.894727+07:00</t>
+        </is>
+      </c>
+      <c r="H825" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_438201.png</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>สมุทรสาคร</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>375</v>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:28.845442+07:00</t>
+        </is>
+      </c>
+      <c r="H826" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_474000.png</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>สระบุรี</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>500</v>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:53.041011+07:00</t>
+        </is>
+      </c>
+      <c r="H827" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_418000.png</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>สระแก้ว</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>875</v>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:56.702074+07:00</t>
+        </is>
+      </c>
+      <c r="H828" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_440401.png</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr"/>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>สิงห์บุรี</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:50.951722+07:00</t>
+        </is>
+      </c>
+      <c r="H829" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_416000.png</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:53.042937+07:00</t>
+        </is>
+      </c>
+      <c r="H830" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_425201.png</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr"/>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>สุราษฎร์ธานี</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>875</v>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:39:00.671439+07:00</t>
+        </is>
+      </c>
+      <c r="H831" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_551201.png</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr"/>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>สุรินทร์</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>875</v>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:48.594388+07:00</t>
+        </is>
+      </c>
+      <c r="H832" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_432201.png</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr"/>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>สุโขทัย</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>500</v>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:36.135506+07:00</t>
+        </is>
+      </c>
+      <c r="H833" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_373201.png</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr"/>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>หนองคาย</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:40.148730+07:00</t>
+        </is>
+      </c>
+      <c r="H834" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_352201.png</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr"/>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>หนองบัวลำภู</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:42.492614+07:00</t>
+        </is>
+      </c>
+      <c r="H835" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_360201.png</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>อำนาจเจริญ</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:44.615639+07:00</t>
+        </is>
+      </c>
+      <c r="H836" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr"/>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>อุดรธานี</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:40.191795+07:00</t>
+        </is>
+      </c>
+      <c r="H837" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr"/>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>อุตรดิตถ์</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>375</v>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:33.790040+07:00</t>
+        </is>
+      </c>
+      <c r="H838" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_351201.png</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>อุทัยธานี</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:48.689393+07:00</t>
+        </is>
+      </c>
+      <c r="H839" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_410201.png</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>อุบลราชธานี</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>875</v>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:37.816883+07:00</t>
+        </is>
+      </c>
+      <c r="H840" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_407501.png</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr"/>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>อ่างทอง</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:50.949592+07:00</t>
+        </is>
+      </c>
+      <c r="H841" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_414000.png</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>เชียงราย</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>500</v>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:28.847007+07:00</t>
+        </is>
+      </c>
+      <c r="H842" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_303201.png</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>เชียงใหม่</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>375</v>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:28.846368+07:00</t>
+        </is>
+      </c>
+      <c r="H843" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_327501.png</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>เพชรบุรี</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>250</v>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:58.905897+07:00</t>
+        </is>
+      </c>
+      <c r="H844" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_465201.png</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>500</v>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:37.816068+07:00</t>
+        </is>
+      </c>
+      <c r="H845" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_379201.png</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>เลย</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>875</v>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:40.150024+07:00</t>
+        </is>
+      </c>
+      <c r="H846" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_353201.png</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>แพร่</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>125</v>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:33.788912+07:00</t>
+        </is>
+      </c>
+      <c r="H847" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_330201.png</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr"/>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>แม่ฮ่องสอน</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>625</v>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>2026-10-29 00Z</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:38:30.915990+07:00</t>
+        </is>
+      </c>
+      <c r="H848" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_300201.png</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I771"/>
+  <autoFilter ref="A1:I848"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -36019,6 +39182,83 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H769" r:id="rId768"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H770" r:id="rId769"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H771" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H772" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H773" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H774" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H775" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H776" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H777" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H778" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H779" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H780" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H781" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H782" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H783" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H784" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H785" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H786" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H787" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H788" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H789" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H790" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H791" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H792" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H793" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H794" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H795" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H796" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H797" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H798" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H799" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H800" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H801" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H802" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H803" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H804" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H805" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H806" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H807" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H808" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H809" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H810" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H811" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H812" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H813" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H814" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H815" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H816" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H817" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H818" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H819" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H820" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H821" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H822" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H823" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H824" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H825" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H826" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H827" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H828" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H829" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H830" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H831" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H832" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H833" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H834" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H835" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H836" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H837" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H838" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H839" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H840" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H841" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H842" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H843" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H844" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H845" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H846" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H847" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H848" r:id="rId847"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ventilation.xlsx
+++ b/data/ventilation.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:02.348156+07:00</t>
+          <t>2026-10-30T09:57:41.150174+07:00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:25.878367+07:00</t>
+          <t>2026-10-30T09:57:08.214173+07:00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:54.898034+07:00</t>
+          <t>2026-10-30T09:57:34.038244+07:00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:42.507936+07:00</t>
+          <t>2026-10-30T09:57:23.444750+07:00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:36.149270+07:00</t>
+          <t>2026-10-30T09:57:18.069775+07:00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:38.320126+07:00</t>
+          <t>2026-10-30T09:57:19.864257+07:00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:57.120352+07:00</t>
+          <t>2026-10-30T09:57:35.895575+07:00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:54.898961+07:00</t>
+          <t>2026-10-30T09:57:34.105301+07:00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:54.902569+07:00</t>
+          <t>2026-10-30T09:57:34.105945+07:00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:49.026297+07:00</t>
+          <t>2026-10-30T09:57:28.764491+07:00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:44.636144+07:00</t>
+          <t>2026-10-30T09:57:25.222675+07:00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:00.470505+07:00</t>
+          <t>2026-10-30T09:57:39.341789+07:00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:04.577304+07:00</t>
+          <t>2026-10-30T09:57:42.697769+07:00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:58.626476+07:00</t>
+          <t>2026-10-30T09:57:37.519884+07:00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:33.789485+07:00</t>
+          <t>2026-10-30T09:57:15.520662+07:00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:50.952321+07:00</t>
+          <t>2026-10-30T09:57:30.544292+07:00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:28.844881+07:00</t>
+          <t>2026-10-30T09:57:10.943146+07:00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:40.189007+07:00</t>
+          <t>2026-10-30T09:57:21.654228+07:00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:47.325100+07:00</t>
+          <t>2026-10-30T09:57:27.002543+07:00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:02.292980+07:00</t>
+          <t>2026-10-30T09:57:41.134961+07:00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:48.658010+07:00</t>
+          <t>2026-10-30T09:57:28.724576+07:00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:25.879040+07:00</t>
+          <t>2026-10-30T09:57:08.214851+07:00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:06.382959+07:00</t>
+          <t>2026-10-30T09:57:44.377183+07:00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:30.954128+07:00</t>
+          <t>2026-10-30T09:57:13.590283+07:00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:38.321311+07:00</t>
+          <t>2026-10-30T09:57:19.882864+07:00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:46.430381+07:00</t>
+          <t>2026-10-30T09:57:26.959820+07:00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:25.879433+07:00</t>
+          <t>2026-10-30T09:57:08.215245+07:00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:00.407963+07:00</t>
+          <t>2026-10-30T09:57:39.268142+07:00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:56.663643+07:00</t>
+          <t>2026-10-30T09:57:35.813589+07:00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:04.578390+07:00</t>
+          <t>2026-10-30T09:57:42.901581+07:00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:50.950800+07:00</t>
+          <t>2026-10-30T09:57:30.513158+07:00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:30.916754+07:00</t>
+          <t>2026-10-30T09:57:13.587818+07:00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:02.219072+07:00</t>
+          <t>2026-10-30T09:57:40.995154+07:00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:02.460235+07:00</t>
+          <t>2026-10-30T09:57:41.168176+07:00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:36.151040+07:00</t>
+          <t>2026-10-30T09:57:18.104399+07:00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:36.136269+07:00</t>
+          <t>2026-10-30T09:57:18.063447+07:00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:58.708619+07:00</t>
+          <t>2026-10-30T09:57:37.640408+07:00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:44.613919+07:00</t>
+          <t>2026-10-30T09:57:25.150379+07:00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:42.506876+07:00</t>
+          <t>2026-10-30T09:57:23.403713+07:00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:04.615429+07:00</t>
+          <t>2026-10-30T09:57:42.920119+07:00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:46.317606+07:00</t>
+          <t>2026-10-30T09:57:26.958822+07:00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:00.546220+07:00</t>
+          <t>2026-10-30T09:57:39.399308+07:00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:56.614764+07:00</t>
+          <t>2026-10-30T09:57:35.774483+07:00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:53.041835+07:00</t>
+          <t>2026-10-30T09:57:32.267505+07:00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:44.614845+07:00</t>
+          <t>2026-10-30T09:57:25.187837+07:00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:53.043505+07:00</t>
+          <t>2026-10-30T09:57:32.338309+07:00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:33.788158+07:00</t>
+          <t>2026-10-30T09:57:15.230449+07:00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:30.954863+07:00</t>
+          <t>2026-10-30T09:57:13.605705+07:00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:46.431445+07:00</t>
+          <t>2026-10-30T09:57:26.960653+07:00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:42.493622+07:00</t>
+          <t>2026-10-30T09:57:23.402806+07:00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:58.687237+07:00</t>
+          <t>2026-10-30T09:57:37.572573+07:00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:04.579683+07:00</t>
+          <t>2026-10-30T09:57:42.919200+07:00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:25.879945+07:00</t>
+          <t>2026-10-30T09:57:08.215829+07:00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:54.894727+07:00</t>
+          <t>2026-10-30T09:57:34.006892+07:00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:28.845442+07:00</t>
+          <t>2026-10-30T09:57:10.943711+07:00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:53.041011+07:00</t>
+          <t>2026-10-30T09:57:32.265183+07:00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:56.702074+07:00</t>
+          <t>2026-10-30T09:57:35.857622+07:00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:50.951722+07:00</t>
+          <t>2026-10-30T09:57:30.533140+07:00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:53.042937+07:00</t>
+          <t>2026-10-30T09:57:32.317455+07:00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:00.671439+07:00</t>
+          <t>2026-10-30T09:57:39.416999+07:00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:48.594388+07:00</t>
+          <t>2026-10-30T09:57:28.723532+07:00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:36.135506+07:00</t>
+          <t>2026-10-30T09:57:18.062473+07:00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:40.148730+07:00</t>
+          <t>2026-10-30T09:57:21.606230+07:00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:42.492614+07:00</t>
+          <t>2026-10-30T09:57:23.362870+07:00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:44.615639+07:00</t>
+          <t>2026-10-30T09:57:25.199315+07:00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:40.191795+07:00</t>
+          <t>2026-10-30T09:57:21.654901+07:00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:33.790040+07:00</t>
+          <t>2026-10-30T09:57:15.526309+07:00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:48.689393+07:00</t>
+          <t>2026-10-30T09:57:28.754114+07:00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:37.816883+07:00</t>
+          <t>2026-10-30T09:57:19.840148+07:00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:50.949592+07:00</t>
+          <t>2026-10-30T09:57:30.484548+07:00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:28.847007+07:00</t>
+          <t>2026-10-30T09:57:10.944880+07:00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:28.846368+07:00</t>
+          <t>2026-10-30T09:57:10.944223+07:00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:58.905897+07:00</t>
+          <t>2026-10-30T09:57:37.665275+07:00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:37.816068+07:00</t>
+          <t>2026-10-30T09:57:19.827952+07:00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:40.150024+07:00</t>
+          <t>2026-10-30T09:57:21.607153+07:00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:33.788912+07:00</t>
+          <t>2026-10-30T09:57:15.300415+07:00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:30.915990+07:00</t>
+          <t>2026-10-30T09:57:13.561604+07:00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -35283,7 +35283,7 @@
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:02.348156+07:00</t>
+          <t>2026-10-30T09:57:41.150174+07:00</t>
         </is>
       </c>
       <c r="H772" s="2" t="inlineStr">
@@ -35324,7 +35324,7 @@
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:25.878367+07:00</t>
+          <t>2026-10-30T09:57:08.214173+07:00</t>
         </is>
       </c>
       <c r="H773" s="2" t="inlineStr">
@@ -35365,7 +35365,7 @@
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:54.898034+07:00</t>
+          <t>2026-10-30T09:57:34.038244+07:00</t>
         </is>
       </c>
       <c r="H774" s="2" t="inlineStr">
@@ -35406,7 +35406,7 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:42.507936+07:00</t>
+          <t>2026-10-30T09:57:23.444750+07:00</t>
         </is>
       </c>
       <c r="H775" s="2" t="inlineStr">
@@ -35447,7 +35447,7 @@
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:36.149270+07:00</t>
+          <t>2026-10-30T09:57:18.069775+07:00</t>
         </is>
       </c>
       <c r="H776" s="2" t="inlineStr">
@@ -35488,7 +35488,7 @@
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:38.320126+07:00</t>
+          <t>2026-10-30T09:57:19.864257+07:00</t>
         </is>
       </c>
       <c r="H777" s="2" t="inlineStr">
@@ -35529,7 +35529,7 @@
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:57.120352+07:00</t>
+          <t>2026-10-30T09:57:35.895575+07:00</t>
         </is>
       </c>
       <c r="H778" s="2" t="inlineStr">
@@ -35570,7 +35570,7 @@
       </c>
       <c r="G779" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:54.898961+07:00</t>
+          <t>2026-10-30T09:57:34.105301+07:00</t>
         </is>
       </c>
       <c r="H779" s="2" t="inlineStr">
@@ -35611,7 +35611,7 @@
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:54.902569+07:00</t>
+          <t>2026-10-30T09:57:34.105945+07:00</t>
         </is>
       </c>
       <c r="H780" s="2" t="inlineStr">
@@ -35652,7 +35652,7 @@
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:49.026297+07:00</t>
+          <t>2026-10-30T09:57:28.764491+07:00</t>
         </is>
       </c>
       <c r="H781" s="2" t="inlineStr">
@@ -35693,7 +35693,7 @@
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:44.636144+07:00</t>
+          <t>2026-10-30T09:57:25.222675+07:00</t>
         </is>
       </c>
       <c r="H782" s="2" t="inlineStr">
@@ -35734,7 +35734,7 @@
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:00.470505+07:00</t>
+          <t>2026-10-30T09:57:39.341789+07:00</t>
         </is>
       </c>
       <c r="H783" s="2" t="inlineStr">
@@ -35775,7 +35775,7 @@
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:04.577304+07:00</t>
+          <t>2026-10-30T09:57:42.697769+07:00</t>
         </is>
       </c>
       <c r="H784" s="2" t="inlineStr">
@@ -35816,7 +35816,7 @@
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:58.626476+07:00</t>
+          <t>2026-10-30T09:57:37.519884+07:00</t>
         </is>
       </c>
       <c r="H785" s="2" t="inlineStr">
@@ -35857,7 +35857,7 @@
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:33.789485+07:00</t>
+          <t>2026-10-30T09:57:15.520662+07:00</t>
         </is>
       </c>
       <c r="H786" s="2" t="inlineStr">
@@ -35898,7 +35898,7 @@
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:50.952321+07:00</t>
+          <t>2026-10-30T09:57:30.544292+07:00</t>
         </is>
       </c>
       <c r="H787" s="2" t="inlineStr">
@@ -35939,7 +35939,7 @@
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:28.844881+07:00</t>
+          <t>2026-10-30T09:57:10.943146+07:00</t>
         </is>
       </c>
       <c r="H788" s="2" t="inlineStr">
@@ -35980,7 +35980,7 @@
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:40.189007+07:00</t>
+          <t>2026-10-30T09:57:21.654228+07:00</t>
         </is>
       </c>
       <c r="H789" s="2" t="inlineStr">
@@ -36021,7 +36021,7 @@
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:47.325100+07:00</t>
+          <t>2026-10-30T09:57:27.002543+07:00</t>
         </is>
       </c>
       <c r="H790" s="2" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:02.292980+07:00</t>
+          <t>2026-10-30T09:57:41.134961+07:00</t>
         </is>
       </c>
       <c r="H791" s="2" t="inlineStr">
@@ -36103,7 +36103,7 @@
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:48.658010+07:00</t>
+          <t>2026-10-30T09:57:28.724576+07:00</t>
         </is>
       </c>
       <c r="H792" s="2" t="inlineStr">
@@ -36144,7 +36144,7 @@
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:25.879040+07:00</t>
+          <t>2026-10-30T09:57:08.214851+07:00</t>
         </is>
       </c>
       <c r="H793" s="2" t="inlineStr">
@@ -36185,7 +36185,7 @@
       </c>
       <c r="G794" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:06.382959+07:00</t>
+          <t>2026-10-30T09:57:44.377183+07:00</t>
         </is>
       </c>
       <c r="H794" s="2" t="inlineStr">
@@ -36226,7 +36226,7 @@
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:30.954128+07:00</t>
+          <t>2026-10-30T09:57:13.590283+07:00</t>
         </is>
       </c>
       <c r="H795" s="2" t="inlineStr">
@@ -36267,7 +36267,7 @@
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:38.321311+07:00</t>
+          <t>2026-10-30T09:57:19.882864+07:00</t>
         </is>
       </c>
       <c r="H796" s="2" t="inlineStr">
@@ -36308,7 +36308,7 @@
       </c>
       <c r="G797" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:46.430381+07:00</t>
+          <t>2026-10-30T09:57:26.959820+07:00</t>
         </is>
       </c>
       <c r="H797" s="2" t="inlineStr">
@@ -36349,7 +36349,7 @@
       </c>
       <c r="G798" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:25.879433+07:00</t>
+          <t>2026-10-30T09:57:08.215245+07:00</t>
         </is>
       </c>
       <c r="H798" s="2" t="inlineStr">
@@ -36390,7 +36390,7 @@
       </c>
       <c r="G799" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:00.407963+07:00</t>
+          <t>2026-10-30T09:57:39.268142+07:00</t>
         </is>
       </c>
       <c r="H799" s="2" t="inlineStr">
@@ -36431,7 +36431,7 @@
       </c>
       <c r="G800" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:56.663643+07:00</t>
+          <t>2026-10-30T09:57:35.813589+07:00</t>
         </is>
       </c>
       <c r="H800" s="2" t="inlineStr">
@@ -36472,7 +36472,7 @@
       </c>
       <c r="G801" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:04.578390+07:00</t>
+          <t>2026-10-30T09:57:42.901581+07:00</t>
         </is>
       </c>
       <c r="H801" s="2" t="inlineStr">
@@ -36513,7 +36513,7 @@
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:50.950800+07:00</t>
+          <t>2026-10-30T09:57:30.513158+07:00</t>
         </is>
       </c>
       <c r="H802" s="2" t="inlineStr">
@@ -36554,7 +36554,7 @@
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:30.916754+07:00</t>
+          <t>2026-10-30T09:57:13.587818+07:00</t>
         </is>
       </c>
       <c r="H803" s="2" t="inlineStr">
@@ -36595,7 +36595,7 @@
       </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:02.219072+07:00</t>
+          <t>2026-10-30T09:57:40.995154+07:00</t>
         </is>
       </c>
       <c r="H804" s="2" t="inlineStr">
@@ -36636,7 +36636,7 @@
       </c>
       <c r="G805" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:02.460235+07:00</t>
+          <t>2026-10-30T09:57:41.168176+07:00</t>
         </is>
       </c>
       <c r="H805" s="2" t="inlineStr">
@@ -36677,7 +36677,7 @@
       </c>
       <c r="G806" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:36.151040+07:00</t>
+          <t>2026-10-30T09:57:18.104399+07:00</t>
         </is>
       </c>
       <c r="H806" s="2" t="inlineStr">
@@ -36718,7 +36718,7 @@
       </c>
       <c r="G807" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:36.136269+07:00</t>
+          <t>2026-10-30T09:57:18.063447+07:00</t>
         </is>
       </c>
       <c r="H807" s="2" t="inlineStr">
@@ -36759,7 +36759,7 @@
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:58.708619+07:00</t>
+          <t>2026-10-30T09:57:37.640408+07:00</t>
         </is>
       </c>
       <c r="H808" s="2" t="inlineStr">
@@ -36800,7 +36800,7 @@
       </c>
       <c r="G809" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:44.613919+07:00</t>
+          <t>2026-10-30T09:57:25.150379+07:00</t>
         </is>
       </c>
       <c r="H809" s="2" t="inlineStr">
@@ -36841,7 +36841,7 @@
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:42.506876+07:00</t>
+          <t>2026-10-30T09:57:23.403713+07:00</t>
         </is>
       </c>
       <c r="H810" s="2" t="inlineStr">
@@ -36882,7 +36882,7 @@
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:04.615429+07:00</t>
+          <t>2026-10-30T09:57:42.920119+07:00</t>
         </is>
       </c>
       <c r="H811" s="2" t="inlineStr">
@@ -36923,7 +36923,7 @@
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:46.317606+07:00</t>
+          <t>2026-10-30T09:57:26.958822+07:00</t>
         </is>
       </c>
       <c r="H812" s="2" t="inlineStr">
@@ -36964,7 +36964,7 @@
       </c>
       <c r="G813" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:00.546220+07:00</t>
+          <t>2026-10-30T09:57:39.399308+07:00</t>
         </is>
       </c>
       <c r="H813" s="2" t="inlineStr">
@@ -37005,7 +37005,7 @@
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:56.614764+07:00</t>
+          <t>2026-10-30T09:57:35.774483+07:00</t>
         </is>
       </c>
       <c r="H814" s="2" t="inlineStr">
@@ -37046,7 +37046,7 @@
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:53.041835+07:00</t>
+          <t>2026-10-30T09:57:32.267505+07:00</t>
         </is>
       </c>
       <c r="H815" s="2" t="inlineStr">
@@ -37087,7 +37087,7 @@
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:44.614845+07:00</t>
+          <t>2026-10-30T09:57:25.187837+07:00</t>
         </is>
       </c>
       <c r="H816" s="2" t="inlineStr">
@@ -37128,7 +37128,7 @@
       </c>
       <c r="G817" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:53.043505+07:00</t>
+          <t>2026-10-30T09:57:32.338309+07:00</t>
         </is>
       </c>
       <c r="H817" s="2" t="inlineStr">
@@ -37169,7 +37169,7 @@
       </c>
       <c r="G818" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:33.788158+07:00</t>
+          <t>2026-10-30T09:57:15.230449+07:00</t>
         </is>
       </c>
       <c r="H818" s="2" t="inlineStr">
@@ -37210,7 +37210,7 @@
       </c>
       <c r="G819" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:30.954863+07:00</t>
+          <t>2026-10-30T09:57:13.605705+07:00</t>
         </is>
       </c>
       <c r="H819" s="2" t="inlineStr">
@@ -37251,7 +37251,7 @@
       </c>
       <c r="G820" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:46.431445+07:00</t>
+          <t>2026-10-30T09:57:26.960653+07:00</t>
         </is>
       </c>
       <c r="H820" s="2" t="inlineStr">
@@ -37292,7 +37292,7 @@
       </c>
       <c r="G821" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:42.493622+07:00</t>
+          <t>2026-10-30T09:57:23.402806+07:00</t>
         </is>
       </c>
       <c r="H821" s="2" t="inlineStr">
@@ -37333,7 +37333,7 @@
       </c>
       <c r="G822" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:58.687237+07:00</t>
+          <t>2026-10-30T09:57:37.572573+07:00</t>
         </is>
       </c>
       <c r="H822" s="2" t="inlineStr">
@@ -37374,7 +37374,7 @@
       </c>
       <c r="G823" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:04.579683+07:00</t>
+          <t>2026-10-30T09:57:42.919200+07:00</t>
         </is>
       </c>
       <c r="H823" s="2" t="inlineStr">
@@ -37415,7 +37415,7 @@
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:25.879945+07:00</t>
+          <t>2026-10-30T09:57:08.215829+07:00</t>
         </is>
       </c>
       <c r="H824" s="2" t="inlineStr">
@@ -37456,7 +37456,7 @@
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:54.894727+07:00</t>
+          <t>2026-10-30T09:57:34.006892+07:00</t>
         </is>
       </c>
       <c r="H825" s="2" t="inlineStr">
@@ -37497,7 +37497,7 @@
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:28.845442+07:00</t>
+          <t>2026-10-30T09:57:10.943711+07:00</t>
         </is>
       </c>
       <c r="H826" s="2" t="inlineStr">
@@ -37538,7 +37538,7 @@
       </c>
       <c r="G827" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:53.041011+07:00</t>
+          <t>2026-10-30T09:57:32.265183+07:00</t>
         </is>
       </c>
       <c r="H827" s="2" t="inlineStr">
@@ -37579,7 +37579,7 @@
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:56.702074+07:00</t>
+          <t>2026-10-30T09:57:35.857622+07:00</t>
         </is>
       </c>
       <c r="H828" s="2" t="inlineStr">
@@ -37620,7 +37620,7 @@
       </c>
       <c r="G829" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:50.951722+07:00</t>
+          <t>2026-10-30T09:57:30.533140+07:00</t>
         </is>
       </c>
       <c r="H829" s="2" t="inlineStr">
@@ -37661,7 +37661,7 @@
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:53.042937+07:00</t>
+          <t>2026-10-30T09:57:32.317455+07:00</t>
         </is>
       </c>
       <c r="H830" s="2" t="inlineStr">
@@ -37702,7 +37702,7 @@
       </c>
       <c r="G831" t="inlineStr">
         <is>
-          <t>2026-10-30T09:39:00.671439+07:00</t>
+          <t>2026-10-30T09:57:39.416999+07:00</t>
         </is>
       </c>
       <c r="H831" s="2" t="inlineStr">
@@ -37743,7 +37743,7 @@
       </c>
       <c r="G832" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:48.594388+07:00</t>
+          <t>2026-10-30T09:57:28.723532+07:00</t>
         </is>
       </c>
       <c r="H832" s="2" t="inlineStr">
@@ -37784,7 +37784,7 @@
       </c>
       <c r="G833" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:36.135506+07:00</t>
+          <t>2026-10-30T09:57:18.062473+07:00</t>
         </is>
       </c>
       <c r="H833" s="2" t="inlineStr">
@@ -37825,7 +37825,7 @@
       </c>
       <c r="G834" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:40.148730+07:00</t>
+          <t>2026-10-30T09:57:21.606230+07:00</t>
         </is>
       </c>
       <c r="H834" s="2" t="inlineStr">
@@ -37866,7 +37866,7 @@
       </c>
       <c r="G835" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:42.492614+07:00</t>
+          <t>2026-10-30T09:57:23.362870+07:00</t>
         </is>
       </c>
       <c r="H835" s="2" t="inlineStr">
@@ -37907,7 +37907,7 @@
       </c>
       <c r="G836" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:44.615639+07:00</t>
+          <t>2026-10-30T09:57:25.199315+07:00</t>
         </is>
       </c>
       <c r="H836" s="2" t="inlineStr">
@@ -37948,7 +37948,7 @@
       </c>
       <c r="G837" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:40.191795+07:00</t>
+          <t>2026-10-30T09:57:21.654901+07:00</t>
         </is>
       </c>
       <c r="H837" s="2" t="inlineStr">
@@ -37989,7 +37989,7 @@
       </c>
       <c r="G838" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:33.790040+07:00</t>
+          <t>2026-10-30T09:57:15.526309+07:00</t>
         </is>
       </c>
       <c r="H838" s="2" t="inlineStr">
@@ -38030,7 +38030,7 @@
       </c>
       <c r="G839" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:48.689393+07:00</t>
+          <t>2026-10-30T09:57:28.754114+07:00</t>
         </is>
       </c>
       <c r="H839" s="2" t="inlineStr">
@@ -38071,7 +38071,7 @@
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:37.816883+07:00</t>
+          <t>2026-10-30T09:57:19.840148+07:00</t>
         </is>
       </c>
       <c r="H840" s="2" t="inlineStr">
@@ -38112,7 +38112,7 @@
       </c>
       <c r="G841" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:50.949592+07:00</t>
+          <t>2026-10-30T09:57:30.484548+07:00</t>
         </is>
       </c>
       <c r="H841" s="2" t="inlineStr">
@@ -38153,7 +38153,7 @@
       </c>
       <c r="G842" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:28.847007+07:00</t>
+          <t>2026-10-30T09:57:10.944880+07:00</t>
         </is>
       </c>
       <c r="H842" s="2" t="inlineStr">
@@ -38194,7 +38194,7 @@
       </c>
       <c r="G843" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:28.846368+07:00</t>
+          <t>2026-10-30T09:57:10.944223+07:00</t>
         </is>
       </c>
       <c r="H843" s="2" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="G844" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:58.905897+07:00</t>
+          <t>2026-10-30T09:57:37.665275+07:00</t>
         </is>
       </c>
       <c r="H844" s="2" t="inlineStr">
@@ -38276,7 +38276,7 @@
       </c>
       <c r="G845" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:37.816068+07:00</t>
+          <t>2026-10-30T09:57:19.827952+07:00</t>
         </is>
       </c>
       <c r="H845" s="2" t="inlineStr">
@@ -38317,7 +38317,7 @@
       </c>
       <c r="G846" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:40.150024+07:00</t>
+          <t>2026-10-30T09:57:21.607153+07:00</t>
         </is>
       </c>
       <c r="H846" s="2" t="inlineStr">
@@ -38358,7 +38358,7 @@
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:33.788912+07:00</t>
+          <t>2026-10-30T09:57:15.300415+07:00</t>
         </is>
       </c>
       <c r="H847" s="2" t="inlineStr">
@@ -38399,7 +38399,7 @@
       </c>
       <c r="G848" t="inlineStr">
         <is>
-          <t>2026-10-30T09:38:30.915990+07:00</t>
+          <t>2026-10-30T09:57:13.561604+07:00</t>
         </is>
       </c>
       <c r="H848" s="2" t="inlineStr">

--- a/data/ventilation.xlsx
+++ b/data/ventilation.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ล่าสุด'!$A$1:$I$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$848</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ย้อนหลัง'!$A$1:$I$925</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'รอตรวจสอบ'!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1625</v>
+        <v>500</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:41.150174+07:00</t>
+          <t>2026-10-31T09:56:08.009361+07:00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>625</v>
+        <v>250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:08.214173+07:00</t>
+          <t>2026-10-31T09:55:36.044019+07:00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:34.038244+07:00</t>
+          <t>2026-10-31T09:56:01.347247+07:00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2125</v>
+        <v>875</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:23.444750+07:00</t>
+          <t>2026-10-31T09:55:51.051229+07:00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>250</v>
+        <v>625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:18.069775+07:00</t>
+          <t>2026-10-31T09:55:45.169757+07:00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1875</v>
+        <v>625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:19.864257+07:00</t>
+          <t>2026-10-31T09:55:47.146217+07:00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:35.895575+07:00</t>
+          <t>2026-10-31T09:56:03.165041+07:00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>875</v>
+        <v>500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:34.105301+07:00</t>
+          <t>2026-10-31T09:56:01.583107+07:00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:34.105945+07:00</t>
+          <t>2026-10-31T09:56:01.626328+07:00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1750</v>
+        <v>750</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:28.764491+07:00</t>
+          <t>2026-10-31T09:55:56.681545+07:00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -933,16 +933,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2750</v>
+        <v>1125</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:25.222675+07:00</t>
+          <t>2026-10-31T09:55:53.484885+07:00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4000</v>
+        <v>1125</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:39.341789+07:00</t>
+          <t>2026-10-31T09:56:05.892136+07:00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>875</v>
+        <v>250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:42.697769+07:00</t>
+          <t>2026-10-31T09:56:08.117972+07:00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>125</v>
+        <v>375</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:37.519884+07:00</t>
+          <t>2026-10-31T09:56:03.298719+07:00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>750</v>
+        <v>625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:15.520662+07:00</t>
+          <t>2026-10-31T09:55:42.372748+07:00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:30.544292+07:00</t>
+          <t>2026-10-31T09:55:58.186712+07:00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>625</v>
+        <v>125</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:10.943146+07:00</t>
+          <t>2026-10-31T09:55:38.541114+07:00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:21.654228+07:00</t>
+          <t>2026-10-31T09:55:49.007092+07:00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1750</v>
+        <v>375</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:27.002543+07:00</t>
+          <t>2026-10-31T09:55:55.160133+07:00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1000</v>
+        <v>625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:41.134961+07:00</t>
+          <t>2026-10-31T09:56:07.352872+07:00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:28.724576+07:00</t>
+          <t>2026-10-31T09:55:56.568216+07:00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:08.214851+07:00</t>
+          <t>2026-10-31T09:55:36.044711+07:00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>875</v>
+        <v>375</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:44.377183+07:00</t>
+          <t>2026-10-31T09:56:09.693101+07:00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>125</v>
+        <v>625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:13.590283+07:00</t>
+          <t>2026-10-31T09:55:40.532551+07:00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>625</v>
+        <v>375</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:19.882864+07:00</t>
+          <t>2026-10-31T09:55:47.161476+07:00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1539,7 +1539,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1375</v>
+        <v>375</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:26.959820+07:00</t>
+          <t>2026-10-31T09:55:54.452357+07:00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:08.215245+07:00</t>
+          <t>2026-10-31T09:55:36.045284+07:00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1375</v>
+        <v>625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:39.268142+07:00</t>
+          <t>2026-10-31T09:56:04.808564+07:00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:35.813589+07:00</t>
+          <t>2026-10-31T09:56:02.881710+07:00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>875</v>
+        <v>500</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:42.901581+07:00</t>
+          <t>2026-10-31T09:56:08.796472+07:00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1125</v>
+        <v>375</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:30.513158+07:00</t>
+          <t>2026-10-31T09:55:58.050498+07:00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1783,50 +1783,44 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>พะเยา</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>125</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-10-29 00Z</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2026-10-30T09:57:13.587818+07:00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:40.510982+07:00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_310201.png</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '(1375)'/'(1375)'</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1835,16 +1829,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3250</v>
+        <v>625</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1854,7 +1848,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:40.995154+07:00</t>
+          <t>2026-10-31T09:56:06.540379+07:00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1867,7 +1861,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1876,7 +1870,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1250</v>
+        <v>375</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1885,7 +1879,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1895,7 +1889,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:41.168176+07:00</t>
+          <t>2026-10-31T09:56:08.036640+07:00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1908,7 +1902,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1926,7 +1920,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1936,7 +1930,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:18.104399+07:00</t>
+          <t>2026-10-31T09:55:45.191124+07:00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1949,7 +1943,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1958,7 +1952,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1967,7 +1961,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1977,7 +1971,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:18.063447+07:00</t>
+          <t>2026-10-31T09:55:45.167358+07:00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1990,7 +1984,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1999,16 +1993,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3500</v>
+        <v>875</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2018,7 +2012,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:37.640408+07:00</t>
+          <t>2026-10-31T09:56:04.673512+07:00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2031,7 +2025,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2040,16 +2034,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2250</v>
+        <v>875</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2059,7 +2053,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:25.150379+07:00</t>
+          <t>2026-10-31T09:55:52.429418+07:00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2072,7 +2066,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2081,16 +2075,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2375</v>
+        <v>1000</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2100,7 +2094,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:23.403713+07:00</t>
+          <t>2026-10-31T09:55:51.009493+07:00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2113,7 +2107,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2122,7 +2116,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2131,7 +2125,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2141,7 +2135,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:42.920119+07:00</t>
+          <t>2026-10-31T09:56:09.562544+07:00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2154,7 +2148,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2163,7 +2157,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1875</v>
+        <v>625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2172,7 +2166,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2182,7 +2176,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:26.958822+07:00</t>
+          <t>2026-10-31T09:55:54.429154+07:00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2195,7 +2189,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2204,7 +2198,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1625</v>
+        <v>375</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2213,7 +2207,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2223,7 +2217,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:39.399308+07:00</t>
+          <t>2026-10-31T09:56:06.417568+07:00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2236,7 +2230,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2245,7 +2239,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>625</v>
+        <v>1125</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2254,7 +2248,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2264,7 +2258,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:35.774483+07:00</t>
+          <t>2026-10-31T09:56:01.752709+07:00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2277,7 +2271,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2286,7 +2280,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>625</v>
+        <v>250</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2295,7 +2289,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2305,7 +2299,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:32.267505+07:00</t>
+          <t>2026-10-31T09:55:59.803356+07:00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2318,7 +2312,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2327,16 +2321,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2000</v>
+        <v>625</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2346,7 +2340,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:25.187837+07:00</t>
+          <t>2026-10-31T09:55:52.561253+07:00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2359,7 +2353,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2368,16 +2362,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2000</v>
+        <v>375</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2387,7 +2381,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:32.338309+07:00</t>
+          <t>2026-10-31T09:55:59.886560+07:00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2400,7 +2394,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2418,7 +2412,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2428,7 +2422,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:15.230449+07:00</t>
+          <t>2026-10-31T09:55:42.277459+07:00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2441,7 +2435,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2450,7 +2444,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2459,7 +2453,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2469,7 +2463,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:13.605705+07:00</t>
+          <t>2026-10-31T09:55:40.548696+07:00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2482,7 +2476,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2491,7 +2485,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2500,7 +2494,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2510,7 +2504,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:26.960653+07:00</t>
+          <t>2026-10-31T09:55:54.456972+07:00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2523,7 +2517,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2532,16 +2526,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2375</v>
+        <v>875</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2551,7 +2545,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:23.402806+07:00</t>
+          <t>2026-10-31T09:55:51.002581+07:00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2564,7 +2558,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2573,7 +2567,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1625</v>
+        <v>500</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2582,7 +2576,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2592,7 +2586,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:37.572573+07:00</t>
+          <t>2026-10-31T09:56:04.424941+07:00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2605,7 +2599,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2614,7 +2608,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>625</v>
+        <v>125</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2623,7 +2617,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2633,7 +2627,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:42.919200+07:00</t>
+          <t>2026-10-31T09:56:09.528335+07:00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2646,7 +2640,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2655,7 +2649,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>500</v>
+        <v>875</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2664,7 +2658,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2674,7 +2668,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:08.215829+07:00</t>
+          <t>2026-10-31T09:55:36.046157+07:00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2687,7 +2681,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2696,7 +2690,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>375</v>
+        <v>125</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2705,7 +2699,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2715,7 +2709,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:34.006892+07:00</t>
+          <t>2026-10-31T09:56:00.271324+07:00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2728,7 +2722,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2737,7 +2731,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>375</v>
+        <v>625</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2746,7 +2740,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2756,7 +2750,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:10.943711+07:00</t>
+          <t>2026-10-31T09:55:38.541527+07:00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2769,7 +2763,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2787,7 +2781,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2797,7 +2791,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:32.265183+07:00</t>
+          <t>2026-10-31T09:55:58.832484+07:00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2810,7 +2804,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2828,7 +2822,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2838,7 +2832,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:35.857622+07:00</t>
+          <t>2026-10-31T09:56:03.148438+07:00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2851,7 +2845,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2860,16 +2854,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2125</v>
+        <v>375</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2879,7 +2873,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:30.533140+07:00</t>
+          <t>2026-10-31T09:55:58.119836+07:00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2892,7 +2886,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2901,7 +2895,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1375</v>
+        <v>375</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2910,7 +2904,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2920,7 +2914,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:32.317455+07:00</t>
+          <t>2026-10-31T09:55:59.836569+07:00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2933,7 +2927,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2951,7 +2945,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2961,7 +2955,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:39.416999+07:00</t>
+          <t>2026-10-31T09:56:06.538682+07:00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2974,7 +2968,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2983,7 +2977,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>875</v>
+        <v>375</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2992,7 +2986,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3002,7 +2996,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:28.723532+07:00</t>
+          <t>2026-10-31T09:55:55.906799+07:00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3015,7 +3009,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3033,7 +3027,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3043,7 +3037,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:18.062473+07:00</t>
+          <t>2026-10-31T09:55:45.151185+07:00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3054,50 +3048,44 @@
       <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>หนองคาย</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v>1250</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2026-10-29 00Z</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2026-10-30T09:57:21.606230+07:00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:48.971250+07:00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_352201.png</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '(1375)'/'(1375)'</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3106,7 +3094,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1000</v>
+        <v>625</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3115,7 +3103,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3125,7 +3113,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:23.362870+07:00</t>
+          <t>2026-10-31T09:55:50.925058+07:00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3138,7 +3126,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3147,16 +3135,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2250</v>
+        <v>500</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3166,7 +3154,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:25.199315+07:00</t>
+          <t>2026-10-31T09:55:52.568160+07:00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3177,50 +3165,44 @@
       <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>อุดรธานี</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>1375</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2026-10-29 00Z</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2026-10-30T09:57:21.654901+07:00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="C67" s="3" t="n"/>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:49.016060+07:00</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '(1375)'/'(1375)'</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3229,7 +3211,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3238,7 +3220,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3248,7 +3230,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:15.526309+07:00</t>
+          <t>2026-10-31T09:55:42.379123+07:00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3261,7 +3243,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3270,7 +3252,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3279,7 +3261,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3289,7 +3271,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:28.754114+07:00</t>
+          <t>2026-10-31T09:55:56.589701+07:00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3302,7 +3284,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3311,7 +3293,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>875</v>
+        <v>500</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3320,7 +3302,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3330,7 +3312,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:19.840148+07:00</t>
+          <t>2026-10-31T09:55:47.143501+07:00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3343,7 +3325,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3352,7 +3334,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1250</v>
+        <v>375</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3361,7 +3343,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3371,7 +3353,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:30.484548+07:00</t>
+          <t>2026-10-31T09:55:57.367139+07:00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3382,50 +3364,44 @@
       <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>เชียงราย</t>
         </is>
       </c>
-      <c r="C72" t="n">
-        <v>500</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>2026-10-29 00Z</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>อ่านได้</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2026-10-30T09:57:10.944880+07:00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:38.542378+07:00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
         <is>
           <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_303201.png</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '(1250)'/'(1250)'</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3434,7 +3410,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>375</v>
+        <v>625</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3443,7 +3419,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3453,7 +3429,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:10.944223+07:00</t>
+          <t>2026-10-31T09:55:38.541860+07:00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3466,7 +3442,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3475,7 +3451,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3484,7 +3460,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3494,7 +3470,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:37.665275+07:00</t>
+          <t>2026-10-31T09:56:04.732892+07:00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3507,7 +3483,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3516,7 +3492,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3525,7 +3501,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3535,7 +3511,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:19.827952+07:00</t>
+          <t>2026-10-31T09:55:47.115250+07:00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3548,7 +3524,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3566,7 +3542,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3576,7 +3552,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:21.607153+07:00</t>
+          <t>2026-10-31T09:55:48.982924+07:00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3589,7 +3565,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3607,7 +3583,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3617,7 +3593,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:15.300415+07:00</t>
+          <t>2026-10-31T09:55:42.351786+07:00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3630,7 +3606,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3639,7 +3615,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>625</v>
+        <v>750</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3648,7 +3624,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-29 00Z</t>
+          <t>2026-10-30 00Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3658,7 +3634,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-30T09:57:13.561604+07:00</t>
+          <t>2026-10-31T09:55:40.398035+07:00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3759,7 +3735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I848"/>
+  <dimension ref="A1:I925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -38409,8 +38385,3141 @@
       </c>
       <c r="I848" t="inlineStr"/>
     </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>กระบี่</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>500</v>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:08.009361+07:00</t>
+        </is>
+      </c>
+      <c r="H849" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_566202.png</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr"/>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>250</v>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:36.044019+07:00</t>
+        </is>
+      </c>
+      <c r="H850" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_455301.png</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>250</v>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:01.347247+07:00</t>
+        </is>
+      </c>
+      <c r="H851" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_450201.png</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr"/>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>กาฬสินธุ์</t>
+        </is>
+      </c>
+      <c r="C852" t="n">
+        <v>875</v>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:51.051229+07:00</t>
+        </is>
+      </c>
+      <c r="H852" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_388401.png</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>กำแพงเพชร</t>
+        </is>
+      </c>
+      <c r="C853" t="n">
+        <v>625</v>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:45.169757+07:00</t>
+        </is>
+      </c>
+      <c r="H853" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_380201.png</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>ขอนแก่น</t>
+        </is>
+      </c>
+      <c r="C854" t="n">
+        <v>625</v>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:47.146217+07:00</t>
+        </is>
+      </c>
+      <c r="H854" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_381201.png</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>จันทบุรี</t>
+        </is>
+      </c>
+      <c r="C855" t="n">
+        <v>500</v>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:03.165041+07:00</t>
+        </is>
+      </c>
+      <c r="H855" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_480201.png</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>ฉะเชิงเทรา</t>
+        </is>
+      </c>
+      <c r="C856" t="n">
+        <v>500</v>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:01.583107+07:00</t>
+        </is>
+      </c>
+      <c r="H856" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_423301.png</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr"/>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>ชลบุรี</t>
+        </is>
+      </c>
+      <c r="C857" t="n">
+        <v>375</v>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:01.626328+07:00</t>
+        </is>
+      </c>
+      <c r="H857" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_459201.png</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr"/>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>ชัยนาท</t>
+        </is>
+      </c>
+      <c r="C858" t="n">
+        <v>750</v>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:56.681545+07:00</t>
+        </is>
+      </c>
+      <c r="H858" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_402301.png</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>ชัยภูมิ</t>
+        </is>
+      </c>
+      <c r="C859" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:53.484885+07:00</t>
+        </is>
+      </c>
+      <c r="H859" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_403201.png</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr"/>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="C860" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:05.892136+07:00</t>
+        </is>
+      </c>
+      <c r="H860" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_517201.png</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr"/>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>ตรัง</t>
+        </is>
+      </c>
+      <c r="C861" t="n">
+        <v>250</v>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:08.117972+07:00</t>
+        </is>
+      </c>
+      <c r="H861" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_567201.png</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr"/>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>ตราด</t>
+        </is>
+      </c>
+      <c r="C862" t="n">
+        <v>375</v>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:03.298719+07:00</t>
+        </is>
+      </c>
+      <c r="H862" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_501201.png</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr"/>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>ตาก</t>
+        </is>
+      </c>
+      <c r="C863" t="n">
+        <v>625</v>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:42.372748+07:00</t>
+        </is>
+      </c>
+      <c r="H863" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_376201.png</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr"/>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="C864" t="n">
+        <v>500</v>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:58.186712+07:00</t>
+        </is>
+      </c>
+      <c r="H864" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_417201.png</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr"/>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="C865" t="n">
+        <v>125</v>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:38.541114+07:00</t>
+        </is>
+      </c>
+      <c r="H865" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_451301.png</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr"/>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>นครพนม</t>
+        </is>
+      </c>
+      <c r="C866" t="n">
+        <v>750</v>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:49.007092+07:00</t>
+        </is>
+      </c>
+      <c r="H866" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_357201.png</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr"/>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>นครราชสีมา</t>
+        </is>
+      </c>
+      <c r="C867" t="n">
+        <v>375</v>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:55.160133+07:00</t>
+        </is>
+      </c>
+      <c r="H867" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_431201.png</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr"/>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>นครศรีธรรมราช</t>
+        </is>
+      </c>
+      <c r="C868" t="n">
+        <v>625</v>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:07.352872+07:00</t>
+        </is>
+      </c>
+      <c r="H868" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_552201.png</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr"/>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>นครสวรรค์</t>
+        </is>
+      </c>
+      <c r="C869" t="n">
+        <v>500</v>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:56.568216+07:00</t>
+        </is>
+      </c>
+      <c r="H869" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_400201.png</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr"/>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="C870" t="n">
+        <v>500</v>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:36.044711+07:00</t>
+        </is>
+      </c>
+      <c r="H870" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_411000.png</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr"/>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>นราธิวาส</t>
+        </is>
+      </c>
+      <c r="C871" t="n">
+        <v>375</v>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:09.693101+07:00</t>
+        </is>
+      </c>
+      <c r="H871" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_583201.png</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr"/>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>น่าน</t>
+        </is>
+      </c>
+      <c r="C872" t="n">
+        <v>625</v>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:40.532551+07:00</t>
+        </is>
+      </c>
+      <c r="H872" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_331201.png</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr"/>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>บึงกาฬ</t>
+        </is>
+      </c>
+      <c r="C873" t="n">
+        <v>375</v>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:47.161476+07:00</t>
+        </is>
+      </c>
+      <c r="H873" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_363201.png</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr"/>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>บุรีรัมย์</t>
+        </is>
+      </c>
+      <c r="C874" t="n">
+        <v>375</v>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:54.452357+07:00</t>
+        </is>
+      </c>
+      <c r="H874" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_436201.png</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr"/>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>ปทุมธานี</t>
+        </is>
+      </c>
+      <c r="C875" t="n">
+        <v>500</v>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:36.045284+07:00</t>
+        </is>
+      </c>
+      <c r="H875" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_419301.png</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr"/>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>ประจวบคีรีขันธ์</t>
+        </is>
+      </c>
+      <c r="C876" t="n">
+        <v>625</v>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:04.808564+07:00</t>
+        </is>
+      </c>
+      <c r="H876" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_500201.png</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>ปราจีนบุรี</t>
+        </is>
+      </c>
+      <c r="C877" t="n">
+        <v>625</v>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:02.881710+07:00</t>
+        </is>
+      </c>
+      <c r="H877" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_430201.png</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr"/>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="C878" t="n">
+        <v>500</v>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:08.796472+07:00</t>
+        </is>
+      </c>
+      <c r="H878" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_580201.png</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr"/>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>พระนครศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="C879" t="n">
+        <v>375</v>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:58.050498+07:00</t>
+        </is>
+      </c>
+      <c r="H879" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_415301.png</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B880" s="3" t="inlineStr">
+        <is>
+          <t>พะเยา</t>
+        </is>
+      </c>
+      <c r="C880" s="3" t="n"/>
+      <c r="D880" s="3" t="inlineStr"/>
+      <c r="E880" s="3" t="inlineStr"/>
+      <c r="F880" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G880" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:40.510982+07:00</t>
+        </is>
+      </c>
+      <c r="H880" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_310201.png</t>
+        </is>
+      </c>
+      <c r="I880" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '(1375)'/'(1375)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>พังงา</t>
+        </is>
+      </c>
+      <c r="C881" t="n">
+        <v>625</v>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:06.540379+07:00</t>
+        </is>
+      </c>
+      <c r="H881" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_561201.png</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>พัทลุง</t>
+        </is>
+      </c>
+      <c r="C882" t="n">
+        <v>375</v>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:08.036640+07:00</t>
+        </is>
+      </c>
+      <c r="H882" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_560301.png</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>พิจิตร</t>
+        </is>
+      </c>
+      <c r="C883" t="n">
+        <v>250</v>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:45.191124+07:00</t>
+        </is>
+      </c>
+      <c r="H883" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_386301.png</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="C884" t="n">
+        <v>250</v>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:45.167358+07:00</t>
+        </is>
+      </c>
+      <c r="H884" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_378201.png</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>ภูเก็ต</t>
+        </is>
+      </c>
+      <c r="C885" t="n">
+        <v>875</v>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:04.673512+07:00</t>
+        </is>
+      </c>
+      <c r="H885" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_564201.png</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>มหาสารคาม</t>
+        </is>
+      </c>
+      <c r="C886" t="n">
+        <v>875</v>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:52.429418+07:00</t>
+        </is>
+      </c>
+      <c r="H886" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_387401.png</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr"/>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>มุกดาหาร</t>
+        </is>
+      </c>
+      <c r="C887" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:51.009493+07:00</t>
+        </is>
+      </c>
+      <c r="H887" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_383201.png</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr"/>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>ยะลา</t>
+        </is>
+      </c>
+      <c r="C888" t="n">
+        <v>250</v>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:09.562544+07:00</t>
+        </is>
+      </c>
+      <c r="H888" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_581301.png</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr"/>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>ยโสธร</t>
+        </is>
+      </c>
+      <c r="C889" t="n">
+        <v>625</v>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:54.429154+07:00</t>
+        </is>
+      </c>
+      <c r="H889" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_406201.png</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr"/>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>ระนอง</t>
+        </is>
+      </c>
+      <c r="C890" t="n">
+        <v>375</v>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:06.417568+07:00</t>
+        </is>
+      </c>
+      <c r="H890" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_532201.png</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr"/>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>ระยอง</t>
+        </is>
+      </c>
+      <c r="C891" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:01.752709+07:00</t>
+        </is>
+      </c>
+      <c r="H891" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_478201.png</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr"/>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>ราชบุรี</t>
+        </is>
+      </c>
+      <c r="C892" t="n">
+        <v>250</v>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:59.803356+07:00</t>
+        </is>
+      </c>
+      <c r="H892" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_424301.png</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr"/>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="C893" t="n">
+        <v>625</v>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:52.561253+07:00</t>
+        </is>
+      </c>
+      <c r="H893" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_405201.png</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr"/>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>ลพบุรี</t>
+        </is>
+      </c>
+      <c r="C894" t="n">
+        <v>375</v>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:59.886560+07:00</t>
+        </is>
+      </c>
+      <c r="H894" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_426201.png</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr"/>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>ลำปาง</t>
+        </is>
+      </c>
+      <c r="C895" t="n">
+        <v>250</v>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:42.277459+07:00</t>
+        </is>
+      </c>
+      <c r="H895" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_328201.png</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr"/>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>ลำพูน</t>
+        </is>
+      </c>
+      <c r="C896" t="n">
+        <v>375</v>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:40.548696+07:00</t>
+        </is>
+      </c>
+      <c r="H896" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_329201.png</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>ศรีสะเกษ</t>
+        </is>
+      </c>
+      <c r="C897" t="n">
+        <v>500</v>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:54.456972+07:00</t>
+        </is>
+      </c>
+      <c r="H897" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_409301.png</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr"/>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>สกลนคร</t>
+        </is>
+      </c>
+      <c r="C898" t="n">
+        <v>875</v>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:51.002581+07:00</t>
+        </is>
+      </c>
+      <c r="H898" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_356201.png</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr"/>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>สงขลา</t>
+        </is>
+      </c>
+      <c r="C899" t="n">
+        <v>500</v>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:04.424941+07:00</t>
+        </is>
+      </c>
+      <c r="H899" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_568501.png</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr"/>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>สตูล</t>
+        </is>
+      </c>
+      <c r="C900" t="n">
+        <v>125</v>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:09.528335+07:00</t>
+        </is>
+      </c>
+      <c r="H900" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_570201.png</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>สมุทรปราการ</t>
+        </is>
+      </c>
+      <c r="C901" t="n">
+        <v>875</v>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:36.046157+07:00</t>
+        </is>
+      </c>
+      <c r="H901" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_429301.png</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr"/>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>สมุทรสงคราม</t>
+        </is>
+      </c>
+      <c r="C902" t="n">
+        <v>125</v>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:00.271324+07:00</t>
+        </is>
+      </c>
+      <c r="H902" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_438201.png</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr"/>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>สมุทรสาคร</t>
+        </is>
+      </c>
+      <c r="C903" t="n">
+        <v>625</v>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:38.541527+07:00</t>
+        </is>
+      </c>
+      <c r="H903" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_474000.png</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr"/>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>สระบุรี</t>
+        </is>
+      </c>
+      <c r="C904" t="n">
+        <v>500</v>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:58.832484+07:00</t>
+        </is>
+      </c>
+      <c r="H904" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_418000.png</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr"/>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>สระแก้ว</t>
+        </is>
+      </c>
+      <c r="C905" t="n">
+        <v>875</v>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:03.148438+07:00</t>
+        </is>
+      </c>
+      <c r="H905" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_440401.png</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr"/>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>สิงห์บุรี</t>
+        </is>
+      </c>
+      <c r="C906" t="n">
+        <v>375</v>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:58.119836+07:00</t>
+        </is>
+      </c>
+      <c r="H906" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_416000.png</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr"/>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="C907" t="n">
+        <v>375</v>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:59.836569+07:00</t>
+        </is>
+      </c>
+      <c r="H907" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_425201.png</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr"/>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>สุราษฎร์ธานี</t>
+        </is>
+      </c>
+      <c r="C908" t="n">
+        <v>875</v>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:06.538682+07:00</t>
+        </is>
+      </c>
+      <c r="H908" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_551201.png</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>สุรินทร์</t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>375</v>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:55.906799+07:00</t>
+        </is>
+      </c>
+      <c r="H909" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_432201.png</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr"/>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>สุโขทัย</t>
+        </is>
+      </c>
+      <c r="C910" t="n">
+        <v>500</v>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:45.151185+07:00</t>
+        </is>
+      </c>
+      <c r="H910" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_373201.png</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B911" s="3" t="inlineStr">
+        <is>
+          <t>หนองคาย</t>
+        </is>
+      </c>
+      <c r="C911" s="3" t="n"/>
+      <c r="D911" s="3" t="inlineStr"/>
+      <c r="E911" s="3" t="inlineStr"/>
+      <c r="F911" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G911" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:48.971250+07:00</t>
+        </is>
+      </c>
+      <c r="H911" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_352201.png</t>
+        </is>
+      </c>
+      <c r="I911" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '(1375)'/'(1375)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>หนองบัวลำภู</t>
+        </is>
+      </c>
+      <c r="C912" t="n">
+        <v>625</v>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:50.925058+07:00</t>
+        </is>
+      </c>
+      <c r="H912" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_360201.png</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr"/>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>อำนาจเจริญ</t>
+        </is>
+      </c>
+      <c r="C913" t="n">
+        <v>500</v>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:52.568160+07:00</t>
+        </is>
+      </c>
+      <c r="H913" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_391201.png</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr"/>
+    </row>
+    <row r="914">
+      <c r="A914" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B914" s="3" t="inlineStr">
+        <is>
+          <t>อุดรธานี</t>
+        </is>
+      </c>
+      <c r="C914" s="3" t="n"/>
+      <c r="D914" s="3" t="inlineStr"/>
+      <c r="E914" s="3" t="inlineStr"/>
+      <c r="F914" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G914" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:49.016060+07:00</t>
+        </is>
+      </c>
+      <c r="H914" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
+        </is>
+      </c>
+      <c r="I914" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '(1375)'/'(1375)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>อุตรดิตถ์</t>
+        </is>
+      </c>
+      <c r="C915" t="n">
+        <v>500</v>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:42.379123+07:00</t>
+        </is>
+      </c>
+      <c r="H915" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_351201.png</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr"/>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>อุทัยธานี</t>
+        </is>
+      </c>
+      <c r="C916" t="n">
+        <v>500</v>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:56.589701+07:00</t>
+        </is>
+      </c>
+      <c r="H916" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_410201.png</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr"/>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>อุบลราชธานี</t>
+        </is>
+      </c>
+      <c r="C917" t="n">
+        <v>500</v>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:47.143501+07:00</t>
+        </is>
+      </c>
+      <c r="H917" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_407501.png</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr"/>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>อ่างทอง</t>
+        </is>
+      </c>
+      <c r="C918" t="n">
+        <v>375</v>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:57.367139+07:00</t>
+        </is>
+      </c>
+      <c r="H918" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_414000.png</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr"/>
+    </row>
+    <row r="919">
+      <c r="A919" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B919" s="3" t="inlineStr">
+        <is>
+          <t>เชียงราย</t>
+        </is>
+      </c>
+      <c r="C919" s="3" t="n"/>
+      <c r="D919" s="3" t="inlineStr"/>
+      <c r="E919" s="3" t="inlineStr"/>
+      <c r="F919" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G919" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:38.542378+07:00</t>
+        </is>
+      </c>
+      <c r="H919" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_303201.png</t>
+        </is>
+      </c>
+      <c r="I919" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '(1250)'/'(1250)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>เชียงใหม่</t>
+        </is>
+      </c>
+      <c r="C920" t="n">
+        <v>625</v>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:38.541860+07:00</t>
+        </is>
+      </c>
+      <c r="H920" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_327501.png</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>เพชรบุรี</t>
+        </is>
+      </c>
+      <c r="C921" t="n">
+        <v>375</v>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:56:04.732892+07:00</t>
+        </is>
+      </c>
+      <c r="H921" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_465201.png</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr"/>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="C922" t="n">
+        <v>0</v>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:47.115250+07:00</t>
+        </is>
+      </c>
+      <c r="H922" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_379201.png</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr"/>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>เลย</t>
+        </is>
+      </c>
+      <c r="C923" t="n">
+        <v>875</v>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:48.982924+07:00</t>
+        </is>
+      </c>
+      <c r="H923" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_353201.png</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr"/>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>แพร่</t>
+        </is>
+      </c>
+      <c r="C924" t="n">
+        <v>125</v>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:42.351786+07:00</t>
+        </is>
+      </c>
+      <c r="H924" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_330201.png</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr"/>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>แม่ฮ่องสอน</t>
+        </is>
+      </c>
+      <c r="C925" t="n">
+        <v>750</v>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>2026-10-30 00Z</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>อ่านได้</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:40.398035+07:00</t>
+        </is>
+      </c>
+      <c r="H925" s="2" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_300201.png</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I848"/>
+  <autoFilter ref="A1:I925"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -39259,6 +42368,83 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H846" r:id="rId845"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H847" r:id="rId846"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H848" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H849" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H850" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H851" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H852" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H853" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H854" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H855" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H856" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H857" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H858" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H859" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H860" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H861" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H862" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H863" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H864" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H865" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H866" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H867" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H868" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H869" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H870" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H871" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H872" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H873" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H874" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H875" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H876" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H877" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H878" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H879" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H880" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H881" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H882" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H883" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H884" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H885" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H886" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H887" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H888" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H889" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H890" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H891" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H892" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H893" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H894" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H895" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H896" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H897" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H898" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H899" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H900" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H901" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H902" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H903" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H904" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H905" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H906" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H907" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H908" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H909" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H910" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H911" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H912" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H913" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H914" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H915" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H916" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H917" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H918" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H919" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H920" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H921" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H922" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H923" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H924" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H925" r:id="rId924"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39270,7 +42456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -40136,8 +43322,148 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>พะเยา</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:40.510982+07:00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_310201.png</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '(1375)'/'(1375)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>หนองคาย</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:48.971250+07:00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_352201.png</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '(1375)'/'(1375)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>อุดรธานี</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:49.016060+07:00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_354201.png</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '(1375)'/'(1375)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>เชียงราย</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>รอตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:55:38.542378+07:00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>https://ozone.tmd.go.th/PM2.5/weather/Metgram/output/VR_daily/daily_VR_303201.png</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>number_ocr_uncertain: '(1250)'/'(1250)'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I24"/>
+  <autoFilter ref="A1:I28"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -40162,6 +43488,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
